--- a/data/input/asics.xlsx
+++ b/data/input/asics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979BC794-0C60-B74D-ACC8-163E04E68004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239C25E8-5CDA-524F-8779-81B50F5A1D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16020" yWindow="600" windowWidth="22380" windowHeight="21000" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="1" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="187">
   <si>
     <t>ID</t>
   </si>
@@ -205,10 +205,6 @@
     <t>At the same time, all of us at ASICS understand the thought that went into Mr. Onitsuka’s founding philosophy, which is the origin of our Company name. The “Sound Mind, Sound Body” concept declares our intention to create products based on human-centric science, compliance and meeting customer expectations without exception.</t>
   </si>
   <si>
-    <t>The ASICS business model is centered on highly competitive manufactured goods or “products.” As a sports equipment manufacturer, we develop products that are made at outsourced production factories and sold
-all over the world—this is our basic form. With this business model, ASICS strength lies in in the fact that it has established strong relationships of trust with materials and resource suppliers and production outsourcers. Outsourced production factories are rapidly expanding production lines based on demand forecasts and complying with production policies required by ASICS, which is made possible by the fact that ASICS conducted dialogues on equal terms to create better products.</t>
-  </si>
-  <si>
     <t>To continue the production and supply of products in a timely and appropriate manner, we are also working to prepare for unexpected disruptions in the supply chain. Going forward, we will transform our business model under the keywords “digital” and “sustainable” based on relationships of trust with the
 various partners that make up the ASICS supply chain, enhancing our existing strengths to make them even stronger.</t>
   </si>
@@ -236,10 +232,6 @@
 are being cancelled due to COVID-19, we launched the ASICS World Ekiden 2020 virtual relay race in which approximately 56,000 people participated. Going forward, we will continue to proactively hold both virtual and real world events.</t>
   </si>
   <si>
-    <t>Analysis and Diagnosis: Coaching Based on Personal Data
-Amid growing demand for running products, the number of subscribers to Runkeeper™, OneASICS™ and other digital services continues to grow. In terms of analysis and diagnosis, based on data collected by these digital services, ASICS will collaborate with other companies and combine personalized services to provide an unprecedented experience. In March 2021, we collaborated with CASIO COMPUTER CO., LTD. which possesses advanced sensing technologies, to launch the Runmetrix service, which visualizes running using a motion sensor attached to the runner’s waist to provide personal coaching services tailored to each individual. As a next step, in October we plan to launch provision of Walkmetrix for walkers.</t>
-  </si>
-  <si>
     <t>To realize our 10-year vision, we formulated Mid-Term Plan 2023 covering the crucial first three-year period. Before touching on that, I want to look back on the AGP2020, the previous three-year plan upon which the new one is based.</t>
   </si>
   <si>
@@ -247,9 +239,6 @@
   </si>
   <si>
     <t>ASICS must reflect on the previous mid-term plan, squarely address issues that have emerged since the onset of COVID-19 and improve our management structure to generate profits.</t>
-  </si>
-  <si>
-    <t>At the same time, we will promote innovations. From fiscal 2019 up to now, we combined existing organizations separated by function into five categories promoting business that integrates manufacturing and sales. This category system has strengthened management visualization and collaborations between the Head Office and sales companies, significantly transforming the management cycle. Even amid the turmoil caused by COVID-19, we were able to respond quickly in each region, securing funds and managing inventory properly, evidence that our category system worked well. Even in Performance Running, where we have stepped up efforts as a product growth area, the addition of functions reflecting feedback from sales companies has improved ASICS product evaluations, which I feel will be seen in future business performance. e-Commerce (EC) is also expanding rapidly, as consumers shift to more digital purchases. In the new mid-term plan, based on reflection points and issues raised so far, we will carefully cultivate the green shoots that have begun to emerge and promote the necessary reforms by crouching low and leaping high.</t>
   </si>
   <si>
     <t>Under the Mid-Term Plan 2023, we will continue major policies from the previous plan by maintaining our focus on the Performance Running category, accelerating growth in China and improving profitability in the apparel and ASICS operated store categories. We will allocate management resources most heavily in the digital category with the aim of transitioning to digitally-focused management. By region, while accelerating growth in Greater China and further expanding profits in Oceania, we will accelerate growth while investing in India, Indonesia and the Middle East, areas that are expected to become pillars of earnings in the future. In mature markets such as Japan, the United States and Europe, we will focus on improving profitability.</t>
@@ -306,6 +295,335 @@
   <si>
     <t>While passing on our founding philosophy, ASICS will continue to provide valuable products and services to sports lovers and all ASICS stakeholders by adapting changes in line with today’s digital revolution. Additionally, we will contribute to the realization of a sustainable environment and society by focusing on sustainability in all our business activities. ASICS will be intimately involved in exercise and sports for the rest of our lives and will continue to strive toward the realization of a world in which everyone has a healthy mind
 and body. We ask for your continued understanding and support of ASICS stance and initiatives.</t>
+  </si>
+  <si>
+    <t>body_text</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title </t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>positive</t>
+  </si>
+  <si>
+    <t>STRAT</t>
+  </si>
+  <si>
+    <t>MARKET</t>
+  </si>
+  <si>
+    <t>JPN20A01-01</t>
+  </si>
+  <si>
+    <t>JPN20A01-00</t>
+  </si>
+  <si>
+    <t>JPN20A01-02</t>
+  </si>
+  <si>
+    <t>JPN20A01-03</t>
+  </si>
+  <si>
+    <t>JPN20A01-04</t>
+  </si>
+  <si>
+    <t>JPN20A01-05</t>
+  </si>
+  <si>
+    <t>PERF</t>
+  </si>
+  <si>
+    <t>STAKE</t>
+  </si>
+  <si>
+    <t>The ASICS business model is centered on highly competitive manufactured goods or “products.” As a sports equipment manufacturer, we develop products that are made at outsourced production factories and sold
+all over the world—this is our basic form. With this business model, ASICS strength lies in in the fact that it has established strong relationships of trust with materials and resource suppliers and production outsourcers.</t>
+  </si>
+  <si>
+    <t>Outsourced production factories are rapidly expanding production lines based on demand forecasts and complying with production policies required by ASICS, which is made possible by the fact that ASICS conducted dialogues on equal terms to create better products.</t>
+  </si>
+  <si>
+    <t>CHALL</t>
+  </si>
+  <si>
+    <t>negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analysis and Diagnosis: Coaching Based on Personal Data
+Amid growing demand for running products, the number of subscribers to Runkeeper™, OneASICS™ and other digital services continues to grow. In terms of analysis and diagnosis, based on data collected by these digital services, ASICS will collaborate with other companies and combine personalized services to provide an unprecedented experience. </t>
+  </si>
+  <si>
+    <t>In March 2021, we collaborated with CASIO COMPUTER CO., LTD. which possesses advanced sensing technologies, to launch the Runmetrix service, which visualizes running using a motion sensor attached to the runner’s waist to provide personal coaching services tailored to each individual. As a next step, in October we plan to launch provision of Walkmetrix for walkers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the same time, we will promote innovations. From fiscal 2019 up to now, we combined existing organizations separated by function into five categories promoting business that integrates manufacturing and sales. This category system has strengthened management visualization and collaborations between the Head Office and sales companies, significantly transforming the management cycle. Even amid the turmoil caused by COVID-19, we were able to respond quickly in each region, securing funds and managing inventory properly, evidence that our category system worked well. Even in Performance Running, where we have stepped up efforts as a product growth area, the addition of functions reflecting feedback from sales companies has improved ASICS product evaluations, which I feel will be seen in future business performance. e-Commerce (EC) is also expanding rapidly, as consumers shift to more digital purchases. </t>
+  </si>
+  <si>
+    <t>In the new mid-term plan, based on reflection points and issues raised so far, we will carefully cultivate the green shoots that have begun to emerge and promote the necessary reforms by crouching low and leaping high.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">neutral </t>
+  </si>
+  <si>
+    <t>JPN20A02-00</t>
+  </si>
+  <si>
+    <t>JPN20A02-01</t>
+  </si>
+  <si>
+    <t>JPN20A02-02</t>
+  </si>
+  <si>
+    <t>JPN20A02-03</t>
+  </si>
+  <si>
+    <t>JPN20A02-04</t>
+  </si>
+  <si>
+    <t>JPN20A03-00</t>
+  </si>
+  <si>
+    <t>JPN20A03-01</t>
+  </si>
+  <si>
+    <t>JPN20A03-02</t>
+  </si>
+  <si>
+    <t>JPN20A03-03</t>
+  </si>
+  <si>
+    <t>JPN20A04-00</t>
+  </si>
+  <si>
+    <t>JPN20A04-01</t>
+  </si>
+  <si>
+    <t>JPN20A04-02</t>
+  </si>
+  <si>
+    <t>JPN20A04-03</t>
+  </si>
+  <si>
+    <t>JPN20A05-00</t>
+  </si>
+  <si>
+    <t>JPN20A05-01</t>
+  </si>
+  <si>
+    <t>JPN20A05-02</t>
+  </si>
+  <si>
+    <t>JPN20A05-03</t>
+  </si>
+  <si>
+    <t>JPN20A05-04</t>
+  </si>
+  <si>
+    <t>JPN20A05-05</t>
+  </si>
+  <si>
+    <t>JPN20A05-06</t>
+  </si>
+  <si>
+    <t>JPN20A05-07</t>
+  </si>
+  <si>
+    <t>JPN20A06-00</t>
+  </si>
+  <si>
+    <t>JPN20A06-01</t>
+  </si>
+  <si>
+    <t>JPN20A06-02</t>
+  </si>
+  <si>
+    <t>JPN20A06-03</t>
+  </si>
+  <si>
+    <t>JPN20A06-04</t>
+  </si>
+  <si>
+    <t>JPN20A06-05</t>
+  </si>
+  <si>
+    <t>JPN20A07-00</t>
+  </si>
+  <si>
+    <t>JPN20A07-01</t>
+  </si>
+  <si>
+    <t>JPN20A07-02</t>
+  </si>
+  <si>
+    <t>JPN20A07-03</t>
+  </si>
+  <si>
+    <t>JPN20A07-04</t>
+  </si>
+  <si>
+    <t>JPN20A07-05</t>
+  </si>
+  <si>
+    <t>JPN20A07-06</t>
+  </si>
+  <si>
+    <t>JPN20A08-00</t>
+  </si>
+  <si>
+    <t>JPN20A08-01</t>
+  </si>
+  <si>
+    <t>JPN20A08-02</t>
+  </si>
+  <si>
+    <t>JPN20A08-03</t>
+  </si>
+  <si>
+    <t>JPN20A09-00</t>
+  </si>
+  <si>
+    <t>JPN20A09-01</t>
+  </si>
+  <si>
+    <t>JPN20A09-02</t>
+  </si>
+  <si>
+    <t>JPN20A09-03</t>
+  </si>
+  <si>
+    <t>JPN20A09-04</t>
+  </si>
+  <si>
+    <t>JPN20A10-00</t>
+  </si>
+  <si>
+    <t>JPN20A10-01</t>
+  </si>
+  <si>
+    <t>JPN20A10-02</t>
+  </si>
+  <si>
+    <t>JPN20A10-03</t>
+  </si>
+  <si>
+    <t>JPN20A10-04</t>
+  </si>
+  <si>
+    <t>JPN20A10-05</t>
+  </si>
+  <si>
+    <t>JPN20A10-06</t>
+  </si>
+  <si>
+    <t>JPN20A10-07</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>StRAT</t>
+  </si>
+  <si>
+    <t>STRAT-MARKET</t>
+  </si>
+  <si>
+    <t>With the results of our reforms now steadily materializing, in 2022 we will seek even further progress while carrying on the legacy of Tokyo 2020.</t>
+  </si>
+  <si>
+    <t>Review of 2021</t>
+  </si>
+  <si>
+    <t>The results of reforms are powerfully reflected in business performance</t>
+  </si>
+  <si>
+    <t>Last year I mentioned that in Mid-Term Plan 2023, we would aspire to reforms that involve “digging deep and jumping high.” It turned out that in 2021, the results of past reforms were strongly reflected in our business performance, making it a year in which we built solid founda- tions toward future growth. Our biggest accomplishment was seeing through our role as a Gold Partner to the Tokyo 2020 Games. This filled us with a great deal of confidence. Despite almost no opportunities for merchandise sales at venues due to events being held without spectators, over the course of the Games we managed to draw global attention to the ASICS brand through the media. We also saw positive business performance. Net sales returned to the 400 billion yen range and operating income broke 20 billion yen for the first time in five years, with each profit metric going back into positive territory.</t>
+  </si>
+  <si>
+    <t>The health-conscious movement will continue in a post-COVID world</t>
+  </si>
+  <si>
+    <t>Looking at the business environment, although we have still not over- come COVID-19, rates of participation in sports such as walking and running have risen above pre-pandemic levels, against a backdrop of rising health consciousness. ASICS future vision of ensuring a world in which each and every one of us can engage in exercise and sports throughout our lives and continue to live in good health, both mentally and physically (Lifetime Athletes in All of Us) is also riding this global trend of health awareness, and we expect that when restrictions under the pandemic are eliminated, this movement will gain even greater momentum.</t>
+  </si>
+  <si>
+    <t>Due to the spread of COVID-19 infections, last year ASICS temporarily suspended operations at its Vietnam factory, which accounts for almost half of its total production, but even when these risks materialized, we managed to secure profits by swiftly implementing measures such as reducing low-profit items and revising inventory. There are many other risks lurking in supply chains, but we will take proper measures and seize upon the significant growth opportunities that tailwinds bring.</t>
+  </si>
+  <si>
+    <t>Category strategies, winning in the realm of performance running</t>
+  </si>
+  <si>
+    <t>With “winning at performance running” positioned as our top priority, we have expanded our product lineup of shoes that meet all manner of runner needs. As a result, in 2021 we saw strong growth in the performance running category, recording an increase of 30% year on year. METASPEED™, our speed-focused model for top athletes, even helped some top athletes on the way to achieving personal bests.</t>
+  </si>
+  <si>
+    <t>Aiming to recapture the leading position among top athletes</t>
+  </si>
+  <si>
+    <t>METASPEED™ is a strategic product that is part of the Chojo Project (C Project) designed to recapture a leading market share in the area of top athletes. The shoes even received an award from the world’s most prestigious running magazine. At the New Year Ekiden and Hakone Ekiden held in January 2021, we faced the frustrating experience of zero athletes competing in ASICS shoes, but this year we earned the support of over 10% of athletes, and managed to impress the world with the beginnings of ASICS’ counterattack. Seeing success from the C Project has led to improved confidence and unifying force on our part, and we are committed to breaking our competitors' stranglehold in the area of top athletes by releasing new products with improved functionality.</t>
+  </si>
+  <si>
+    <t>Current status and future of the global portfolio</t>
+  </si>
+  <si>
+    <t>Over 75% of ASICS’ sales come from overseas. Operations in Australia and Europe are highly profitable, followed closely by China, and although operations in Japan and the US have moved into the black, further improvements to profitability remain as an issue. Of all these regions, ASICS is focused on product strength and attentive sales in the U.S., a dominant country in the running world where it aims to achieve a leading market share.</t>
+  </si>
+  <si>
+    <t>Passing on the legacy of the Tokyo 2020 Games to future generations</t>
+  </si>
+  <si>
+    <t>The Tokyo 2020 Games are over, and efforts have gotten underway to pass on insights gained from the experience as a legacy for future generations. One of these is Para Sports. If ASICS is serious about striving to ensure a world in which each and every one of us can engage in exercise and sports throughout our lives and continue to live in good health, both mentally and physically, it must make a full-fledged commitment to Para Sports. I personally have experience serving as a guide runner for a blind marathon athlete, and believe that we can gain insights and new lessons by deepening our understanding of Para Sports and people with disabilities. With the Para Sports Planning Department that was newly established this year playing a central role, we will start by considering development based around running and walking.</t>
+  </si>
+  <si>
+    <t>Another of these insights is to do with new sports. Among these, starting this year ASICS will make a full-scale entry into the US markets in addition to Japan for skateboarding, whose competitive population is expected to grow in the future. Skateboarding is a sport that involves split-second skills and is the subject of a thriving area of digital analysis. By combining its technologies in many ways, ASICS will be able to create value that goes beyond the conventional provision of products, including in the area of facilities &amp; community digitally providing locations and communities for people to enjoy sports, and the area of analysis &amp; diagnosis involving the provision of analysis and diagnostic findings using data obtained from those activities. Beyond the fusion of sport and digital technologies, we also hope to develop the new world of e-sports. We also aim to further expand the scope of the C Project that has to date focused on middle and long distances in track and field in a serious attempt to reach the pinnacle of performance in short distance and sprinting categories as well. We have begun developing new products and signing deals with athletes, aiming to reach the summit together with athletes who have the ability to make the podium in international competition for track and field’s highest profile event, the 100-meter sprint. In Japan, the support culture of TEAM RED that was cultivated during the Tokyo 2020 Games and the SUNRISE RED attire worn by Japanese Olympic athletes will continue to be passed down in the future. We will weave a legacy for the next generation in terms of both products and branding to ensure the idea that “ASICS is associated with the Olympics and Paralympics” firmly takes root.</t>
+  </si>
+  <si>
+    <t>Towards medium and long-term growth</t>
+  </si>
+  <si>
+    <t>Switching to management based on digital technologies</t>
+  </si>
+  <si>
+    <t>In Mid-Term Plan 2023 formulated to achieve the long-term VISION 2030, ASICS has positioned digital strategy as one of its strategic goals. While continuing to emphasize the need to cash in on our existing businesses, we will seek to maximize efficiency gains and profitability across the supply chain with new business development and new business models with digital at their core.</t>
+  </si>
+  <si>
+    <t>Working from a base of more than 5.8 million members (as of February 28, 2022) on our free membership-based service OneASICSTM, we will organically link the smartphone-based exercise recording app RunkeeperTM used in about 250 countries and regions around the world with the Race Roster race sign-up platform mainly used in the US and Canada and the Register Now race sign-up platform in Australia. Together with these services, we will form a worldwide running ecosystem providing services to runners, including through Runmetrix, which uses sensor technologies to measure running in real time and provide coaching, and Shoe Finder, which recommends shoes that are best for each individual based on their running style and images of their feet taken with a smartphone. In addition, in 2021 we launched ASICS STEPNOTE, an app-based service that measures the size of small children’s feet and predicts their growth to recommend the right shoes, reflecting our efforts to also develop a kids ecosystem. To make this running ecosystem a reality, we will need to foster and instill an organizational culture that thinks of everything in digital terms. We will transform ASICS into a digitally-driven company by appointing human resources from the digital native generation and re-skilling employees.</t>
+  </si>
+  <si>
+    <t>Sustainability is the core of management</t>
+  </si>
+  <si>
+    <t>Another strategic goal declared in Mid-Term Plan 2023 is sustainability. Sport is a symbol of peace, and sports will not be possible unless a good global environment is preserved. As a sports-related manufacturer, ASICS sees protecting a global environment that enables sports to be synonymous with safeguarding its own survival as a business.</t>
+  </si>
+  <si>
+    <t>In terms of consideration for the environment, in 2019 ASICS was the first sports-related manufacturer in the world to indicate support for the recommendations of the Task Force on Climate-related Financial Disclosures (TCFD), and to achieve the goal of reducing our CO2 emissions by 63% compared with 2015 levels by the year 2030, we are pursuing the initiatives outlined below.</t>
+  </si>
+  <si>
+    <t>(1) We are shifting to 100% renewable energy usage at domestic operating sites and promoting a shift to renewable energies at contracted production factories. (2) We have promoted recycling-oriented production utilizing recycled materials for at least 90% of new shoe products, and are continuing efforts with the ultimate goal of using 100% recycled materials for polyester, a major material used in our products. (3) In terms of finance, we have issued Japan’s first sustainability-linked bonds in which CO2 emission credits are purchased based on the target achievement levels. Measures to combat climate change are more effective when companies cooperate with one another through teamwork instead of going it alone. Going forward, ASICS will continue to run at the head of the pack and lead the way with sustainable initiatives.</t>
+  </si>
+  <si>
+    <t>From the perspective of contributing to society, we will work harder to improve working environments for the many skilled workers involved with our shoe manufacturing processes in Vietnam, Indonesia, Cambodia and elsewhere. Since shoes feature many curves, there are many aspects to the manufacturing process that rely on skilled manual sewng work, and retaining skilled workers in these areas is extremely important for maintaining and improving production quality. We have been implementing human rights due diligence activities in our overseas supply chains for more than two decades, and have introduced internal reporting systems and developed mechanisms to conduct engagement surveys and other activities simultaneously on a global basis. Each year we conduct technical skills training for more than 60 of our primary, secondary and tertiary suppliers, and also continue efforts to enhance welfare benefits and offer higher wages than our competitors. While being interrupted by the COVID-19 pandemic, I usually visit our manufacturing factories once a year to speak with factory managers and check working  conditions on-site. To ensure that ASICS is the choice for multiple stakeholders, including employees and customers, sustainability is the core of management.</t>
+  </si>
+  <si>
+    <t>Digitally minded human resources are the subject of intense competition for recruitment. At ASICS, some 400 digitally-literate human resources collaborate organically in Boston (headquarters of ASICS Digital), Toronto (Digital Strategy Development Division) and Amsterdam (IT Headquarters) with a sense of speed and sensitivity to human rights, leading the way in fostering and enhancing the digital mindset of all employees</t>
+  </si>
+  <si>
+    <t>Making 2022 a breakthrough year!</t>
+  </si>
+  <si>
+    <t>In 2022, the uncertain management environment is ongoing, with the prolonged COVID-19 pandemic, Russia’s invasion of Ukraine and other developments. But on the starting line for ASICS is a solid foundation built through past reforms, and I believe that 2022 will be a breakthrough year for us. By “breakthrough” I don’t mean rapid growth as a result of something accidental; I envisage significant growth as a result of all our efforts to date.</t>
+  </si>
+  <si>
+    <t>As the world changes, so will the way sports are played, enjoyed and supported. ASICS will continue to pass down its founding philosophy of “a sound mind in a sound body (“Anima Sana In Corpore Sano”) and the “Sound Mind, Sound Body” brand tagline while providing products and services that are valuable to all sports enthusiasts and stakeholders involved with ASICS’ businesses through reforms consistent with the today’s digital revolution. As a member of top management, I promise that we will seize upon changes in the times and major opportunities, engage in sound and transparent management, and enhance corporate value sustainably in the long term.</t>
+  </si>
+  <si>
+    <t>I hope that all of our stakeholders will look forward to seeing the ASICS Group achieve significant growth through the actions we take in line with the strategies and policies we have set forth.</t>
   </si>
 </sst>
 </file>
@@ -626,48 +944,48 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L57" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L57" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L60" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
+  <autoFilter ref="A1:L60" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="81"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L2" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L31" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L31" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1086,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3826A9C-6C80-494E-9252-B920A5705A8F}">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1145,6 +1463,12 @@
       <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>43</v>
       </c>
@@ -1165,9 +1489,18 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>43</v>
       </c>
@@ -1188,9 +1521,21 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>43</v>
       </c>
@@ -1211,9 +1556,21 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>43</v>
       </c>
@@ -1234,9 +1591,21 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>43</v>
       </c>
@@ -1257,9 +1626,21 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>43</v>
       </c>
@@ -1280,9 +1661,21 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>43</v>
       </c>
@@ -1303,9 +1696,21 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>43</v>
       </c>
@@ -1326,9 +1731,21 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="C10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>43</v>
       </c>
@@ -1349,9 +1766,21 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="C11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>43</v>
       </c>
@@ -1372,9 +1801,18 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="C12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
@@ -1395,8 +1833,17 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>43</v>
@@ -1421,6 +1868,15 @@
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="C14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="F14" s="1" t="s">
         <v>43</v>
       </c>
@@ -1441,9 +1897,21 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="C15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="F15" s="1" t="s">
         <v>43</v>
       </c>
@@ -1463,969 +1931,1485 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="B16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" ht="102" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="s">
+      <c r="C18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
+      <c r="C20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" ht="102" x14ac:dyDescent="0.2">
-      <c r="B20" s="2" t="s">
+      <c r="C21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" ht="136" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" ht="170" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
+      <c r="C25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" ht="187" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" ht="204" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
+      <c r="C27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" ht="187" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
+      <c r="C30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
+      <c r="C33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" ht="221" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
+      <c r="C34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
+      <c r="C39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" ht="272" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
+      <c r="C40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" ht="170" x14ac:dyDescent="0.2">
-      <c r="B36" s="2" t="s">
+      <c r="C41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="B37" s="2" t="s">
+      <c r="C42" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" ht="170" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
+      <c r="C43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" ht="119" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
+      <c r="C45" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" ht="68" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
+      <c r="C46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B42" s="2" t="s">
+      <c r="C47" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" ht="153" x14ac:dyDescent="0.2">
-      <c r="B43" s="2" t="s">
+      <c r="C50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I43" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" ht="170" x14ac:dyDescent="0.2">
-      <c r="B44" s="2" t="s">
+      <c r="C51" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I44" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B45" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I46" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" ht="102" x14ac:dyDescent="0.2">
-      <c r="B47" s="2" t="s">
+      <c r="C52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" ht="85" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
+      <c r="C55" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" ht="187" x14ac:dyDescent="0.2">
-      <c r="B49" s="2" t="s">
+      <c r="C56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I49" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B50" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I50" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B51" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I51" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" ht="204" x14ac:dyDescent="0.2">
-      <c r="B52" s="2" t="s">
+      <c r="C57" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" ht="136" x14ac:dyDescent="0.2">
-      <c r="B53" s="2" t="s">
+      <c r="C58" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I53" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" ht="170" x14ac:dyDescent="0.2">
-      <c r="B54" s="2" t="s">
+      <c r="C59" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I54" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" ht="170" x14ac:dyDescent="0.2">
-      <c r="B55" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I55" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11" ht="204" x14ac:dyDescent="0.2">
-      <c r="B56" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I56" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11" ht="170" x14ac:dyDescent="0.2">
-      <c r="B57" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I57" s="1">
-        <v>2020</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K57" s="1" t="s">
+      <c r="F60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="1">
+        <v>2020</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2440,11 +3424,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD18CE3-D2D1-DD49-8602-5C2A7C693BA7}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="100.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -2492,11 +3476,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2511,6 +3500,151 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="B5" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="B8" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="255" x14ac:dyDescent="0.2">
+      <c r="B17" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="187" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" ht="136" x14ac:dyDescent="0.2">
+      <c r="B25" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" ht="187" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" ht="102" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="B31" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/asics.xlsx
+++ b/data/input/asics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239C25E8-5CDA-524F-8779-81B50F5A1D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA462953-C6BA-D04B-B48E-EEF02C276102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="1" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="2" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="253">
   <si>
     <t>ID</t>
   </si>
@@ -624,6 +624,208 @@
   </si>
   <si>
     <t>I hope that all of our stakeholders will look forward to seeing the ASICS Group achieve significant growth through the actions we take in line with the strategies and policies we have set forth.</t>
+  </si>
+  <si>
+    <t>JPN21A01-00</t>
+  </si>
+  <si>
+    <t>JPN21A01-01</t>
+  </si>
+  <si>
+    <t>JPN21A01-02</t>
+  </si>
+  <si>
+    <t>JPN21A01-03</t>
+  </si>
+  <si>
+    <t>JPN21A01-04</t>
+  </si>
+  <si>
+    <t>JPN21A01-05</t>
+  </si>
+  <si>
+    <t>JPN21A01-06</t>
+  </si>
+  <si>
+    <t>JPN21A01-07</t>
+  </si>
+  <si>
+    <t>JPN21A01-08</t>
+  </si>
+  <si>
+    <t>JPN21A01-09</t>
+  </si>
+  <si>
+    <t>JPN21A01-10</t>
+  </si>
+  <si>
+    <t>JPN21A01-11</t>
+  </si>
+  <si>
+    <t>JPN21A01-12</t>
+  </si>
+  <si>
+    <t>JPN21A01-13</t>
+  </si>
+  <si>
+    <t>JPN21A01-14</t>
+  </si>
+  <si>
+    <t>JPN21A002-00</t>
+  </si>
+  <si>
+    <t>JPN21A002-01</t>
+  </si>
+  <si>
+    <t>JPN21A002-02</t>
+  </si>
+  <si>
+    <t>JPN21A002-03</t>
+  </si>
+  <si>
+    <t>JPN21A002-04</t>
+  </si>
+  <si>
+    <t>JPN21A002-05</t>
+  </si>
+  <si>
+    <t>JPN21A002-06</t>
+  </si>
+  <si>
+    <t>JPN21A002-07</t>
+  </si>
+  <si>
+    <t>JPN21A002-08</t>
+  </si>
+  <si>
+    <t>JPN21A002-09</t>
+  </si>
+  <si>
+    <t>JPN21A002-10</t>
+  </si>
+  <si>
+    <t>JPN21A002-11</t>
+  </si>
+  <si>
+    <t>JPN21A002-12</t>
+  </si>
+  <si>
+    <t>JPN21A002-13</t>
+  </si>
+  <si>
+    <t>With a following wind, we will continue to achieve breakthroughs, aiming to enable anyone to continue to live in good physical and mental health over the course of their lives.</t>
+  </si>
+  <si>
+    <t>In the Current Business Environment, We Have a Following Wind</t>
+  </si>
+  <si>
+    <t>Regardless of the era, people have an unwavering desire to stay healthy. People’s growing health awareness, which was triggered by the COVID-19 pandemic, is a following wind for ASICS as a company operating business focused on exercise and sports which are essential for leading a healthy life. I myself feel refreshed when exercising. Every time I get that feeling, I am reminded of the greatness of the power of sports. In addition, the relationships and happiness made possible by playing sports with friends are invaluable. Due to the easing of COVID-19 restrictions, we are finally allowed to watch sports in stadiums and cheer loudly. I believe that many people now understand the appeal of watching, cheering, supporting and playing sports.</t>
+  </si>
+  <si>
+    <t>VISION 2030 Incorporating Our Founding Philosoph</t>
+  </si>
+  <si>
+    <t>In 2020, we created VISION 2030, a long-term vision for 2030, a decade into the future. It was formulated mainly by the young employees who will play core roles in ASICS in 2030. The thoughts of our founder, Kihachiro Onitsuka, are surely reflected in one of the vision’s goals, ensuring a world in which each and every one of us can engage in exercise and sports throughout our lives and continue to live in good health, both mentally and physically. He founded ASICS with a desire to enable young people to develop soundly through sports at a time when Japanese society was struggling in the aftermath of World War II. The founding philosophy, “ANIMA SANA IN CORPORE SANO (a Latin phrase for ‘a sound mind in a sound body’)” is the origin of ASICS. It is also the name of the company</t>
+  </si>
+  <si>
+    <t>In Japan, a country known for the longevity of its people, there is now an approx. ten-year gap between the physical life expectancy and the healthy life expectancy for both men and women. Initiatives for achieving the Vision also lead to a longer healthy life expectancy.</t>
+  </si>
+  <si>
+    <t>Toward a Future Where Anyone Can Continue to Live In Good Physical and Mental Health over the Course of Their Lives</t>
+  </si>
+  <si>
+    <t>To achieve the Vision, we will focus our efforts on three business domains in the medium term</t>
+  </si>
+  <si>
+    <t>The focus of our business has been products, including shoes and apparel. Going forward, we will also focus our efforts on the provision of programs and services which will help people improve their health by increasing the effect of exercise more safely and effectively based on analyses and diagnoses using digital technologies while creating sports facilities and communities. We aim to achieve an operating income ratio of 10% while increasing net sales in the three business domains of Products, Facilities &amp; Communities, and Analysis &amp; Diagnosis to the same level.</t>
+  </si>
+  <si>
+    <t>On the other hand, a peaceful, stable society is necessary for there to be an environment where people can play sports. ASICS recognizes geopolitical risks, including the Russian invasion of Ukraine that began last year, and an unstable economic environment to be risks.</t>
+  </si>
+  <si>
+    <t>Breakthroughs Achieved in 2022</t>
+  </si>
+  <si>
+    <t>In the integrated report published last year, I positioned 2022 as a breakthrough year and vowed to achieve significant growth as a result of all our efforts to date. Now, 2022 is over and I am very happy to show you that we are a company that has achieved major breakthroughs.</t>
+  </si>
+  <si>
+    <t>In 2022, the business environment was affected by the COVID-19 pandemic, with the number of infected people remaining large even though the pandemic subsided. A typical example of this was the lockdown in China. In this environment, we achieved the numerical targets set in Mid-Term Plan 2023 a year earlier. Net sales grew by double digits in all regions, to a record high of 484.6 billion yen. Operating income also reached a record high of 34.0 billion yen (with an operating income ratio of 7.0%), both far exceeding the targets in the Mid-Term Plan. We have also achieved various other KPI targets in the Mid-Term Plan released the previous year, including the ratio of e-commerce net sales to overall net sales, the number of OneASICS members and the female manager ratio</t>
+  </si>
+  <si>
+    <t>These Breakthroughs Were Achieved by Mobilizing the Capabilities of All Employees Globally</t>
+  </si>
+  <si>
+    <t>With a profit-oriented mission, all of the employees shared and understood each measure globally and worked on them together uncompromisingly, moving in the same direction, focused on the two axes of digital technologies and sustainability. This produced quantifiable results. They changed their thinking, shifting from a sales-oriented approach to a profit- oriented one while sales subsidiaries responded to the transition to a category-based structure. These and other understandable struggles were experienced by the people working on-site. I feel sure that the efforts accelerated in this way supported the breakthroughs achieved in 2022 and form the foundation for the breakthrough that will be achieved in and after 2023.</t>
+  </si>
+  <si>
+    <t>2022 breakthroughs 1 Evolution of the Running Ecosystem</t>
+  </si>
+  <si>
+    <t>Race registration is a key point in the process of building a running ecosystem, through which we are able to comprehensively support runners, including the provision of shoes and other products, time measurement services, training programs, and supporting race participation. Starting in 2019, we acquired race registration companies in North America and Australia. In 2022, we affiliated with race registration companies in Japan and Europe who became new members of the ASICS Group. This enabled us to connect with approx. 12 million runners. We will attract them to OneASICS, thus expanding the reach of our products and services. In addition, the acquisition of race registration companies, which provide services digitally, has led to the enhancement of the digital human resources of the ASICS Group.</t>
+  </si>
+  <si>
+    <t>2022 breakthroughs 2 World Athletics Championships Oregon 22</t>
+  </si>
+  <si>
+    <t>In the World Athletics Championships held in 2022 in Oregon, the United States, which is a key region for ASICS, athletes wearing METASPEED series performed brilliantly. Thus, a certain degree of achievement was seen in the Chojo Project (C Project) designed to recapture a leading market share in the area of top athletes. In addition, we took the Oregon 22 as an opportunity to deploy promotional vehicles all across the United States to enable non- professional runners to see and use ASICS products. This strongly increased the appeal of the ASICS brand to consumers. We will continue this kind of initiatives.</t>
+  </si>
+  <si>
+    <t>2022 breakthroughs 3 The Lightest CO2 Sneaker*
+* Based on available industry data for life cycle CO2e emissions as of Sep. 2022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the product front, we developed and announced GEL-LYTE III CM 1.95, The lightest CO2 sneaker throughout the product lifecycle were limited to 1.95 kg CO2e. The CO2 emitted by a typical shoe is believed to be 8 to 12 kg CO2e. For this product, we developed technologies by identifying measures to reduce emissions throughout the product lifecycle, including material procurement, manufacturing, transportation, use and disposal. We also made it comfortable to wear and applied uncompromising standards in the functional aspects, as is expected of ASICS. This product is scheduled to be released in the autumn of 2023. We will use the knowledge we have obtained this time for our future products.
+</t>
+  </si>
+  <si>
+    <t>Room for Growth Is Konna Mon Janai (Far More than This)</t>
+  </si>
+  <si>
+    <t>I feel that the room for growth to be achieved in and after 2023 is Konna Mon Janai (far more than this). Konna Mon Janai (far more than this) is the catchphrase for METASPEED, which also achieved a breakthrough in the Ekiden relay races held in the beginning of this year. I feel certain that by addressing the issues recognized in 2022, the year when we achieved the best performance ever, we can continue to set new records in and after 2023.</t>
+  </si>
+  <si>
+    <t>One of the issues that we had yet to address in 2022 is in the apparel business. We will restore the profitability of this business in 2023. Target regions are North America and Japan. In the US, net sales grew significantly, but not with profit. We will increase profit by narrowing down the apparel products we provide, closing unprofitable directly operated stores, ensuring that we attach importance to profit in our sales channels, and strengthening e-commerce. In Japan, we will also narrow down the apparel products we provide and position tennis, football, and
+basketball as our sports of focus. In addition, we will also dedicate efforts to work shoes, sales of which are strong in recent years. We will reinforce our profit structure through these initiatives.</t>
+  </si>
+  <si>
+    <t>Emerging Countries Will Be a Growth Driver in the Medium and Long Term</t>
+  </si>
+  <si>
+    <t>One of the key drivers of our future growth is emerging countries. In the city of Mumbai, India, which I visited at the beginning of this year, I was surprised to see the streets already filled with runners in the morning. India, where one of ASICS’ shoes production factories is located, has a big advantage in that local production for local consumption is possible. We aim to achieve net sales of 10.0 billion yen as soon as possible in this growth market where the population is increasing remarkably and the economy is growing. In Southeast Asia, we will focus our efforts on Indonesia and Vietnam, where the average age is low and economic growth continues, in addition to our existing markets of Singapore, Thailand, and Malaysia. South American markets, such as Brazil, Chile and Columbia, and the Middle East market, where the growth of the exercising population is mainly occurring in Saudi Arabia, are also attractive. We will expand our business, which we have been operating mainly in North America, Europe, Japan, Greater China, and Australia, even more broadly to other countries in the world.</t>
+  </si>
+  <si>
+    <t>Performance Running Drives Other Categories of Business</t>
+  </si>
+  <si>
+    <t>Regarding our business categories, we will enhance the presence of performance running, where we have a full lineup in various aspects, including types of runners and price ranges. In Greater China, ASICS continued to grow during the COVID-19 pandemic thanks to the communication of its brand image, “Choose ASICS if you run or do exercise.” The brand’s enhanced presence in the realm of performance running positively impacts other categories of business. Further, in addition to the existing business categories, we will continue to take on challenges in Para Sports, urban sports, and e-sports as three areas that we established after the end of the Tokyo Olympics and Paralympics as areas where we want to establish a legacy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human Capital and Intellectual Capital Support Brand Value
+</t>
+  </si>
+  <si>
+    <t>Regarding intangible assets, it is important that we surely protect the brand and increase its value. This is supported by human capital and intellectual capital. It is said that business is people. Improving the environment to attract many highly talented human resources to ASICS and enable them to work leveraging diverse work styles is also a duty I have as a top manegement. We would like to collect human resources to ensure that ASICS stays an organization where human resources can grow. In addition, ASICS operates its business with a focus on innovation, so we are fully aware of intellectual property. We will acquire patents and rights while proceeding with projects, and intellectual properties are among the arrows in our quiver.</t>
+  </si>
+  <si>
+    <t>The Environment, Human Rights, and Sustainable Procurement are Central to Managemen</t>
+  </si>
+  <si>
+    <t>It is not possible to play sports on a scorching planet. Therefore, we will accelerate initiatives to address climate change by positioning the protection of the environment of a planet where playing sports is possible as an important task that is vital to the survival of ASICS. ASICS advances initiatives by sharing a specific roadmap toward the achievement of net-zero emissions from its entire supply chain by 2050. Once a year, I visit production factories, which have an extremely important place in the supply chain, to check their actual conditions in person. We will take initiatives to protect the human rights of workers and improve their work environment, such as streamlining production through mechanization, while also establishing systems and operations that prevent child labor, excessive work hours, and other problems. In addition, to protect the global environment, we will accelerate the shift of our production factories to renewable energy.</t>
+  </si>
+  <si>
+    <t>We will indicate CO2 emissions on the products, starting from the 30th anniversary model of a long-selling product from ASICS (GEL-KAYANO), which we will launch this year. We will also advance initiatives regarding the disposal of products, to enable customers to know the CO2 emissions throughout the product lifecycle and also to consider environmental issues together with them.</t>
+  </si>
+  <si>
+    <t>With regard to governance, we have abolished anti-takeover measures, reflecting the improvement of our corporate value through the formulation and execution of Mid-Term Plan 2023 and the recent trend of prevention policy.</t>
+  </si>
+  <si>
+    <t>Afterword</t>
+  </si>
+  <si>
+    <t>Let me repeat that we aim to ensure a world in which each and every one of us can engage in exercise and sports throughout our lives and continue to live in good health, both mentally and physically. We would like to expand our business by valuing the feeling of excitement that sports enable and maintain our relationships with our stakeholders that make the growth of ASICS a pleasure. To our shareholders, we have promised to increase shareholder returns to an exciting level, targeting a total return ratio of at least 50%. We cannot be what we intend to be like without moving hand-in-hand with our stakeholders. We will keep moving forward to achieve our vision. Please look forward to the future of ASICS.</t>
+  </si>
+  <si>
+    <t>message_management</t>
   </si>
 </sst>
 </file>
@@ -968,120 +1170,120 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L31" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L31" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:L31" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:L2" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:L37" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L37" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="CEO" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="CEO" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F4CFA2B5-C917-F844-B271-8DED374536B3}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F4CFA2B5-C917-F844-B271-8DED374536B3}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1C585532-6DA9-5942-A236-48F217D9793B}" name="ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{AFC9478D-55B1-C64F-B6B2-5E647B97E369}" name="Text" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{CA1B3214-0E1A-D849-864C-46A73414B549}" name="Text_type" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{2CBB1CC4-8BEF-914A-8AC6-9314C6CEB421}" name="Leadership_context" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{ED1A1168-CA54-924E-A023-2C2A99864277}" name="Information_valence" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{982EE0DB-A77B-AD4E-9EA1-1FBF76C538D9}" name="Communication_type" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{FBE2387C-B298-FC41-A34B-E687C4505262}" name="Company" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{50B3B34A-605B-CC46-BC27-653EAE9654AF}" name="Country" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{A96C931B-13DE-8648-AEAD-750D615CF9BE}" name="Year" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{2A86642C-7CAE-C14F-8135-2BA007A81A3B}" name="Covid" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{0B085943-2CC0-2146-909D-EB83EE4A4F6D}" name="CEO" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{C918E018-24BF-2F49-A610-D272E04AAEF5}" name="Comment" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{1C585532-6DA9-5942-A236-48F217D9793B}" name="ID" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{AFC9478D-55B1-C64F-B6B2-5E647B97E369}" name="Text" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{CA1B3214-0E1A-D849-864C-46A73414B549}" name="Text_type" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{2CBB1CC4-8BEF-914A-8AC6-9314C6CEB421}" name="Leadership_context" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{ED1A1168-CA54-924E-A023-2C2A99864277}" name="Information_valence" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{982EE0DB-A77B-AD4E-9EA1-1FBF76C538D9}" name="Communication_type" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{FBE2387C-B298-FC41-A34B-E687C4505262}" name="Company" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{50B3B34A-605B-CC46-BC27-653EAE9654AF}" name="Country" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{A96C931B-13DE-8648-AEAD-750D615CF9BE}" name="Year" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{2A86642C-7CAE-C14F-8135-2BA007A81A3B}" name="Covid" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{0B085943-2CC0-2146-909D-EB83EE4A4F6D}" name="CEO" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{C918E018-24BF-2F49-A610-D272E04AAEF5}" name="Comment" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="CEO" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="CEO" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{8DEBADB1-BE5F-F543-AE06-80C153895417}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{8B65CBCF-32BB-5C44-B286-3C8D05E43969}" name="Text" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{FA1AB22B-304F-E14F-9E52-8C69987599E3}" name="Text_type" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="CEO" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{8DEBADB1-BE5F-F543-AE06-80C153895417}" name="ID" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{8B65CBCF-32BB-5C44-B286-3C8D05E43969}" name="Text" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{FA1AB22B-304F-E14F-9E52-8C69987599E3}" name="Text_type" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="CEO" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1412,7 +1614,7 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="10" width="10.83203125" style="1"/>
     <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
@@ -1470,7 +1672,7 @@
         <v>81</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
@@ -1502,7 +1704,7 @@
         <v>81</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>14</v>
@@ -1537,7 +1739,7 @@
         <v>82</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>14</v>
@@ -1572,7 +1774,7 @@
         <v>81</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>14</v>
@@ -1607,7 +1809,7 @@
         <v>82</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>14</v>
@@ -1642,7 +1844,7 @@
         <v>82</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>14</v>
@@ -1677,7 +1879,7 @@
         <v>82</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>14</v>
@@ -1712,7 +1914,7 @@
         <v>81</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>14</v>
@@ -1747,7 +1949,7 @@
         <v>81</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>14</v>
@@ -1782,7 +1984,7 @@
         <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>14</v>
@@ -1814,7 +2016,7 @@
         <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>14</v>
@@ -1846,7 +2048,7 @@
         <v>83</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>14</v>
@@ -1878,7 +2080,7 @@
         <v>81</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>14</v>
@@ -1913,7 +2115,7 @@
         <v>82</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>14</v>
@@ -1948,7 +2150,7 @@
         <v>82</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>14</v>
@@ -1983,7 +2185,7 @@
         <v>81</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>14</v>
@@ -2018,7 +2220,7 @@
         <v>82</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>14</v>
@@ -2053,7 +2255,7 @@
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>14</v>
@@ -2088,7 +2290,7 @@
         <v>81</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>14</v>
@@ -2123,7 +2325,7 @@
         <v>96</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>14</v>
@@ -2158,7 +2360,7 @@
         <v>81</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>14</v>
@@ -2193,7 +2395,7 @@
         <v>81</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>14</v>
@@ -2228,7 +2430,7 @@
         <v>81</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>14</v>
@@ -2263,7 +2465,7 @@
         <v>81</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>14</v>
@@ -2298,7 +2500,7 @@
         <v>81</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>14</v>
@@ -2333,7 +2535,7 @@
         <v>96</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>14</v>
@@ -2368,7 +2570,7 @@
         <v>82</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>14</v>
@@ -2400,7 +2602,7 @@
         <v>81</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>14</v>
@@ -2435,7 +2637,7 @@
         <v>81</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>14</v>
@@ -2470,7 +2672,7 @@
         <v>81</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>14</v>
@@ -2502,7 +2704,7 @@
         <v>154</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>14</v>
@@ -2537,7 +2739,7 @@
         <v>96</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>14</v>
@@ -2572,7 +2774,7 @@
         <v>96</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>14</v>
@@ -2607,7 +2809,7 @@
         <v>81</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>14</v>
@@ -2642,7 +2844,7 @@
         <v>101</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>14</v>
@@ -2677,7 +2879,7 @@
         <v>102</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>14</v>
@@ -2709,7 +2911,7 @@
         <v>83</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>14</v>
@@ -2741,7 +2943,7 @@
         <v>83</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>14</v>
@@ -2770,7 +2972,7 @@
         <v>78</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>14</v>
@@ -2802,7 +3004,7 @@
         <v>83</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>14</v>
@@ -2837,7 +3039,7 @@
         <v>96</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>14</v>
@@ -2872,7 +3074,7 @@
         <v>102</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>14</v>
@@ -2904,7 +3106,7 @@
         <v>96</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>14</v>
@@ -2936,7 +3138,7 @@
         <v>81</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>14</v>
@@ -2965,7 +3167,7 @@
         <v>78</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>14</v>
@@ -2994,7 +3196,7 @@
         <v>78</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>14</v>
@@ -3029,7 +3231,7 @@
         <v>102</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>14</v>
@@ -3064,7 +3266,7 @@
         <v>81</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>14</v>
@@ -3099,7 +3301,7 @@
         <v>96</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>14</v>
@@ -3128,7 +3330,7 @@
         <v>78</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>14</v>
@@ -3157,7 +3359,7 @@
         <v>78</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>14</v>
@@ -3189,7 +3391,7 @@
         <v>92</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>14</v>
@@ -3221,7 +3423,7 @@
         <v>92</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>14</v>
@@ -3250,7 +3452,7 @@
         <v>78</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>14</v>
@@ -3279,7 +3481,7 @@
         <v>78</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>14</v>
@@ -3308,7 +3510,7 @@
         <v>78</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>14</v>
@@ -3337,7 +3539,7 @@
         <v>78</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>14</v>
@@ -3366,7 +3568,7 @@
         <v>78</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>14</v>
@@ -3395,7 +3597,7 @@
         <v>78</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>14</v>
@@ -3483,8 +3685,11 @@
       <c r="B2" s="2" t="s">
         <v>157</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="F2" s="1" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
@@ -3503,151 +3708,848 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>159</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>160</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>161</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="C7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>163</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="C9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>165</v>
       </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>166</v>
       </c>
+      <c r="C11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>167</v>
       </c>
+      <c r="C12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>197</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>169</v>
       </c>
+      <c r="C14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>170</v>
       </c>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>200</v>
+      </c>
       <c r="B16" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" ht="255" x14ac:dyDescent="0.2">
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="255" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="B17" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="B18" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="C19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="21" spans="2:2" ht="187" x14ac:dyDescent="0.2">
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="22" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="C22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="24" spans="2:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="C23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="25" spans="2:2" ht="136" x14ac:dyDescent="0.2">
+      <c r="C24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" ht="187" x14ac:dyDescent="0.2">
+      <c r="C25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="27" spans="2:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="C26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="B27" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="28" spans="2:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="C27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="B28" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="29" spans="2:2" ht="68" x14ac:dyDescent="0.2">
+      <c r="C28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="30" spans="2:2" ht="102" x14ac:dyDescent="0.2">
+      <c r="C29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="31" spans="2:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="C30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="B31" s="2" t="s">
         <v>186</v>
       </c>
+      <c r="C31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3657,16 +4559,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F818BF7-D6BE-A545-9E45-A87A4152B2E0}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
+    <col min="7" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
   </cols>
@@ -3709,11 +4614,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
@@ -3727,6 +4640,916 @@
         <v>11</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="B8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B17" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="B25" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="255" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="B31" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B32" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>17</v>
       </c>
     </row>

--- a/data/input/asics.xlsx
+++ b/data/input/asics.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA462953-C6BA-D04B-B48E-EEF02C276102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C2AE49-E58E-ED46-9233-904B01BECFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="2" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
     <sheet name="2021" sheetId="4" r:id="rId2"/>
     <sheet name="2022" sheetId="5" r:id="rId3"/>
-    <sheet name="2023" sheetId="6" r:id="rId4"/>
+    <sheet name="2023" sheetId="10" r:id="rId4"/>
     <sheet name="2024" sheetId="8" r:id="rId5"/>
     <sheet name="2025" sheetId="9" r:id="rId6"/>
   </sheets>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="369">
   <si>
     <t>ID</t>
   </si>
@@ -826,6 +826,365 @@
   </si>
   <si>
     <t>message_management</t>
+  </si>
+  <si>
+    <t>Transformation to a Global Integrated Enterprise by Continuing to Drive the Implementation of Our Global × Digital Approach</t>
+  </si>
+  <si>
+    <t>Message from the new President and COO</t>
+  </si>
+  <si>
+    <t>My name is Mitsuyuki Tominaga, and I was appointed President in January this year. First, I</t>
+  </si>
+  <si>
+    <t>would like to briefly introduce myself to our valued stakeholders.</t>
+  </si>
+  <si>
+    <t>My name is Mitsuyuki Tominaga, and I was appointed President in January this year. First, I would like to briefly introduce myself to our valued stakeholders.</t>
+  </si>
+  <si>
+    <t>I am a fan of all kinds of sports, but I was particularly fond of tennis and even studied overseas in my university days in the hopes of turning pro. Even today, I continue to enjoy the game with a strong passion. I spent my childhood and university years overseas, and up until joining ASICS in 2018 I had worked at various global companies with a focus on digital technology and IT. Since joining ASICS, I have filled a dual CDO and CIO role as head of the digital business, promoting ASICS’ Group-wide digital transformation including the running ecosystem.</t>
+  </si>
+  <si>
+    <t>In November last year, ASICS unveiled Mid-Term Plan 2026 (MTP 2026), and the further promotion of the “Global × Digital” approach laid out in MTP 2026 falls precisely in line with my career to date. As President and COO, I will make every effort to fully capitalize on the experience I have cultivated to date and raise ASICS to yet another stage.</t>
+  </si>
+  <si>
+    <t>message_president</t>
+  </si>
+  <si>
+    <t>weg</t>
+  </si>
+  <si>
+    <t>Looking to Further Global Growth</t>
+  </si>
+  <si>
+    <t>ASICS has grown into a global company, with overseas sales accounting for more than 80% of total sales. The regional spread is also well balanced across North America, Europe, Greater China, Japan and developing countries. In this global competitive environment, ASICS has managed to play to its strengths in terms of the quality and functionality of its products. However, to achieve further global growth, I believe there is room for us to improve further on the three aspects of products, regions and services.</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>On the product front, even looking at the single category of shoes, we maintain an extensive lineup ranging from our core performance running shoes to fashion oriented products from Onitsuka Tiger and other divisions. I hope that we will continue to strengthen our existing structure of continually creating a healthy balance of innovative products that embody Sound Mind, Sound Body, rather than relying on a few products that sell well. Today, running shoes have become a key pillar, accounting for almost 50% of our overall sales, but going forward we will
+focus on developing other categories into new pillars that stand next to running. For example, my favorite sport of tennis is one such candidate. ASICS currently has sponsorship agreements with around 40 top tennis players. Each year, the four Grand Slam and other major tournaments take place around the world, and there is room to capitalize on our relationships with these top athletes and collaboration with tournaments more effectively. Having the Head Quarter coordinate with regional operating companies in more organic ways will strengthen our products.</t>
+  </si>
+  <si>
+    <t>Regions</t>
+  </si>
+  <si>
+    <t>Maintaining a good balance across regions is also important in terms of mitigating geopolitical risks. We will focus on establishing footprints in high-growth regions while continuing to reinforce our presence in key markets including North America, Japan, Europe and Greater China.</t>
+  </si>
+  <si>
+    <t>Among these key markets, North America is considered the primary market in terms of competition, which has become extremely intense as new players join the fray. Past challenges have taught us that there is a significant ripple effect on branding when top runners choose ASICS shoes. Given this, we have set the ambitious target of securing a 25% market share at running specialty stores, which play a key role. From there, we aim to create a trickle-down effect that will reach non-professional marathon runners. In addition, utilizing the data accumulated through race registrations and other means, we will strive to further enhance the brand by reaching out directly to runners who wear competing shoe brands.</t>
+  </si>
+  <si>
+    <t>Meanwhile, in markets such as India and Southeast Asia that are expected to enjoy high growth, we will promote ASICS’ philosophy along with brand recognition by dedicating human and financial resources through the dispatch of young talent personnel, investments in stores and other efforts. India, in particular, is highly attractive not only for its potential as a market but also because it is home to many tech-savvy workers with world-class skills. ASICS is the main sponsor of the Mumbai Marathon, and I have personally traveled there to strengthen our ties with the local race registration company. Outside India, there are many other regions with strong prospects for market growth such as Indonesia, and we are making
+progress in market development while considering the adoption of prior examples from other regions. For example, in Australia, where we have established ourselves as a brand with a leading market share, ASICS shoes are highly regarded from a medical standpoint, and one idea is to take our approach in Australia of spreading recognition of the ASICS brand in conjunction with our Sound Mind, Sound Body philosophy and expanding it to other regions. Rather than being directed from the Head Quarter, our aim is for each regional operating company, which is familiar with its own market characteristics, to pursue measures autonomously, drive regional growth and, as a result, contribute to the global growth of ASICS.</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>In promoting the ideals of Sound Mind, Sound Body, Services is the area in which ASICS’ values can be expanded to the broadest extent. ASICS customers use our products on a daily basis as they engage in a variety of training toward their respective goals, culminating in a race or other event. In addition to products, we provide services that aid customers in their day-to-day training, allow them to register for races, and incorporate medical and supplement support. The ability to achieve this is a key strength of ASICS and is the very embodiment of “Sound Mind, Sound Body.” Improving services is not something that can be fully achieved over a three-year period. It is important to operate these services as a robust core business over the long term and at a global scale that includes developing countries. The core of this lies in the utilization of digital technology, and we want to be a company that continues to support customers by strengthening these digital services.</t>
+  </si>
+  <si>
+    <t>Transformation to a Global Integrated Enterprise</t>
+  </si>
+  <si>
+    <t>The question is what kind of organization should we be to achieve the global growth I just mentioned? The answer lies in the major policy laid out in MTP 2026: our Transformation to a Global Integrated Enterprise, or GIE. Under this policy, we will work to enhance coordination between the Head Quarter and regional operating companies and build an organic category-based management system.</t>
+  </si>
+  <si>
+    <t>Management System</t>
+  </si>
+  <si>
+    <t>To transform to a Global Integrated Enterprise, we have made significant changes to our management decision-making mechanisms. The CEOs of our regional operating companies have been placed directly under the President, and starting this year our management meetings will be held as global management meetings with members from key overseas regional operating companies also taking part. To reinvigorate communication between regional operating companies and facilitate overall optimization, these meetings will be held in English. In addition, twice a year we will hold a Global Summit at our Kobe head office to gather the CEOs of all the regional operating companies in one place. These will be a chance to thoroughly discuss a range of topics including branding, the supply chain and our global
+talent strategy.</t>
+  </si>
+  <si>
+    <t>The members responsible for this management structure have also undergone a shakeup, and close to 60% of the management team have assumed new leadership roles. The management team, which now has more women and overseas members, is not only younger and more diverse but also better equipped than ever to drive our digital, services and global priorities. Under this management system, we will make dynamic use of IT platforms, data and talent worldwide as a GIE.</t>
+  </si>
+  <si>
+    <t>Human Resources Strategy</t>
+  </si>
+  <si>
+    <t>For the human resources supporting ASICS as a GIE, we aim to create a structure where people with various specialties in different countries have avenues for success that are not limited to their own regions. Instead, we will establish regions where experts in each field gather as global heads from which they will oversee global efforts.</t>
+  </si>
+  <si>
+    <t>For example, until now we have assembled a team of 70 personnel in Europe who are well versed in business operations, systems and project management to link our IT systems globally. By rolling out systems from this base, we have managed to build IT systems that are standardized across the Group. In the areas of e-commerce and software, our Boston, USA–based ASICS Digital oversees the global implementation of digital technologies, while race registration is handled by our team in Canada. In terms of products, at the ASICS Creation Center that was established in Boston this year, personnel familiar with trends in the European and U.S. markets will collaborate organically with our Institute of Sports Science in Japan and other categories. Our style is to look at and oversee a particular field globally from the most appropriate region instead of always looking at the global picture from Japan. This style applies not only to digital technologies but also to category, human resources, legal affairs, supply chain management and so on. I believe our transformation to a Global Integrated Enterprise is quite a challenging endeavor. However, I regard it as an essential transformation as ASICS’ next step to becoming a leading global company in the truest sense. On top of the strengths that ASICS has always enjoyed, such as the quality and functionality of its products, the teamwork of its employees and brand loyalty, if we can gain the ability to improve productivity by incorporating new innovations emerging around the world, a bright future for ASICS is assured. As someone who is Japanese but has built a career in a multinational environment, I think I can contribute in significant ways to this transformation and it is something that I will push for with zeal</t>
+  </si>
+  <si>
+    <t>Digital Technology and the OneASICS Strategy</t>
+  </si>
+  <si>
+    <t>ASICS has evolved as a digitally driven company at a global scale, and even on the
+operational front, we pursue operational excellence in an effort to boost productivity through the full use of AI in supply chain management, including R&amp;D and inventory control. With respect to customers, over the past three years we have increased the number of direct points of contact, and direct-to-consumer (DTC) sales have risen as a percentage of total sales. Underpinning these efforts is our OneASICS loyalty program. The number of OneASICS members still stands at only 15 million and involves elements designed to attract customers such as the granting of points and free shipping, but in the future, we will further improve
+and expand the service offerings by utilizing the data we have accumulated to date,
+including purchase histories, training results and race entry history. For example, in addition to utilizing OneASICS for daily training or to sign up for sports events with friends, we will expand tools designed for exercise or to boost motivation targeting middle-aged and senior customers who want to build up their training due to concerns about declining physical fitness. I think this precisely represents the promotion of ASICS’ Sound Mind, Sound Body philosophy. We aim to increase the number of OneASICS members to 30 million and raise the DTC sales ratio to 40% while expanding the number of facility users and holders of OneASICS bonds. ASICS builds databases of people who enjoy a wide range of sports in addition to running, and by coordinating with partners familiar with other areas such as the
+tracking of medical and training data, we can link that data to improvements in marketing, products and services. By doing so, our aim is to change the current impression that many people have of ASICS as a shoes company to a “company that promotes Sound Mind and Sound Body.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Pursuit of Sound Mind, Sound Body </t>
+  </si>
+  <si>
+    <t>Allocation of Management Resources</t>
+  </si>
+  <si>
+    <t>When considering our future business portfolio and the allocation of management resources, whether something contributes to our becoming a company that promotes Sound Mind, Sound Body will serve as our decision-making criteria. In various operations including products, services and marketing, we will promote a selection and concentration approach to items that fall outside these decision-making criteria or which do not necessarily need to be handled by ASICS.</t>
+  </si>
+  <si>
+    <t>Intangible Assets</t>
+  </si>
+  <si>
+    <t>As part of our efforts to promote ASICS’ philosophy, we emphasize human-centric science as a basis for product development. As a result of steadfastly investing in research and development for more than four decades, ASICS has passed down proprietary technologies, innovations and approaches, not only in the area of shoes but also apparel. The knowledge accumulated by the Institute of Sports Science is a source of value enabling ASICS to demonstrate strengths that its competitors lack, and the ASICS Design Philosophy we have built to date is an intangible asset that will be preserved into the future. At the same time, we will promote collaborations with other industrial organizations, universities and other entities at an even greater rate, and invest in development that utilizes IT and digital technologies.</t>
+  </si>
+  <si>
+    <t>Human Capital</t>
+  </si>
+  <si>
+    <t>The core human capital in a GIE can work globally, have the ability to utilize digital tools and, of course, identify with the Sound Mind, Sound Body philosophy as a key foundation. Investment in human capital is essential for corporate growth in the medium to long term, and we aim to offer industry-leading compensation in an effort to continually secure talented personnel. We have already significantly increased starting salaries offered to new graduate hires from FY2024 onward. We also paid a one-off lump-sum payment to all global employees to reflect our strong business performance. We aim to strengthen investments in human capital with the introduction of profit-sharing bonuses, the launching of a transfer restricted stock-based incentive scheme through shareholding associations and other measures. At the same time, we will focus on human resource development through initiatives such as job rotations and overseas assignments. In every area from manufacturingto sales, sports events and production, we have now managed to build a corporate structure enabling the use of cutting-edge technologies and developed a personnel evaluation system that is standardized globally. With these systems in place, we will turn into a high-performance company that provides significant results by offering good compensation to human resources who are willing to take on challenges.</t>
+  </si>
+  <si>
+    <t>I feel a strong sense of crisis over climate change and global warming as major risks not only to ASICS but also the entire sports industry. We are strongly committed to tackling these issues, and specific initiatives we have undertaken include developing shoes that generate the world’s fewest CO2 emissions. We will continue to pursue initiatives that emphasize sustainability from environmental perspectives such as recycled models and efforts to address human rights. We will also make appeals to customers and society writ large regarding these topics.</t>
+  </si>
+  <si>
+    <t>Governance</t>
+  </si>
+  <si>
+    <t>The ASICS Board Meeting includes professionals in the areas of management, legal affairs, finance and accounting, in addition to members with extensive experience in the sports industry. The Board engages in lively exchanges of views and discussions on a range of topics including key strategies and medium- to long-term policies each month. The Board also actively discusses matters on specific themes including sustainability, product innovation and diversity. Opinions and observations provided by outside directors at Board Meetings are brought up for further discussion and consideration at Management Meetings, and then reported back to the Board Meeting the following month.</t>
+  </si>
+  <si>
+    <t>To Our Stakeholders</t>
+  </si>
+  <si>
+    <t>We have begun to see the results of building and implementing the category-based
+management system we began in 2019, and today ASICS is demonstrating a strong
+competitive advantage globally based on its dominant products. In MTP 2026, which began in 2024, we will pool our strengths to promote the Global × Digital approach under a new management structure, and strive to meet our targets.</t>
+  </si>
+  <si>
+    <t>In terms of shareholder return, we will aim to achieve a consolidated total payout ratio of 50% over the three years of MTP 2026. We will also take a flexible approach in considering additional shareholder return based on the premise of maintaining progressive dividends while taking into account profit distribution, cash reserves and the investment situation.</t>
+  </si>
+  <si>
+    <t>Through digital transformation, starting internally we have made progress in the visualization of data including human resources, business opportunities, growth potential and profitability by category or region. We will further enhance decision-
+making transparency by using visualized data to determine what decisions are made, where management resources are invested and to what degree. By improving transparency internally, we will also fulfill our accountability to shareholders
+and investors, enhancing our ability to properly explain with even greater transparency about why we invest in certain areas, or why we pursue certain initiatives. We are committed to making investments that advance visualization and our Sound Mind, Sound Body philosophy while ensuring ongoing shareholder returns, and we appreciate your continuedsupport.</t>
+  </si>
+  <si>
+    <t>JPN22A01-00</t>
+  </si>
+  <si>
+    <t>JPN22A01-01</t>
+  </si>
+  <si>
+    <t>JPN22A02-00</t>
+  </si>
+  <si>
+    <t>JPN22A02-01</t>
+  </si>
+  <si>
+    <t>JPN22A02-02</t>
+  </si>
+  <si>
+    <t>JPN22A03-00</t>
+  </si>
+  <si>
+    <t>JPN22A03-01</t>
+  </si>
+  <si>
+    <t>JPN22A03-02</t>
+  </si>
+  <si>
+    <t>JPN22A04-00</t>
+  </si>
+  <si>
+    <t>JPN22A04-01</t>
+  </si>
+  <si>
+    <t>JPN22A04-02</t>
+  </si>
+  <si>
+    <t>JPN22A05-00</t>
+  </si>
+  <si>
+    <t>JPN22A05-01</t>
+  </si>
+  <si>
+    <t>JPN22A05-02</t>
+  </si>
+  <si>
+    <t>JPN22A05-03</t>
+  </si>
+  <si>
+    <t>JPN22A05-04</t>
+  </si>
+  <si>
+    <t>JPN22A05-05</t>
+  </si>
+  <si>
+    <t>JPN22A05-06</t>
+  </si>
+  <si>
+    <t>JPN22A05-07</t>
+  </si>
+  <si>
+    <t>JPN22A06-00</t>
+  </si>
+  <si>
+    <t>JPN22A06-01</t>
+  </si>
+  <si>
+    <t>JPN22A06-02</t>
+  </si>
+  <si>
+    <t>JPN22A07-00</t>
+  </si>
+  <si>
+    <t>JPN22A07-01</t>
+  </si>
+  <si>
+    <t>JPN22A08-00</t>
+  </si>
+  <si>
+    <t>JPN22A08-01</t>
+  </si>
+  <si>
+    <t>JPN22A09-00</t>
+  </si>
+  <si>
+    <t>JPN22A09-01</t>
+  </si>
+  <si>
+    <t>JPN22A10-00</t>
+  </si>
+  <si>
+    <t>JPN22A10-01</t>
+  </si>
+  <si>
+    <t>JPN22A10-02</t>
+  </si>
+  <si>
+    <t>JPN22A10-03</t>
+  </si>
+  <si>
+    <t>JPN22A11-00</t>
+  </si>
+  <si>
+    <t>JPN22A11-01</t>
+  </si>
+  <si>
+    <t>JPN23A01-00</t>
+  </si>
+  <si>
+    <t>JPN23A01-01</t>
+  </si>
+  <si>
+    <t>JPN23A01-02</t>
+  </si>
+  <si>
+    <t>JPN23A01-03</t>
+  </si>
+  <si>
+    <t>JPN23A02-00</t>
+  </si>
+  <si>
+    <t>JPN23A02-01</t>
+  </si>
+  <si>
+    <t>JPN23A02-02</t>
+  </si>
+  <si>
+    <t>JPN23A02-03</t>
+  </si>
+  <si>
+    <t>JPN23A02-04</t>
+  </si>
+  <si>
+    <t>JPN23A02-05</t>
+  </si>
+  <si>
+    <t>JPN23A02-06</t>
+  </si>
+  <si>
+    <t>JPN23A02-07</t>
+  </si>
+  <si>
+    <t>JPN23A02-08</t>
+  </si>
+  <si>
+    <t>JPN23A02-09</t>
+  </si>
+  <si>
+    <t>JPN23A03-00</t>
+  </si>
+  <si>
+    <t>JPN23A03-01</t>
+  </si>
+  <si>
+    <t>JPN23A03-02</t>
+  </si>
+  <si>
+    <t>JPN23A03-03</t>
+  </si>
+  <si>
+    <t>JPN23A03-04</t>
+  </si>
+  <si>
+    <t>JPN23A03-05</t>
+  </si>
+  <si>
+    <t>JPN23A03-06</t>
+  </si>
+  <si>
+    <t>JPN23A03-07</t>
+  </si>
+  <si>
+    <t>JPN23A03-08</t>
+  </si>
+  <si>
+    <t>JPN23A03-09</t>
+  </si>
+  <si>
+    <t>JPN23A04-00</t>
+  </si>
+  <si>
+    <t>JPN23A04-01</t>
+  </si>
+  <si>
+    <t>JPN23A04-02</t>
+  </si>
+  <si>
+    <t>JPN23A04-03</t>
+  </si>
+  <si>
+    <t>JPN23A04-04</t>
+  </si>
+  <si>
+    <t>JPN23A04-05</t>
+  </si>
+  <si>
+    <t>JPN23A04-06</t>
+  </si>
+  <si>
+    <t>JPN23A04-07</t>
+  </si>
+  <si>
+    <t>JPN23A04-08</t>
+  </si>
+  <si>
+    <t>JPN23A04-09</t>
+  </si>
+  <si>
+    <t>JPN23A04-10</t>
+  </si>
+  <si>
+    <t>JPN23A05-00</t>
+  </si>
+  <si>
+    <t>JPN23A05-01</t>
+  </si>
+  <si>
+    <t>JPN23A05-02</t>
+  </si>
+  <si>
+    <t>JPN23A05-03</t>
   </si>
 </sst>
 </file>
@@ -890,27 +1249,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -923,36 +1261,30 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -965,6 +1297,24 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -977,24 +1327,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1007,6 +1339,24 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1019,24 +1369,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1049,6 +1381,24 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1061,25 +1411,34 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1170,120 +1529,120 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L31" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L31" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="A1:L31" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="30"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:L37" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:L37" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
   <autoFilter ref="A1:L37" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="CEO" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="CEO" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F4CFA2B5-C917-F844-B271-8DED374536B3}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{91060F3E-0B02-0F49-9464-096A57BA32E7}" name="Tableau1348" displayName="Tableau1348" ref="A1:L41" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1C585532-6DA9-5942-A236-48F217D9793B}" name="ID" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{AFC9478D-55B1-C64F-B6B2-5E647B97E369}" name="Text" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{CA1B3214-0E1A-D849-864C-46A73414B549}" name="Text_type" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{2CBB1CC4-8BEF-914A-8AC6-9314C6CEB421}" name="Leadership_context" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{ED1A1168-CA54-924E-A023-2C2A99864277}" name="Information_valence" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{982EE0DB-A77B-AD4E-9EA1-1FBF76C538D9}" name="Communication_type" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{FBE2387C-B298-FC41-A34B-E687C4505262}" name="Company" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{50B3B34A-605B-CC46-BC27-653EAE9654AF}" name="Country" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{A96C931B-13DE-8648-AEAD-750D615CF9BE}" name="Year" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{2A86642C-7CAE-C14F-8135-2BA007A81A3B}" name="Covid" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{0B085943-2CC0-2146-909D-EB83EE4A4F6D}" name="CEO" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{C918E018-24BF-2F49-A610-D272E04AAEF5}" name="Comment" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{0FC74C30-0962-A14E-847E-3BD5B25B5351}" name="ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{C7C901AE-1A30-FB47-85DC-35A6B31CEC7B}" name="Text" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{F4ED2FC7-93B1-3F4A-9B4F-290279B887B2}" name="Text_type" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{9D90BC68-BA7E-F34D-B3F6-C0973AE7FBAC}" name="Leadership_context" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{BECC38E4-659E-B54D-8D6D-F79323C4FD32}" name="Information_valence" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{0D683163-5F34-8844-B60C-D21DB7EBE838}" name="Communication_type" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{8DDEB90A-3B40-014A-96D8-A24880305585}" name="Company" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{BB63E2C9-1A80-424B-8DB7-B1D47C0A0119}" name="Country" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{4D5F9A30-522F-7D4D-B61F-C3C4E52F9F7C}" name="Year" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{6EB4002B-3104-4E41-BE56-50D81B53C531}" name="Covid" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{77191CD6-3DB8-BB4F-801D-AEE91A59435B}" name="CEO" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{07FAF978-D7C1-4B43-BDE0-228C777612CA}" name="Comment" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:L3" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+  <autoFilter ref="A1:L3" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="CEO" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="CEO" dataDxfId="58"/>
+    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{8DEBADB1-BE5F-F543-AE06-80C153895417}" name="ID" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{8B65CBCF-32BB-5C44-B286-3C8D05E43969}" name="Text" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{FA1AB22B-304F-E14F-9E52-8C69987599E3}" name="Text_type" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="CEO" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{8DEBADB1-BE5F-F543-AE06-80C153895417}" name="ID" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{8B65CBCF-32BB-5C44-B286-3C8D05E43969}" name="Text" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{FA1AB22B-304F-E14F-9E52-8C69987599E3}" name="Text_type" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="CEO" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4644,6 +5003,9 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>217</v>
       </c>
@@ -4670,6 +5032,9 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>218</v>
       </c>
@@ -4696,6 +5061,9 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>219</v>
       </c>
@@ -4722,6 +5090,9 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>220</v>
       </c>
@@ -4748,6 +5119,9 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>300</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>221</v>
       </c>
@@ -4800,6 +5174,9 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>301</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>223</v>
       </c>
@@ -4826,6 +5203,9 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>224</v>
       </c>
@@ -4852,6 +5232,9 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>303</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>225</v>
       </c>
@@ -4878,6 +5261,9 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>304</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>226</v>
       </c>
@@ -4904,6 +5290,9 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>305</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>227</v>
       </c>
@@ -4930,6 +5319,9 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>306</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>228</v>
       </c>
@@ -4956,6 +5348,9 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>307</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>229</v>
       </c>
@@ -4982,6 +5377,9 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>308</v>
+      </c>
       <c r="B16" s="2" t="s">
         <v>230</v>
       </c>
@@ -5007,7 +5405,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>309</v>
+      </c>
       <c r="B17" s="2" t="s">
         <v>231</v>
       </c>
@@ -5033,7 +5434,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="204" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>310</v>
+      </c>
       <c r="B18" s="2" t="s">
         <v>232</v>
       </c>
@@ -5059,7 +5463,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>311</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>233</v>
       </c>
@@ -5085,7 +5492,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>312</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>234</v>
       </c>
@@ -5111,7 +5521,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>235</v>
       </c>
@@ -5137,7 +5550,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="187" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>236</v>
       </c>
@@ -5163,7 +5579,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>237</v>
       </c>
@@ -5189,7 +5608,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>316</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>238</v>
       </c>
@@ -5215,7 +5637,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="187" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>317</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>239</v>
       </c>
@@ -5241,7 +5666,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>240</v>
       </c>
@@ -5267,7 +5695,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="255" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="255" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>319</v>
+      </c>
       <c r="B27" s="2" t="s">
         <v>241</v>
       </c>
@@ -5293,7 +5724,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>320</v>
+      </c>
       <c r="B28" s="2" t="s">
         <v>242</v>
       </c>
@@ -5319,7 +5753,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>321</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>243</v>
       </c>
@@ -5345,7 +5782,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>244</v>
       </c>
@@ -5371,7 +5811,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>323</v>
+      </c>
       <c r="B31" s="2" t="s">
         <v>245</v>
       </c>
@@ -5397,7 +5840,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>324</v>
+      </c>
       <c r="B32" s="2" t="s">
         <v>246</v>
       </c>
@@ -5423,7 +5869,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="221" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>247</v>
       </c>
@@ -5449,7 +5898,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>326</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>248</v>
       </c>
@@ -5475,7 +5927,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>327</v>
+      </c>
       <c r="B35" s="2" t="s">
         <v>249</v>
       </c>
@@ -5501,7 +5956,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>328</v>
+      </c>
       <c r="B36" s="2" t="s">
         <v>250</v>
       </c>
@@ -5527,7 +5985,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="B37" s="2" t="s">
         <v>251</v>
       </c>
@@ -5554,6 +6015,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -5562,8 +6024,550 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62BCC9C2-4BFC-A14A-8E1A-60388FAE4E88}">
-  <dimension ref="A1:L2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{745FBC29-1348-FC4A-97A0-E4A368B4DC13}">
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="248" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="340" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="404" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="187" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="323" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="221" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0DD7501-CB0C-FE45-BCB2-B7DDD63724CD}">
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -5615,94 +6619,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0DD7501-CB0C-FE45-BCB2-B7DDD63724CD}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
@@ -5717,6 +6640,16 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/asics.xlsx
+++ b/data/input/asics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C2AE49-E58E-ED46-9233-904B01BECFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA10469-6A7D-104A-8F24-F70728FB2454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="407">
   <si>
     <t>ID</t>
   </si>
@@ -834,12 +834,6 @@
     <t>Message from the new President and COO</t>
   </si>
   <si>
-    <t>My name is Mitsuyuki Tominaga, and I was appointed President in January this year. First, I</t>
-  </si>
-  <si>
-    <t>would like to briefly introduce myself to our valued stakeholders.</t>
-  </si>
-  <si>
     <t>My name is Mitsuyuki Tominaga, and I was appointed President in January this year. First, I would like to briefly introduce myself to our valued stakeholders.</t>
   </si>
   <si>
@@ -850,9 +844,6 @@
   </si>
   <si>
     <t>message_president</t>
-  </si>
-  <si>
-    <t>weg</t>
   </si>
   <si>
     <t>Looking to Further Global Growth</t>
@@ -1185,6 +1176,193 @@
   </si>
   <si>
     <t>JPN23A05-03</t>
+  </si>
+  <si>
+    <t>Run Past Your Potential</t>
+  </si>
+  <si>
+    <t>“Run past your potential,” is the ASICS slogan for 2025. At ASICS, we believe in the potential of all those who are willing to challenge themselves and we encourage them to press on. Likewise, we strive to be an unrelenting force that never stops moving forward. In this edition of our integrated report, our fifth since the inaugural Integrated Report 2020 , we want to convey ASICS’ potential for further growth in the years to come.</t>
+  </si>
+  <si>
+    <t>Assessment of 2024, the First Year of Mid-Term Plan 2026</t>
+  </si>
+  <si>
+    <t>2024 marked the first year of Mid-Term Plan 2026, and we hit the ground running. Since we have
+already hit all the original 2026 targets announced in November 2023, we updated the plan with new
+numerical targets in November 2024. For me, the standout achievement of 2024 is reaching the
+¥100.0 billion milestone in operating profit for the first time, as it confirms what I have been saying all
+along: that ASICS has reached an entirely new level.</t>
+  </si>
+  <si>
+    <t>Following the same path as our Performance Running category, ASICS’ net sales base, the SportStyle
+and Onitsuka Tiger categories are on track to increase net sales to the ¥100.0 billion mark as well. I
+believe that these businesses can serve as the second and third pillars for ASICS going forward.</t>
+  </si>
+  <si>
+    <t>2024 marked the first year of operations with our new management structure under the leadership
+of current president and COO Mr. Tominaga. I feel that it was also a year of major change from global
+and digital perspectives.</t>
+  </si>
+  <si>
+    <t>On the global front, we expanded communication more than ever by having the CEOs of each
+regional operating company report directly to Mr. Tominaga at our global headquarters. In addition,
+Executive Board Meetings, which were previously limited to Japanese members of the executive
+body, are now attended by non-Japanese members when topics with a global impact are on the
+agenda. Discussions on these topics are held in English. Increasingly, department head roles are
+being taken on by members outside Japan. This all adds up to an organizational structure that is
+becoming ever more global.</t>
+  </si>
+  <si>
+    <t>On the digital front, we are making progress with the introduction of globally-unified, mission-
+critical systems, an effort Mr. Tominaga has been involved with since joining ASICS in his previous role
+as the senior general manager of the IT Division. As a result, we are gaining a granular, real-time
+understanding of the state of business in each region, down to each store and product. We have
+already begun using these systems for demand forecasting and production planning. I believe they
+will help greatly with making forecasts more accurate and with optimizing inventory, which will
+ultimately improve our profit margins.</t>
+  </si>
+  <si>
+    <t>JPN24A00-01</t>
+  </si>
+  <si>
+    <t>JPN24A01-00</t>
+  </si>
+  <si>
+    <t>JPN24A02-00</t>
+  </si>
+  <si>
+    <t>The Founding Philosophy and Establishment of the ASICS Foundation</t>
+  </si>
+  <si>
+    <t>2024 also marked ASICS' 75th anniversary. Since the beginning, our philosophy has been, “Anima
+Sana In Corpore Sano,” which translates to “a sound mind in a sound body.”</t>
+  </si>
+  <si>
+    <t>ASICS was founded after World War II with only two employees and ¥300,000 in capital. While
+living in Kobe City, Japan after serving in the war, the Company’s founder, Kihachiro Onitsuka, wit-
+nessed the tragic reality of the youth with his own eyes. Listless, lost, and with nowhere to go, they
+turned to delinquency to fill the void. As he thought of ways to help solve this problem, he concluded
+that sports could give young people hope, and so the Company was born. Mr. Onitsuka’s original wish
+lives on as ASICS’ founding philosophy to this very day. In that same spirit, we conduct business with
+the goal of creating a world where any one of us can continue to exercise, play sports, and remain in
+good mental and physical health throughout our lives.</t>
+  </si>
+  <si>
+    <t>In July 2024, we announced that we were looking into establishing the ASICS Foundation,
+a general incorporated foundation. The foundation will provide grants to organizations that use sports
+and exercise initiatives to support young people, people with disabilities, women, and any others who
+face social or economic hardships. In addition to Japan, the foundation will primarily target its efforts
+in regions where ASICS operates production sites, such as Vietnam, Indonesia, India, and Cambodia.</t>
+  </si>
+  <si>
+    <t>As part of our never-ending commitment to improving corporate value, we have decided to work
+through the ASICS Foundation to address social issues related to sports and exercise. I believe this
+will enable us to bring better mental and physical health to more people than ever before.</t>
+  </si>
+  <si>
+    <t>As part of the consideration process, we engaged in earnest engagement with shareholders and
+maintained close communication to ensure that they had a clear understanding of the significance of
+establishing the foundation as well as its objectives. I believe that we were able to have in-depth discussions
+on the matter, particularly regarding the method of establishment, ultimately bringing shareholders who
+were initially lukewarm around to the idea. In the end, several shareholders showed their support for the
+plan at the General Meeting of Shareholders held in March 2025, and establishment of the foundation
+was given the go-ahead. My hope is to make this foundation a new means to create value for ASICS,
+working hand in hand with our stakeholders. We are investigating ways to provide readers and
+stakeholders with regular updates on ASICS Foundation activities as we move forward.</t>
+  </si>
+  <si>
+    <t>Facing of the Global Capital Market</t>
+  </si>
+  <si>
+    <t>JPN24A03-00</t>
+  </si>
+  <si>
+    <t>This past year also served as a strong reminder that ASICS is a part of the global market. I had many
+investor relations (IR) meetings overseas, and the interactions I had with investors brought one par-
+ticular issue to my attention. The question that came up time and time again was “Why does ASICS
+continue to hold cross-shareholdings?” Since ASICS is a global brand, I believe that our capital and
+financial standing should meet global standards, and so we have decided to eliminate all cross-
+shareholdings held by the ASICS Group.</t>
+  </si>
+  <si>
+    <t>At the same time, we approached financial institutions and other shareholders who held ASICS
+shares as cross-shareholdings about the prospect of selling, and in July we conducted a secondary
+offering of shares worth ¥200 billion. Our shareholder structure needs reform. Since there will no
+longer be so-called stable shareholders, we will need to face capital markets head-on. I made the
+choice to be prepared as a manager in charge of a company that faces constant pressure from
+capital markets. Going forward, ASICS will need to manage its business with even greater transpar-
+ency and urgency, which may open us up to a new level of expectations and criticism from sharehold-
+ers. However, I believe we can use both these expectations and critical voices, and ultimately the
+dynamism of the global market as a force to drive us forward and an impetus for future growth.</t>
+  </si>
+  <si>
+    <t>Another result of our secondary offering of shares was a significant jump in the number of indi-
+vidual shareholders. I would like to engage in active communication with even more individuals, turn
+them into ASICS fans, and eventually have them become individual investors who purchase shares. In
+March 2025, we held our first IR meeting for individual investors in Okinawa City. We also held these
+meetings in Fukuoka City in May and in Hokkaido City in June. I joined the meetings in Okinawa City and Hokkaido City and spoke directly with individual investors. Our management team plans to keep
+visiting major cities and prefectures across Japan in the future and bring with us an interactive IR
+experience. I welcome you to join one of these events.</t>
+  </si>
+  <si>
+    <t>In Closing</t>
+  </si>
+  <si>
+    <t>At ASICS, we believe our mission is to contribute to people’s physical and mental health. This philoso-
+phy remains the unchanging foundation of all ASICS' business activities. The environment surround-
+ing ASICS may be undergoing major changes—shifts in the global situation, geopolitical risks, and
+otherwise—but amid all of it ASICS will keep on running!</t>
+  </si>
+  <si>
+    <t>As the 2025 slogan says, “Run past your potential.” We will do the same.</t>
+  </si>
+  <si>
+    <t>JPN24A04-00</t>
+  </si>
+  <si>
+    <t>JPN24A01-01</t>
+  </si>
+  <si>
+    <t>JPN24A01-02</t>
+  </si>
+  <si>
+    <t>JPN24A01-03</t>
+  </si>
+  <si>
+    <t>JPN24A01-04</t>
+  </si>
+  <si>
+    <t>JPN24A01-05</t>
+  </si>
+  <si>
+    <t>JPN24A02-01</t>
+  </si>
+  <si>
+    <t>JPN24A02-02</t>
+  </si>
+  <si>
+    <t>JPN24A02-03</t>
+  </si>
+  <si>
+    <t>JPN24A02-04</t>
+  </si>
+  <si>
+    <t>JPN24A02-05</t>
+  </si>
+  <si>
+    <t>JPN24A03-01</t>
+  </si>
+  <si>
+    <t>JPN24A03-02</t>
+  </si>
+  <si>
+    <t>JPN24A03-03</t>
+  </si>
+  <si>
+    <t>JPN24A04-01</t>
+  </si>
+  <si>
+    <t>JPN24A04-02</t>
   </si>
 </sst>
 </file>
@@ -1601,8 +1779,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:L3" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:L3" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:L22" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+  <autoFilter ref="A1:L22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -5004,7 +5182,7 @@
     </row>
     <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>217</v>
@@ -5033,7 +5211,7 @@
     </row>
     <row r="4" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>218</v>
@@ -5062,7 +5240,7 @@
     </row>
     <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>219</v>
@@ -5091,7 +5269,7 @@
     </row>
     <row r="6" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>220</v>
@@ -5120,7 +5298,7 @@
     </row>
     <row r="7" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>221</v>
@@ -5175,7 +5353,7 @@
     </row>
     <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>223</v>
@@ -5204,7 +5382,7 @@
     </row>
     <row r="10" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>224</v>
@@ -5233,7 +5411,7 @@
     </row>
     <row r="11" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>225</v>
@@ -5262,7 +5440,7 @@
     </row>
     <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>226</v>
@@ -5291,7 +5469,7 @@
     </row>
     <row r="13" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>227</v>
@@ -5320,7 +5498,7 @@
     </row>
     <row r="14" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>228</v>
@@ -5349,7 +5527,7 @@
     </row>
     <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>229</v>
@@ -5378,7 +5556,7 @@
     </row>
     <row r="16" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>230</v>
@@ -5407,7 +5585,7 @@
     </row>
     <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>231</v>
@@ -5436,7 +5614,7 @@
     </row>
     <row r="18" spans="1:11" ht="204" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>232</v>
@@ -5465,7 +5643,7 @@
     </row>
     <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>233</v>
@@ -5494,7 +5672,7 @@
     </row>
     <row r="20" spans="1:11" ht="153" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>234</v>
@@ -5523,7 +5701,7 @@
     </row>
     <row r="21" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>235</v>
@@ -5552,7 +5730,7 @@
     </row>
     <row r="22" spans="1:11" ht="187" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>236</v>
@@ -5581,7 +5759,7 @@
     </row>
     <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>237</v>
@@ -5610,7 +5788,7 @@
     </row>
     <row r="24" spans="1:11" ht="102" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>238</v>
@@ -5639,7 +5817,7 @@
     </row>
     <row r="25" spans="1:11" ht="187" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>239</v>
@@ -5668,7 +5846,7 @@
     </row>
     <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>240</v>
@@ -5697,7 +5875,7 @@
     </row>
     <row r="27" spans="1:11" ht="255" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>241</v>
@@ -5726,7 +5904,7 @@
     </row>
     <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>242</v>
@@ -5755,7 +5933,7 @@
     </row>
     <row r="29" spans="1:11" ht="170" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>243</v>
@@ -5784,7 +5962,7 @@
     </row>
     <row r="30" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>244</v>
@@ -5813,7 +5991,7 @@
     </row>
     <row r="31" spans="1:11" ht="170" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>245</v>
@@ -5842,7 +6020,7 @@
     </row>
     <row r="32" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>246</v>
@@ -5871,7 +6049,7 @@
     </row>
     <row r="33" spans="1:11" ht="221" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>247</v>
@@ -5900,7 +6078,7 @@
     </row>
     <row r="34" spans="1:11" ht="102" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>248</v>
@@ -5929,7 +6107,7 @@
     </row>
     <row r="35" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>249</v>
@@ -5958,7 +6136,7 @@
     </row>
     <row r="36" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>250</v>
@@ -5987,7 +6165,7 @@
     </row>
     <row r="37" spans="1:11" ht="170" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>251</v>
@@ -6091,7 +6269,7 @@
         <v>79</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
@@ -6111,7 +6289,7 @@
     </row>
     <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>254</v>
@@ -6120,7 +6298,7 @@
         <v>79</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>14</v>
@@ -6140,337 +6318,877 @@
     </row>
     <row r="4" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>78</v>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2027</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2028</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="248" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2029</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2030</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2031</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2032</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="340" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2033</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2034</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F16" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2035</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="F17" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2036</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="102" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F18" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2037</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="204" x14ac:dyDescent="0.2">
+      <c r="F19" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2038</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="204" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="F20" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2039</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F21" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2040</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="F22" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2041</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="404" x14ac:dyDescent="0.2">
+      <c r="F23" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="1">
+        <v>2042</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="404" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F24" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2043</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="F25" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="1">
+        <v>2044</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F26" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2045</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F27" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2046</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="F28" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="1">
+        <v>2047</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="119" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F29" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="1">
+        <v>2048</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="187" x14ac:dyDescent="0.2">
+      <c r="F30" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="1">
+        <v>2049</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="187" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F31" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="1">
+        <v>2050</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="323" x14ac:dyDescent="0.2">
+      <c r="F32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="1">
+        <v>2051</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="323" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F33" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2052</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>41</v>
@@ -6478,82 +7196,226 @@
       <c r="C34" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="F34" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="1">
+        <v>2053</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="136" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F35" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="1">
+        <v>2054</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="F36" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2055</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="153" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="F37" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2056</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="119" x14ac:dyDescent="0.2">
+      <c r="F38" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="1">
+        <v>2057</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="119" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="85" x14ac:dyDescent="0.2">
+      <c r="F39" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="1">
+        <v>2058</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="221" x14ac:dyDescent="0.2">
+      <c r="F40" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2059</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="221" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="1">
+        <v>2060</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -6567,7 +7429,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0DD7501-CB0C-FE45-BCB2-B7DDD63724CD}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -6619,12 +7481,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>255</v>
+        <v>366</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
@@ -6642,17 +7507,528 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>374</v>
+      </c>
       <c r="B3" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="1" t="s">
-        <v>261</v>
+        <v>367</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2026</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2027</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2028</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2029</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2030</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2031</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2032</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2033</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2034</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2035</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2036</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2037</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2038</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2039</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="306" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2040</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="238" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2041</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2042</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2043</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2044</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/input/asics.xlsx
+++ b/data/input/asics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA10469-6A7D-104A-8F24-F70728FB2454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28C026D-1FC7-8741-9986-A161DA355391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="448">
   <si>
     <t>ID</t>
   </si>
@@ -1363,6 +1363,132 @@
   </si>
   <si>
     <t>JPN24A04-02</t>
+  </si>
+  <si>
+    <t>Aiming to be the No. 1 Global Sports Brand</t>
+  </si>
+  <si>
+    <t>A Look Back on 2025</t>
+  </si>
+  <si>
+    <t>In 2025, strong growth continued, making it a year in which we felt we ascended to an even higher stage of evolution. From a financial perspective, we achieved revenue and profit growth for the fifth consecutive year. Net sales exceeded ¥800.0 billion, operating profit surpassed ¥140.0 billion, and operating margin reached 17.6%, all marking record highs. The operating margin stands at a top-class level within the industry, and we expect continued revenue and profit growth in 2026.</t>
+  </si>
+  <si>
+    <t>Rather than viewing performance on a single-year basis, I aim to steadily deliver stronger results year by year as part of our long-term growth trajectory. Looking at 2025 from this perspective, initiatives in the Performance Running category, which has long been the driving force of ASICS, progressed steadily toward achieving the No. 1 share of shoes worn at major marathons. In addition, the SportStyle and Onitsuka Tiger categories have grown into major pillars supporting overall performance. Net sales for both categories exceeded ¥100.0 billion for the
+first time, and their profitability remains exceptionally high, giving me strong confidence that they will drive our future growth. Onitsuka Tiger in particular has strengthened its brand presence in Europe and is beginning to establish its position as a luxury lifestyle brand that is not reliant on short-term trends</t>
+  </si>
+  <si>
+    <t>It was also a year in which we laid the groundwork for further growth. Positioning 2025 as the “Year of JAPAN,” we leveraged events such as the World Athletics Championships Tokyo 25 to communicate the ASICS brand both within Japan and globally. We also launched METASPEED RAY, our lightest model in the shoe line, which received strong feedback such as “I didn’t know shoes could be this light,” and “They’ve changed the way I view ASICS,” providing a significant catalyst for elevating the brand.</t>
+  </si>
+  <si>
+    <t>In addition, we made further progress in expanding our running ecosystem by bringing race registration companies in Spain and Thailand into the Group and deciding to acquire business assets of multiple race registration services in the United States, steadily increasing contact points with runners worldwide.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We also received multiple external recognitions in areas such as intellectual property (IP), corporate governance, and investor relations (IR), reflecting steady progress in our corporate functions.
+</t>
+  </si>
+  <si>
+    <t>However, ASICS is still growing. We will continue to accelerate our progress and aim to
+become the No. 1 global sports brand from Japan.</t>
+  </si>
+  <si>
+    <t>Dialogue with the Capital Markets</t>
+  </si>
+  <si>
+    <t>JPN25A01-00</t>
+  </si>
+  <si>
+    <t>JPN25A02-00</t>
+  </si>
+  <si>
+    <t>In 2025, we began holding interactive IR briefings for individual investors. I attended sessions in Naha, Okinawa Prefecture; Sapporo, Hokkaido Prefecture; and Tokyo, where I had the opportunity to engage directly with participants. The comments that left a strong impression were, “It is thanks to ASICS shoes that I have been able to stay active at my age.” and “I hope you keep making shoes with this level of comfort.” The participant said they wanted to share this with me directly, which was an extremely rewarding moment. At the IR briefing held in March 2026, Outside Director Mitsuru Murai spoke on the intersection of sports and business, and all outside directors took part at the end of the session to offer their remarks. As a company that handles consumer goods, we aim to cultivate both loyal fans of ASICS and long-term shareholders, and we will continue to promote two-way communication going forward.</t>
+  </si>
+  <si>
+    <t>We also had numerous opportunities to engage with institutional investors, whose insights have been highly valuable in areas such as corporate governance, capital policy, and product development. I have seen an increase in direct engagement from institutional investors, and hearing comments from them about how excited they are to see our growth has been a great source of encouragement. We will continue to use the feedback of capital market participants as a driving force behind our further advancement.</t>
+  </si>
+  <si>
+    <t>Board Operations</t>
+  </si>
+  <si>
+    <t>Our Board of Directors conducts active discussions under a structure in which a majority of its members are outside directors with extensive experience and specialized expertise. In addition to statutory resolutions and reporting matters, the Board designates key matters for discussion related to the future growth of the ASICS Group. Outside directors provide frank opinions and proposals, which are promptly and carefully reflected in management, with the outcomes reported at the following month’s Board meeting. We recognize that the supervision of business execution, led by independent outside directors, is functioning effectively.</t>
+  </si>
+  <si>
+    <t>Furthermore, following approval at the Ordinary General Meeting of Shareholders held in March 2026, Jenifer Rogers was appointed as our first non-Japanese director. With Ms. Rogers bringing a global perspective on corporate management, specialized legal expertise, and extensive experience in the financial sector, her appointment will further strengthen the Board’s oversight function and effectiveness while promoting transparent management.</t>
+  </si>
+  <si>
+    <t>The ASICS Foundation</t>
+  </si>
+  <si>
+    <t>In April 2025, we established the ASICS Foundation, a general incorporated foundation. The Company established the foundation based on the belief that contributing to the mental and physical well-being of more people by addressing social issues related to exercise and sports is a core part of its mission. Under independent operation, in its first year, the foundation is providing grants to six organizations across four countries—Japan, India, Indonesia, and Cambodia—to support their activities for up to three years. While ASICS will continue to pursue growth with a focus on profitability as a business entity, the foundation will take on the role of contributing to individuals facing social and economic challenges.</t>
+  </si>
+  <si>
+    <t>Challenges for Enhancing Corporate Value</t>
+  </si>
+  <si>
+    <t>To date, we have improved profitability through a focus on selection and concentration. While continuing to pursue this high level of profitability and high-quality growth, we believe it is now necessary to expand profit levels going forward. There remain several challenges to address in achieving this.</t>
+  </si>
+  <si>
+    <t>First is the securing of talent to support future growth and innovation. Under the leadership of COO Mitsuyuki Tominaga, diversity of talent has increased significantly as part of the transformation to a Global Integrated Enterprise. For example, the head of ASICS India Private Limited has been appointed as an executive officer at headquarters, and the head of marketing in ASICS Europe B.V. has assumed the role of senior general manager at headquarters. These developments represent major changes, enabling the global deployment of best practices from individual regions and enhancing overall optimization while also fostering shared understanding of management and corporate strategy between headquarters and regional operating companies. They also create opportunities for the development and advancement of next-generation management talent.</t>
+  </si>
+  <si>
+    <t>Second is continuous innovation. To this end, we are strengthening investments in research facilities and manufacturing. In addition to its existing research base in Japan, new research hubs have been established in Europe and the United States, alongside partnerships with universities and research institutions. The Company is also advancing initiatives such as the opening of the Onitsuka Innovative Factory in Tottori Prefecture and the establishment of the ASICS TECHNICAL LAB, a manufacturing facility located in Hyogo Prefecture for top athletes. IP strategy is also critical. By involving the IP function from the product development stage, we will ensure that the outcomes of innovation are firmly linked to brand value.</t>
+  </si>
+  <si>
+    <t>As we enter the next stage of accelerated growth, the Company is addressing these challenges head-on, as outlined in this integrated report. We look forward to your continued expectations as ASICS strives to become the No. 1 global sports brand.</t>
+  </si>
+  <si>
+    <t>JPN25A03-00</t>
+  </si>
+  <si>
+    <t>JPN25A01-01</t>
+  </si>
+  <si>
+    <t>JPN25A01-02</t>
+  </si>
+  <si>
+    <t>JPN25A01-03</t>
+  </si>
+  <si>
+    <t>JPN25A01-04</t>
+  </si>
+  <si>
+    <t>JPN25A01-05</t>
+  </si>
+  <si>
+    <t>JPN25A01-06</t>
+  </si>
+  <si>
+    <t>JPN25A02-01</t>
+  </si>
+  <si>
+    <t>JPN25A02-02</t>
+  </si>
+  <si>
+    <t>JPN25A03-01</t>
+  </si>
+  <si>
+    <t>JPN25A03-02</t>
+  </si>
+  <si>
+    <t>JPN25A04-00</t>
+  </si>
+  <si>
+    <t>JPN25A04-01</t>
+  </si>
+  <si>
+    <t>JPN25A05-00</t>
+  </si>
+  <si>
+    <t>JPN25A05-01</t>
+  </si>
+  <si>
+    <t>JPN25A05-02</t>
+  </si>
+  <si>
+    <t>JPN25A05-03</t>
+  </si>
+  <si>
+    <t>JPN25A05-04</t>
   </si>
 </sst>
 </file>
@@ -1803,8 +1929,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:L22" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+  <autoFilter ref="A1:L22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -8038,7 +8164,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD557F4C-FB45-B54C-81EB-74DD644B336B}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -8090,11 +8216,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
@@ -8111,7 +8242,528 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/input/asics.xlsx
+++ b/data/input/asics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28C026D-1FC7-8741-9986-A161DA355391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98749505-28FD-C142-9C57-F90B2CCDA340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6420" yWindow="600" windowWidth="22380" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="451">
   <si>
     <t>ID</t>
   </si>
@@ -1489,6 +1489,15 @@
   </si>
   <si>
     <t>JPN25A05-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">message </t>
+  </si>
+  <si>
+    <t>Source_type</t>
+  </si>
+  <si>
+    <t>integrated_report</t>
   </si>
 </sst>
 </file>
@@ -1542,19 +1551,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="84">
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="90">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1572,21 +1569,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1745,6 +1727,51 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1809,144 +1836,150 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L60" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
-  <autoFilter ref="A1:L60" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:M60" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+  <autoFilter ref="A1:M60" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="70"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="68"/>
+    <tableColumn id="13" xr3:uid="{6BCF903D-B946-8047-9828-66413972ECB6}" name="Source_type" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="67"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="65"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="64"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="63"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L31" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
-  <autoFilter ref="A1:L31" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:M31" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
+  <autoFilter ref="A1:M31" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="30"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="29"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="54"/>
+    <tableColumn id="13" xr3:uid="{6570256F-1337-8D44-943A-90DA6C5B12A6}" name="Source_type" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:L37" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
-  <autoFilter ref="A1:L37" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:M37" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+  <autoFilter ref="A1:M37" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="CEO" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="15"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{CE985575-B20E-5B41-82ED-541BF3E60C06}" name="Source_type" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="CEO" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{91060F3E-0B02-0F49-9464-096A57BA32E7}" name="Tableau1348" displayName="Tableau1348" ref="A1:L41" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{91060F3E-0B02-0F49-9464-096A57BA32E7}" name="Tableau1348" displayName="Tableau1348" ref="A1:M41" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="A1:M41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{0FC74C30-0962-A14E-847E-3BD5B25B5351}" name="ID" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{C7C901AE-1A30-FB47-85DC-35A6B31CEC7B}" name="Text" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{F4ED2FC7-93B1-3F4A-9B4F-290279B887B2}" name="Text_type" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{9D90BC68-BA7E-F34D-B3F6-C0973AE7FBAC}" name="Leadership_context" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{BECC38E4-659E-B54D-8D6D-F79323C4FD32}" name="Information_valence" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{0D683163-5F34-8844-B60C-D21DB7EBE838}" name="Communication_type" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{8DDEB90A-3B40-014A-96D8-A24880305585}" name="Company" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{BB63E2C9-1A80-424B-8DB7-B1D47C0A0119}" name="Country" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{4D5F9A30-522F-7D4D-B61F-C3C4E52F9F7C}" name="Year" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{6EB4002B-3104-4E41-BE56-50D81B53C531}" name="Covid" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{77191CD6-3DB8-BB4F-801D-AEE91A59435B}" name="CEO" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{07FAF978-D7C1-4B43-BDE0-228C777612CA}" name="Comment" dataDxfId="3"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{0FC74C30-0962-A14E-847E-3BD5B25B5351}" name="ID" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{C7C901AE-1A30-FB47-85DC-35A6B31CEC7B}" name="Text" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{F4ED2FC7-93B1-3F4A-9B4F-290279B887B2}" name="Text_type" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{9D90BC68-BA7E-F34D-B3F6-C0973AE7FBAC}" name="Leadership_context" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{BECC38E4-659E-B54D-8D6D-F79323C4FD32}" name="Information_valence" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{0D683163-5F34-8844-B60C-D21DB7EBE838}" name="Communication_type" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{A142ABD1-0217-3F4A-943B-1E30C4B499DA}" name="Source_type" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{8DDEB90A-3B40-014A-96D8-A24880305585}" name="Company" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{BB63E2C9-1A80-424B-8DB7-B1D47C0A0119}" name="Country" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{4D5F9A30-522F-7D4D-B61F-C3C4E52F9F7C}" name="Year" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{6EB4002B-3104-4E41-BE56-50D81B53C531}" name="Covid" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{77191CD6-3DB8-BB4F-801D-AEE91A59435B}" name="CEO" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{07FAF978-D7C1-4B43-BDE0-228C777612CA}" name="Comment" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:L22" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:L22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:M22" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A1:M22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="CEO" dataDxfId="58"/>
-    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="57"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{A2917E69-1A52-5541-A577-5DDC36BEC468}" name="Source_type" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="CEO" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:L22" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A1:L22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8002BDD6-C2C9-F141-B94A-F674912E18FE}" name="Tableau134567" displayName="Tableau134567" ref="A1:M22" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
+  <autoFilter ref="A1:M22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{8DEBADB1-BE5F-F543-AE06-80C153895417}" name="ID" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{8B65CBCF-32BB-5C44-B286-3C8D05E43969}" name="Text" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{FA1AB22B-304F-E14F-9E52-8C69987599E3}" name="Text_type" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="CEO" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="43"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{8DEBADB1-BE5F-F543-AE06-80C153895417}" name="ID" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{8B65CBCF-32BB-5C44-B286-3C8D05E43969}" name="Text" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{FA1AB22B-304F-E14F-9E52-8C69987599E3}" name="Text_type" dataDxfId="85"/>
+    <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{4833111C-1647-E743-BF99-61B814ACEB88}" name="Source_type" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="81"/>
+    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="80"/>
+    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="79"/>
+    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="78"/>
+    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="CEO" dataDxfId="77"/>
+    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="76"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2269,7 +2302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3826A9C-6C80-494E-9252-B920A5705A8F}">
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2278,12 +2311,13 @@
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2303,25 +2337,28 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -2335,25 +2372,28 @@
         <v>81</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2020</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>86</v>
       </c>
@@ -2367,25 +2407,28 @@
         <v>81</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
         <v>2020</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>85</v>
       </c>
@@ -2402,25 +2445,28 @@
         <v>82</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
         <v>2020</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>87</v>
       </c>
@@ -2437,25 +2483,28 @@
         <v>81</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
         <v>2020</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>88</v>
       </c>
@@ -2472,25 +2521,28 @@
         <v>82</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
         <v>2020</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>89</v>
       </c>
@@ -2507,25 +2559,28 @@
         <v>82</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
         <v>2020</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="306" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>90</v>
       </c>
@@ -2542,25 +2597,28 @@
         <v>82</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
         <v>2020</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>103</v>
       </c>
@@ -2577,25 +2635,28 @@
         <v>81</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="1">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
         <v>2020</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>104</v>
       </c>
@@ -2612,25 +2673,28 @@
         <v>81</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
         <v>2020</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>105</v>
       </c>
@@ -2647,25 +2711,28 @@
         <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
         <v>2020</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>106</v>
       </c>
@@ -2679,25 +2746,28 @@
         <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
         <v>2020</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>107</v>
       </c>
@@ -2711,25 +2781,28 @@
         <v>83</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="1">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
         <v>2020</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
@@ -2743,25 +2816,28 @@
         <v>81</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
         <v>2020</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>108</v>
       </c>
@@ -2778,25 +2854,28 @@
         <v>82</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
         <v>2020</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>109</v>
       </c>
@@ -2813,25 +2892,28 @@
         <v>82</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="1">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
         <v>2020</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>110</v>
       </c>
@@ -2848,25 +2930,28 @@
         <v>81</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
         <v>2021</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>111</v>
       </c>
@@ -2883,25 +2968,28 @@
         <v>82</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
         <v>2020</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>112</v>
       </c>
@@ -2918,25 +3006,28 @@
         <v>81</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
         <v>2020</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>113</v>
       </c>
@@ -2953,25 +3044,28 @@
         <v>81</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
         <v>2020</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>114</v>
       </c>
@@ -2988,25 +3082,28 @@
         <v>96</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1">
         <v>2020</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>115</v>
       </c>
@@ -3023,25 +3120,28 @@
         <v>81</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="1">
         <v>2020</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>116</v>
       </c>
@@ -3058,25 +3158,28 @@
         <v>81</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="1">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1">
         <v>2020</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>117</v>
       </c>
@@ -3093,25 +3196,28 @@
         <v>81</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="1">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="1">
         <v>2020</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>118</v>
       </c>
@@ -3128,25 +3234,28 @@
         <v>81</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="1">
+        <v>14</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="1">
         <v>2020</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>119</v>
       </c>
@@ -3163,25 +3272,28 @@
         <v>81</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="1">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="1">
         <v>2020</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>120</v>
       </c>
@@ -3198,25 +3310,28 @@
         <v>96</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="1">
+        <v>14</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="1">
         <v>2020</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>121</v>
       </c>
@@ -3233,25 +3348,28 @@
         <v>82</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="1">
+        <v>14</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="1">
         <v>2020</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>122</v>
       </c>
@@ -3265,25 +3383,28 @@
         <v>81</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="1">
+        <v>14</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="1">
         <v>2021</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>123</v>
       </c>
@@ -3300,25 +3421,28 @@
         <v>81</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="1">
+        <v>14</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="1">
         <v>2020</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>124</v>
       </c>
@@ -3335,25 +3459,28 @@
         <v>81</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="1">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="1">
         <v>2020</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>125</v>
       </c>
@@ -3367,25 +3494,28 @@
         <v>154</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="1">
+        <v>14</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="1">
         <v>2020</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>126</v>
       </c>
@@ -3402,25 +3532,28 @@
         <v>96</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="1">
+        <v>14</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="1">
         <v>2020</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>127</v>
       </c>
@@ -3437,25 +3570,28 @@
         <v>96</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="1">
+        <v>14</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="1">
         <v>2020</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>128</v>
       </c>
@@ -3472,25 +3608,28 @@
         <v>81</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="1">
+        <v>14</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="1">
         <v>2020</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>129</v>
       </c>
@@ -3507,25 +3646,28 @@
         <v>101</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="1">
+        <v>14</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="1">
         <v>2021</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>130</v>
       </c>
@@ -3542,25 +3684,28 @@
         <v>102</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="1">
+        <v>14</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="1">
         <v>2020</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>131</v>
       </c>
@@ -3574,25 +3719,28 @@
         <v>83</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="1">
+        <v>14</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="1">
         <v>2020</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>132</v>
       </c>
@@ -3606,25 +3754,28 @@
         <v>83</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="1">
+        <v>14</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="1">
         <v>2020</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L39" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>133</v>
       </c>
@@ -3635,25 +3786,28 @@
         <v>78</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="1">
+        <v>14</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="1">
         <v>2020</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>134</v>
       </c>
@@ -3667,25 +3821,28 @@
         <v>83</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="1">
+        <v>14</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="1">
         <v>2020</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L41" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>135</v>
       </c>
@@ -3702,25 +3859,28 @@
         <v>96</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="1">
+        <v>14</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="1">
         <v>2020</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>136</v>
       </c>
@@ -3737,25 +3897,28 @@
         <v>102</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I43" s="1">
+        <v>14</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="1">
         <v>2020</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L43" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>137</v>
       </c>
@@ -3769,25 +3932,28 @@
         <v>96</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I44" s="1">
+        <v>14</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="1">
         <v>2020</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>138</v>
       </c>
@@ -3801,25 +3967,28 @@
         <v>81</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="1">
+        <v>14</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="1">
         <v>2020</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L45" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="153" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>139</v>
       </c>
@@ -3830,25 +3999,28 @@
         <v>78</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I46" s="1">
+        <v>14</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="1">
         <v>2020</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>140</v>
       </c>
@@ -3859,25 +4031,28 @@
         <v>78</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="1">
+        <v>14</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J47" s="1">
         <v>2020</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L47" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>141</v>
       </c>
@@ -3894,25 +4069,28 @@
         <v>102</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="1">
+        <v>14</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="1">
         <v>2020</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L48" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>142</v>
       </c>
@@ -3929,25 +4107,28 @@
         <v>81</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I49" s="1">
+        <v>14</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J49" s="1">
         <v>2020</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>143</v>
       </c>
@@ -3964,25 +4145,28 @@
         <v>96</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I50" s="1">
+        <v>14</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="1">
         <v>2020</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L50" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>144</v>
       </c>
@@ -3993,25 +4177,28 @@
         <v>78</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I51" s="1">
+        <v>14</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="1">
         <v>2020</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>145</v>
       </c>
@@ -4022,25 +4209,28 @@
         <v>78</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52" s="1">
+        <v>14</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="1">
         <v>2020</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L52" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>146</v>
       </c>
@@ -4054,25 +4244,28 @@
         <v>92</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I53" s="1">
+        <v>14</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="1">
         <v>2020</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
@@ -4086,25 +4279,28 @@
         <v>92</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I54" s="1">
+        <v>14</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="1">
         <v>2020</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L54" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>148</v>
       </c>
@@ -4115,25 +4311,28 @@
         <v>78</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I55" s="1">
+        <v>14</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="1">
         <v>2020</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L55" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>149</v>
       </c>
@@ -4144,25 +4343,28 @@
         <v>78</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I56" s="1">
+        <v>14</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="1">
         <v>2020</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L56" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>150</v>
       </c>
@@ -4173,25 +4375,28 @@
         <v>78</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I57" s="1">
+        <v>14</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="1">
         <v>2020</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L57" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>151</v>
       </c>
@@ -4202,25 +4407,28 @@
         <v>78</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I58" s="1">
+        <v>14</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="1">
         <v>2020</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L58" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>152</v>
       </c>
@@ -4231,25 +4439,28 @@
         <v>78</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I59" s="1">
+        <v>14</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="1">
         <v>2020</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L59" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>153</v>
       </c>
@@ -4260,21 +4471,24 @@
         <v>78</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>252</v>
+        <v>448</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I60" s="1">
+        <v>14</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="1">
         <v>2020</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L60" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4289,7 +4503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD18CE3-D2D1-DD49-8602-5C2A7C693BA7}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -4297,13 +4511,13 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4323,25 +4537,28 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -4355,22 +4572,25 @@
         <v>252</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2021</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>187</v>
       </c>
@@ -4384,22 +4604,25 @@
         <v>252</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
         <v>2021</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>188</v>
       </c>
@@ -4413,22 +4636,25 @@
         <v>252</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
         <v>2021</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>189</v>
       </c>
@@ -4442,22 +4668,25 @@
         <v>252</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
         <v>2021</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>190</v>
       </c>
@@ -4471,22 +4700,25 @@
         <v>252</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
         <v>2021</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>191</v>
       </c>
@@ -4500,22 +4732,25 @@
         <v>252</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
         <v>2021</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>192</v>
       </c>
@@ -4529,22 +4764,25 @@
         <v>252</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
         <v>2021</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>193</v>
       </c>
@@ -4558,22 +4796,25 @@
         <v>252</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="1">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
         <v>2021</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>194</v>
       </c>
@@ -4587,22 +4828,25 @@
         <v>252</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
         <v>2021</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>195</v>
       </c>
@@ -4616,22 +4860,25 @@
         <v>252</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
         <v>2021</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>196</v>
       </c>
@@ -4645,22 +4892,25 @@
         <v>252</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
         <v>2021</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>197</v>
       </c>
@@ -4674,22 +4924,25 @@
         <v>252</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="1">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
         <v>2021</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>198</v>
       </c>
@@ -4703,22 +4956,25 @@
         <v>252</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
         <v>2021</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>199</v>
       </c>
@@ -4732,22 +4988,25 @@
         <v>252</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
         <v>2021</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>200</v>
       </c>
@@ -4761,22 +5020,25 @@
         <v>252</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="1">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
         <v>2021</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="255" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>201</v>
       </c>
@@ -4790,22 +5052,25 @@
         <v>252</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
         <v>2021</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>202</v>
       </c>
@@ -4819,22 +5084,25 @@
         <v>252</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
         <v>2021</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>203</v>
       </c>
@@ -4848,22 +5116,25 @@
         <v>252</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
         <v>2021</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>204</v>
       </c>
@@ -4877,22 +5148,25 @@
         <v>252</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
         <v>2021</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>205</v>
       </c>
@@ -4906,22 +5180,25 @@
         <v>252</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1">
         <v>2021</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>206</v>
       </c>
@@ -4935,22 +5212,25 @@
         <v>252</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="1">
         <v>2021</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K22" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>207</v>
       </c>
@@ -4964,22 +5244,25 @@
         <v>252</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="1">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1">
         <v>2021</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K23" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>208</v>
       </c>
@@ -4993,22 +5276,25 @@
         <v>252</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="1">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="1">
         <v>2021</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K24" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>209</v>
       </c>
@@ -5022,22 +5308,25 @@
         <v>252</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="1">
+        <v>14</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="1">
         <v>2021</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K25" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>210</v>
       </c>
@@ -5051,22 +5340,25 @@
         <v>252</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="1">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="1">
         <v>2021</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>211</v>
       </c>
@@ -5080,22 +5372,25 @@
         <v>252</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="1">
+        <v>14</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="1">
         <v>2021</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>212</v>
       </c>
@@ -5109,22 +5404,25 @@
         <v>252</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="1">
+        <v>14</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="1">
         <v>2021</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>213</v>
       </c>
@@ -5138,22 +5436,25 @@
         <v>252</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="1">
+        <v>14</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="1">
         <v>2021</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K29" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>214</v>
       </c>
@@ -5167,22 +5468,25 @@
         <v>252</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="1">
+        <v>14</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="1">
         <v>2021</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K30" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>215</v>
       </c>
@@ -5196,18 +5500,21 @@
         <v>252</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="1">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="1">
         <v>2021</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5222,7 +5529,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F818BF7-D6BE-A545-9E45-A87A4152B2E0}">
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -5230,16 +5537,16 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5259,25 +5566,28 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -5291,22 +5601,25 @@
         <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2022</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -5320,22 +5633,25 @@
         <v>43</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
         <v>2022</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>294</v>
       </c>
@@ -5349,22 +5665,25 @@
         <v>43</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
         <v>2022</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>295</v>
       </c>
@@ -5378,22 +5697,25 @@
         <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
         <v>2022</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="187" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>296</v>
       </c>
@@ -5407,22 +5729,25 @@
         <v>43</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
         <v>2022</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>297</v>
       </c>
@@ -5436,22 +5761,25 @@
         <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
         <v>2022</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>222</v>
       </c>
@@ -5462,22 +5790,25 @@
         <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
         <v>2022</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>298</v>
       </c>
@@ -5491,22 +5822,25 @@
         <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="1">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
         <v>2022</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>299</v>
       </c>
@@ -5520,22 +5854,25 @@
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
         <v>2022</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>300</v>
       </c>
@@ -5549,22 +5886,25 @@
         <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
         <v>2022</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>301</v>
       </c>
@@ -5578,22 +5918,25 @@
         <v>43</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
         <v>2022</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>302</v>
       </c>
@@ -5607,22 +5950,25 @@
         <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="1">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
         <v>2022</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="187" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>303</v>
       </c>
@@ -5636,22 +5982,25 @@
         <v>43</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
         <v>2022</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>304</v>
       </c>
@@ -5665,22 +6014,25 @@
         <v>43</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
         <v>2022</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>305</v>
       </c>
@@ -5694,22 +6046,25 @@
         <v>43</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="1">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
         <v>2022</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>306</v>
       </c>
@@ -5723,22 +6078,25 @@
         <v>43</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
         <v>2022</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>307</v>
       </c>
@@ -5752,22 +6110,25 @@
         <v>43</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
         <v>2022</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>308</v>
       </c>
@@ -5781,22 +6142,25 @@
         <v>43</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
         <v>2022</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="153" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>309</v>
       </c>
@@ -5810,22 +6174,25 @@
         <v>43</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
         <v>2022</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>310</v>
       </c>
@@ -5839,22 +6206,25 @@
         <v>43</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1">
         <v>2022</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>311</v>
       </c>
@@ -5868,22 +6238,25 @@
         <v>43</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="1">
         <v>2022</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K22" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>312</v>
       </c>
@@ -5897,22 +6270,25 @@
         <v>43</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="1">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1">
         <v>2022</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K23" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>313</v>
       </c>
@@ -5926,22 +6302,25 @@
         <v>43</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="1">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="1">
         <v>2022</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K24" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>314</v>
       </c>
@@ -5955,22 +6334,25 @@
         <v>43</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="1">
+        <v>14</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="1">
         <v>2022</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K25" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>315</v>
       </c>
@@ -5984,22 +6366,25 @@
         <v>43</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="1">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="1">
         <v>2022</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="255" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="255" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>316</v>
       </c>
@@ -6013,22 +6398,25 @@
         <v>43</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="1">
+        <v>14</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="1">
         <v>2022</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>317</v>
       </c>
@@ -6042,22 +6430,25 @@
         <v>43</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="1">
+        <v>14</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="1">
         <v>2022</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>318</v>
       </c>
@@ -6071,22 +6462,25 @@
         <v>43</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="1">
+        <v>14</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="1">
         <v>2022</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K29" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>319</v>
       </c>
@@ -6100,22 +6494,25 @@
         <v>43</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="1">
+        <v>14</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="1">
         <v>2022</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K30" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>320</v>
       </c>
@@ -6129,22 +6526,25 @@
         <v>43</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="1">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="1">
         <v>2022</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>321</v>
       </c>
@@ -6158,22 +6558,25 @@
         <v>43</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="1">
+        <v>14</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="1">
         <v>2022</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K32" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>322</v>
       </c>
@@ -6187,22 +6590,25 @@
         <v>43</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="1">
+        <v>14</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="1">
         <v>2022</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K33" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>323</v>
       </c>
@@ -6216,22 +6622,25 @@
         <v>43</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="1">
+        <v>14</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="1">
         <v>2022</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K34" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>324</v>
       </c>
@@ -6245,22 +6654,25 @@
         <v>43</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="1">
+        <v>14</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="1">
         <v>2022</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K35" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>325</v>
       </c>
@@ -6274,22 +6686,25 @@
         <v>43</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="1">
+        <v>14</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="1">
         <v>2022</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>326</v>
       </c>
@@ -6303,18 +6718,21 @@
         <v>43</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="1">
+        <v>14</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="1">
         <v>2022</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6329,7 +6747,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{745FBC29-1348-FC4A-97A0-E4A368B4DC13}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -6337,16 +6755,16 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6366,25 +6784,28 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6398,22 +6819,25 @@
         <v>258</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2023</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>327</v>
       </c>
@@ -6427,22 +6851,25 @@
         <v>258</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
         <v>2022</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>328</v>
       </c>
@@ -6456,22 +6883,25 @@
         <v>258</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
         <v>2023</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>329</v>
       </c>
@@ -6485,22 +6915,25 @@
         <v>258</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
         <v>2024</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>330</v>
       </c>
@@ -6514,22 +6947,25 @@
         <v>258</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
         <v>2025</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>331</v>
       </c>
@@ -6543,22 +6979,25 @@
         <v>258</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
         <v>2026</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>332</v>
       </c>
@@ -6572,22 +7011,25 @@
         <v>258</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
         <v>2027</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>333</v>
       </c>
@@ -6601,22 +7043,25 @@
         <v>258</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="1">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
         <v>2028</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="248" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="248" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>334</v>
       </c>
@@ -6630,22 +7075,25 @@
         <v>258</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
         <v>2029</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>335</v>
       </c>
@@ -6659,22 +7107,25 @@
         <v>258</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
         <v>2030</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>336</v>
       </c>
@@ -6688,22 +7139,25 @@
         <v>258</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
         <v>2031</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>337</v>
       </c>
@@ -6717,22 +7171,25 @@
         <v>258</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="1">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
         <v>2032</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="340" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="340" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>338</v>
       </c>
@@ -6746,22 +7203,25 @@
         <v>258</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
         <v>2033</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>339</v>
       </c>
@@ -6775,22 +7235,25 @@
         <v>258</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
         <v>2034</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="221" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>340</v>
       </c>
@@ -6804,22 +7267,25 @@
         <v>258</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="1">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
         <v>2035</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>341</v>
       </c>
@@ -6833,22 +7299,25 @@
         <v>258</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
         <v>2036</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>342</v>
       </c>
@@ -6862,22 +7331,25 @@
         <v>258</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
         <v>2037</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>343</v>
       </c>
@@ -6891,22 +7363,25 @@
         <v>258</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
         <v>2038</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>344</v>
       </c>
@@ -6920,22 +7395,25 @@
         <v>258</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
         <v>2039</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>345</v>
       </c>
@@ -6949,22 +7427,25 @@
         <v>258</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1">
         <v>2040</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>346</v>
       </c>
@@ -6978,22 +7459,25 @@
         <v>258</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="1">
         <v>2041</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K22" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>347</v>
       </c>
@@ -7007,22 +7491,25 @@
         <v>258</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="1">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1">
         <v>2042</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K23" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="404" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="404" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>348</v>
       </c>
@@ -7036,22 +7523,25 @@
         <v>258</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="1">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="1">
         <v>2043</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K24" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>349</v>
       </c>
@@ -7065,22 +7555,25 @@
         <v>258</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="1">
+        <v>14</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="1">
         <v>2044</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K25" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="409.6" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>350</v>
       </c>
@@ -7094,22 +7587,25 @@
         <v>258</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="1">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="1">
         <v>2045</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>351</v>
       </c>
@@ -7123,22 +7619,25 @@
         <v>258</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="1">
+        <v>14</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="1">
         <v>2046</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>352</v>
       </c>
@@ -7152,22 +7651,25 @@
         <v>258</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="1">
+        <v>14</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="1">
         <v>2047</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>353</v>
       </c>
@@ -7181,22 +7683,25 @@
         <v>258</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="1">
+        <v>14</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="1">
         <v>2048</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K29" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>354</v>
       </c>
@@ -7210,22 +7715,25 @@
         <v>258</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="1">
+        <v>14</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="1">
         <v>2049</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K30" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>355</v>
       </c>
@@ -7239,22 +7747,25 @@
         <v>258</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="1">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="1">
         <v>2050</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>356</v>
       </c>
@@ -7268,22 +7779,25 @@
         <v>258</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="1">
+        <v>14</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="1">
         <v>2051</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K32" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="323" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>357</v>
       </c>
@@ -7297,22 +7811,25 @@
         <v>258</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="1">
+        <v>14</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="1">
         <v>2052</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K33" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>358</v>
       </c>
@@ -7326,22 +7843,25 @@
         <v>258</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="1">
+        <v>14</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="1">
         <v>2053</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K34" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>359</v>
       </c>
@@ -7355,22 +7875,25 @@
         <v>258</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="1">
+        <v>14</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="1">
         <v>2054</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K35" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>360</v>
       </c>
@@ -7384,22 +7907,25 @@
         <v>258</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="1">
+        <v>14</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="1">
         <v>2055</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="153" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="153" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>361</v>
       </c>
@@ -7413,22 +7939,25 @@
         <v>258</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="1">
+        <v>14</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="1">
         <v>2056</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K37" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>362</v>
       </c>
@@ -7442,22 +7971,25 @@
         <v>258</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="1">
+        <v>14</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="1">
         <v>2057</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>363</v>
       </c>
@@ -7471,22 +8003,25 @@
         <v>258</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="1">
+        <v>14</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="1">
         <v>2058</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>364</v>
       </c>
@@ -7500,22 +8035,25 @@
         <v>258</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="1">
+        <v>14</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="1">
         <v>2059</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K40" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="221" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>365</v>
       </c>
@@ -7529,18 +8067,21 @@
         <v>258</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="1">
+        <v>14</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="1">
         <v>2060</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="K41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7555,7 +8096,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0DD7501-CB0C-FE45-BCB2-B7DDD63724CD}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -7563,13 +8104,13 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7589,25 +8130,28 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -7618,22 +8162,25 @@
         <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2024</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>374</v>
       </c>
@@ -7644,22 +8191,25 @@
         <v>43</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
         <v>2025</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>375</v>
       </c>
@@ -7670,22 +8220,25 @@
         <v>43</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
         <v>2026</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="L4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>392</v>
       </c>
@@ -7696,22 +8249,25 @@
         <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
         <v>2027</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="L5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>393</v>
       </c>
@@ -7722,22 +8278,25 @@
         <v>43</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
         <v>2028</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="L6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>394</v>
       </c>
@@ -7748,22 +8307,25 @@
         <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
         <v>2029</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="L7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="221" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>395</v>
       </c>
@@ -7774,22 +8336,25 @@
         <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
         <v>2030</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="L8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="221" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>396</v>
       </c>
@@ -7800,22 +8365,25 @@
         <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="1">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
         <v>2031</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="L9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>376</v>
       </c>
@@ -7826,22 +8394,25 @@
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
         <v>2032</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>397</v>
       </c>
@@ -7852,22 +8423,25 @@
         <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
         <v>2033</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="255" x14ac:dyDescent="0.2">
+      <c r="L11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>398</v>
       </c>
@@ -7878,22 +8452,25 @@
         <v>43</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
         <v>2034</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+      <c r="L12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>399</v>
       </c>
@@ -7904,22 +8481,25 @@
         <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="1">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
         <v>2035</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="L13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>400</v>
       </c>
@@ -7930,22 +8510,25 @@
         <v>43</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
         <v>2036</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="306" x14ac:dyDescent="0.2">
+      <c r="L14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="306" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>401</v>
       </c>
@@ -7956,22 +8539,25 @@
         <v>43</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
         <v>2037</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="L15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>384</v>
       </c>
@@ -7982,22 +8568,25 @@
         <v>43</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="1">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
         <v>2038</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="L16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>402</v>
       </c>
@@ -8008,22 +8597,25 @@
         <v>43</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
         <v>2039</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="306" x14ac:dyDescent="0.2">
+      <c r="L17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="306" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>403</v>
       </c>
@@ -8034,22 +8626,25 @@
         <v>43</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
         <v>2040</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="238" x14ac:dyDescent="0.2">
+      <c r="L18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="238" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>404</v>
       </c>
@@ -8060,22 +8655,25 @@
         <v>43</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
         <v>2041</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>391</v>
       </c>
@@ -8086,22 +8684,25 @@
         <v>43</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
         <v>2042</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="L20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>405</v>
       </c>
@@ -8112,22 +8713,25 @@
         <v>43</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1">
         <v>2043</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>406</v>
       </c>
@@ -8138,18 +8742,21 @@
         <v>43</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="1">
         <v>2044</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8164,7 +8771,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD557F4C-FB45-B54C-81EB-74DD644B336B}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -8172,13 +8779,13 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8198,25 +8805,28 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -8227,22 +8837,25 @@
         <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2025</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>416</v>
       </c>
@@ -8253,22 +8866,25 @@
         <v>43</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="1">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
         <v>2025</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>431</v>
       </c>
@@ -8279,22 +8895,25 @@
         <v>43</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
         <v>2025</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+      <c r="L4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>432</v>
       </c>
@@ -8305,22 +8924,25 @@
         <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="1">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
         <v>2025</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="L5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>433</v>
       </c>
@@ -8331,22 +8953,25 @@
         <v>43</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
         <v>2025</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="L6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>434</v>
       </c>
@@ -8357,22 +8982,25 @@
         <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
         <v>2025</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="L7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>435</v>
       </c>
@@ -8383,22 +9011,25 @@
         <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="1">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
         <v>2025</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="L8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>436</v>
       </c>
@@ -8409,22 +9040,25 @@
         <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="1">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
         <v>2025</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="L9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>417</v>
       </c>
@@ -8435,22 +9069,25 @@
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
         <v>2025</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="L10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="221" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>437</v>
       </c>
@@ -8461,22 +9098,25 @@
         <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
         <v>2025</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="L11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>438</v>
       </c>
@@ -8487,22 +9127,25 @@
         <v>43</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="1">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
         <v>2025</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="L12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>430</v>
       </c>
@@ -8513,22 +9156,25 @@
         <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="1">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
         <v>2025</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="L13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>439</v>
       </c>
@@ -8539,22 +9185,25 @@
         <v>43</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="1">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
         <v>2025</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="L14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>440</v>
       </c>
@@ -8565,22 +9214,25 @@
         <v>43</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="1">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
         <v>2025</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="L15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>441</v>
       </c>
@@ -8591,22 +9243,25 @@
         <v>43</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="1">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
         <v>2025</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="L16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>442</v>
       </c>
@@ -8617,22 +9272,25 @@
         <v>43</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="1">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
         <v>2025</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>443</v>
       </c>
@@ -8643,22 +9301,25 @@
         <v>43</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="1">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
         <v>2025</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="L18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>444</v>
       </c>
@@ -8669,22 +9330,25 @@
         <v>43</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
         <v>2025</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="204" x14ac:dyDescent="0.2">
+      <c r="L19" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>445</v>
       </c>
@@ -8695,22 +9359,25 @@
         <v>43</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
         <v>2025</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="L20" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>446</v>
       </c>
@@ -8721,22 +9388,25 @@
         <v>43</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1">
         <v>2025</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="L21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>447</v>
       </c>
@@ -8747,18 +9417,21 @@
         <v>43</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="1">
         <v>2025</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>17</v>
       </c>
     </row>

--- a/data/input/asics.xlsx
+++ b/data/input/asics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A184DE0-4456-924F-AB5F-9F35E97048F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD31B474-1B85-514E-AB1F-CF0F817A86BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="600" windowWidth="28120" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="6200" yWindow="600" windowWidth="22600" windowHeight="17400" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="452">
   <si>
     <t>ID</t>
   </si>
@@ -293,13 +293,6 @@
     <t>negative</t>
   </si>
   <si>
-    <t xml:space="preserve">Analysis and Diagnosis: Coaching Based on Personal Data
-Amid growing demand for running products, the number of subscribers to Runkeeper™, OneASICS™ and other digital services continues to grow. In terms of analysis and diagnosis, based on data collected by these digital services, ASICS will collaborate with other companies and combine personalized services to provide an unprecedented experience. </t>
-  </si>
-  <si>
-    <t>In March 2021, we collaborated with CASIO COMPUTER CO., LTD. which possesses advanced sensing technologies, to launch the Runmetrix service, which visualizes running using a motion sensor attached to the runner’s waist to provide personal coaching services tailored to each individual. As a next step, in October we plan to launch provision of Walkmetrix for walkers.</t>
-  </si>
-  <si>
     <t xml:space="preserve">At the same time, we will promote innovations. From fiscal 2019 up to now, we combined existing organizations separated by function into five categories promoting business that integrates manufacturing and sales. This category system has strengthened management visualization and collaborations between the Head Office and sales companies, significantly transforming the management cycle. Even amid the turmoil caused by COVID-19, we were able to respond quickly in each region, securing funds and managing inventory properly, evidence that our category system worked well. Even in Performance Running, where we have stepped up efforts as a product growth area, the addition of functions reflecting feedback from sales companies has improved ASICS product evaluations, which I feel will be seen in future business performance. e-Commerce (EC) is also expanding rapidly, as consumers shift to more digital purchases. </t>
   </si>
   <si>
@@ -369,9 +362,6 @@
     <t>JPN20A05-05</t>
   </si>
   <si>
-    <t>JPN20A05-06</t>
-  </si>
-  <si>
     <t>JPN20A05-07</t>
   </si>
   <si>
@@ -469,9 +459,6 @@
   </si>
   <si>
     <t>StRAT</t>
-  </si>
-  <si>
-    <t>STRAT-MARKET</t>
   </si>
   <si>
     <t>With the results of our reforms now steadily materializing, in 2022 we will seek even further progress while carrying on the legacy of Tokyo 2020.</t>
@@ -1321,10 +1308,6 @@
   </si>
   <si>
     <t>2024 marked the first year of operations with our new management structure under the leadership of current president and COO Mr. Tominaga. I feel that it was also a year of major change from global and digital perspectives.</t>
-  </si>
-  <si>
-    <t>On the global front, we expanded communication more than ever by having the CEOs of each regional operating company report directly to Mr. Tominaga at our global headquarters. In addition, Executive Board Meetings, which were previously limited to Japanese members of the executive
-body, are now attended by non-Japanese members when topics with a global impact are on the agenda. Discussions on these topics are held in English. Increasingly, department head roles are being taken on by members outside Japan. This all adds up to an organizational structure that is becoming ever more global.</t>
   </si>
   <si>
     <t>On the digital front, we are making progress with the introduction of globally-unified, mission-critical systems, an effort Mr. Tominaga has been involved with since joining ASICS in his previous role as the senior general manager of the IT Division. As a result, we are gaining a granular, real-time understanding of the state of business in each region, down to each store and product. We have already begun using these systems for demand forecasting and production planning. I believe they will help greatly with making forecasts more accurate and with optimizing inventory, which will ultimately improve our profit margins.</t>
@@ -1419,6 +1402,16 @@
   </si>
   <si>
     <t>While passing on our founding philosophy, ASICS will continue to provide valuable products and services to sports lovers and all ASICS stakeholders by adapting changes in line with today’s digital revolution. Additionally, we will contribute to the realization of a sustainable environment and society by focusing on sustainability in all our business activities. ASICS will be intimately involved in exercise and sports for the rest of our lives and will continue to strive toward the realization of a world in which everyone has a healthy mind and body. We ask for your continued understanding and support of ASICS stance and initiatives.</t>
+  </si>
+  <si>
+    <t>On the global front, we expanded communication more than ever by having the CEOs of each regional operating company report directly to Mr. Tominaga at our global headquarters. In addition, Executive Board Meetings, which were previously limited to Japanese members of the executive body, are now attended by non-Japanese members when topics with a global impact are on the agenda. Discussions on these topics are held in English. Increasingly, department head roles are being taken on by members outside Japan. This all adds up to an organizational structure that is becoming ever more global.</t>
+  </si>
+  <si>
+    <t>Analysis and Diagnosis: Coaching Based on Personal Data
+Amid growing demand for running products, the number of subscribers to Runkeeper™, OneASICS™ and other digital services continues to grow. In terms of analysis and diagnosis, based on data collected by these digital services, ASICS will collaborate with other companies and combine personalized services to provide an unprecedented experience. In March 2021, we collaborated with CASIO COMPUTER CO., LTD. which possesses advanced sensing technologies, to launch the Runmetrix service, which visualizes running using a motion sensor attached to the runner’s waist to provide personal coaching services tailored to each individual. As a next step, in October we plan to launch provision of Walkmetrix for walkers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRAT </t>
   </si>
 </sst>
 </file>
@@ -1474,43 +1467,13 @@
   </cellStyles>
   <dxfs count="96">
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1582,6 +1545,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1595,6 +1564,12 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1666,6 +1641,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1679,6 +1660,12 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1750,6 +1737,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1775,130 +1768,130 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N60" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
-  <autoFilter ref="A1:N60" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N59" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+  <autoFilter ref="A1:N59" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="74"/>
-    <tableColumn id="13" xr3:uid="{6BCF903D-B946-8047-9828-66413972ECB6}" name="Source_type" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="73"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="72"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="71"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="70"/>
-    <tableColumn id="14" xr3:uid="{F85EEC66-2554-3C49-B630-8D54162C843F}" name="Communicator_role" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="69"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="72"/>
+    <tableColumn id="13" xr3:uid="{6BCF903D-B946-8047-9828-66413972ECB6}" name="Source_type" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="67"/>
+    <tableColumn id="14" xr3:uid="{F85EEC66-2554-3C49-B630-8D54162C843F}" name="Communicator_role" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N31" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N31" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:N31" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="62"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="60"/>
-    <tableColumn id="13" xr3:uid="{6570256F-1337-8D44-943A-90DA6C5B12A6}" name="Source_type" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="57"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{D8933292-E7B8-8743-89DB-DAE4A4A319E9}" name="Communicator_role" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{6570256F-1337-8D44-943A-90DA6C5B12A6}" name="Source_type" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{D8933292-E7B8-8743-89DB-DAE4A4A319E9}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:N37" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{19FBEB14-3FB0-C34C-B390-33404A670A38}" name="Tableau134" displayName="Tableau134" ref="A1:N37" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:N37" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="46"/>
-    <tableColumn id="13" xr3:uid="{CE985575-B20E-5B41-82ED-541BF3E60C06}" name="Source_type" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{97EBFFD0-1FE7-064A-BC93-83EB00D83017}" name="Communicator_role" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="Communicator_name" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{AC33188A-6BAF-0F4E-AA43-ABE62FDA0518}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{A7668559-7AA5-AC4F-999A-F66EA79D8EBA}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{481854C3-E5E2-F345-8A1C-089DE3DCDBF2}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{11CD308A-5ACF-834D-BE43-86FEE2B1A99C}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{7E48A7DF-1B9B-BB4C-8BDE-972E2A740EF5}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{4E1EA0CA-018F-AF4B-A825-67AEDFCFCAB9}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{CE985575-B20E-5B41-82ED-541BF3E60C06}" name="Source_type" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{17FA0B02-2AA3-AE43-9AD2-FF34BEC398DF}" name="Company" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{84B28D6D-B1C9-524F-845C-AEFF9F653FA0}" name="Country" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{A323F1F0-1F1F-0D44-95EF-F7A5D9FD389D}" name="Year" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{D1AFF042-363F-A240-8D86-2BC0E53B67F8}" name="Covid" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{97EBFFD0-1FE7-064A-BC93-83EB00D83017}" name="Communicator_role" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{A250291B-6395-3244-B416-4E432FA656C1}" name="Communicator_name" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{A1BB75FB-F1FB-5A4F-B6C8-5E9D56969BC7}" name="Comment" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{91060F3E-0B02-0F49-9464-096A57BA32E7}" name="Tableau1348" displayName="Tableau1348" ref="A1:N41" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{91060F3E-0B02-0F49-9464-096A57BA32E7}" name="Tableau1348" displayName="Tableau1348" ref="A1:N41" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:N41" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{0FC74C30-0962-A14E-847E-3BD5B25B5351}" name="ID" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{C7C901AE-1A30-FB47-85DC-35A6B31CEC7B}" name="Text" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{F4ED2FC7-93B1-3F4A-9B4F-290279B887B2}" name="Text_type" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{9D90BC68-BA7E-F34D-B3F6-C0973AE7FBAC}" name="Leadership_context" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{BECC38E4-659E-B54D-8D6D-F79323C4FD32}" name="Information_valence" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{0D683163-5F34-8844-B60C-D21DB7EBE838}" name="Communication_type" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{A142ABD1-0217-3F4A-943B-1E30C4B499DA}" name="Source_type" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{8DDEB90A-3B40-014A-96D8-A24880305585}" name="Company" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{BB63E2C9-1A80-424B-8DB7-B1D47C0A0119}" name="Country" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{4D5F9A30-522F-7D4D-B61F-C3C4E52F9F7C}" name="Year" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{6EB4002B-3104-4E41-BE56-50D81B53C531}" name="Covid" dataDxfId="28"/>
-    <tableColumn id="14" xr3:uid="{25B63537-0377-344F-A085-9DA95E0D304C}" name="Communicator_role" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{77191CD6-3DB8-BB4F-801D-AEE91A59435B}" name="Communicator_name" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{07FAF978-D7C1-4B43-BDE0-228C777612CA}" name="Comment" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{0FC74C30-0962-A14E-847E-3BD5B25B5351}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{C7C901AE-1A30-FB47-85DC-35A6B31CEC7B}" name="Text" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{F4ED2FC7-93B1-3F4A-9B4F-290279B887B2}" name="Text_type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{9D90BC68-BA7E-F34D-B3F6-C0973AE7FBAC}" name="Leadership_context" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{BECC38E4-659E-B54D-8D6D-F79323C4FD32}" name="Information_valence" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{0D683163-5F34-8844-B60C-D21DB7EBE838}" name="Communication_type" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{A142ABD1-0217-3F4A-943B-1E30C4B499DA}" name="Source_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{8DDEB90A-3B40-014A-96D8-A24880305585}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{BB63E2C9-1A80-424B-8DB7-B1D47C0A0119}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{4D5F9A30-522F-7D4D-B61F-C3C4E52F9F7C}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{6EB4002B-3104-4E41-BE56-50D81B53C531}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{25B63537-0377-344F-A085-9DA95E0D304C}" name="Communicator_role" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{77191CD6-3DB8-BB4F-801D-AEE91A59435B}" name="Communicator_name" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{07FAF978-D7C1-4B43-BDE0-228C777612CA}" name="Comment" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:N22" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{813DFF62-3908-CE4B-818B-56648BDC12C5}" name="Tableau13456" displayName="Tableau13456" ref="A1:N22" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:N22" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{CB292B3C-5554-6741-B78D-0CC8766FA408}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{3FA52504-25AB-C649-9DB3-51D1D0CC99DC}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{A0EC927E-A831-FE47-AEF1-339AB7736A15}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{4B9DA6F0-9B59-2946-8257-7BCE0DC66506}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{4DE23804-4E1D-0B47-AECE-3B738734F80F}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{84C1DE3B-B9A9-BE47-A09B-2F784F645C58}" name="Communication_type" dataDxfId="8"/>
     <tableColumn id="13" xr3:uid="{A2917E69-1A52-5541-A577-5DDC36BEC468}" name="Source_type" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{AC12DA90-5DA9-1E41-9D3A-5C37C222D798}" name="Communicator_role" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="Communicator_name" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{49E0FE05-A639-2645-A861-3A5E118C7662}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{CB97E71D-B5E3-534E-9E50-0B62731EC05D}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{A80DE035-2676-3846-B924-91C081F43101}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{C8FCD363-5F1E-A24E-8999-55538920D95B}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{AC12DA90-5DA9-1E41-9D3A-5C37C222D798}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{950FE7C5-D88B-7848-9BF6-79C409709785}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{C28D05BF-8AA1-3347-88D6-6847F35CCB45}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1917,14 +1910,14 @@
     <tableColumn id="4" xr3:uid="{8FD4F8D3-8054-ED45-8D47-57E81162FBFF}" name="Leadership_context" dataDxfId="90"/>
     <tableColumn id="5" xr3:uid="{5711A194-4722-D643-B4E4-0DAEEB9BB398}" name="Information_valence" dataDxfId="89"/>
     <tableColumn id="6" xr3:uid="{A438B45B-E227-2B4D-816E-2178AF7DE0DF}" name="Communication_type" dataDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{4833111C-1647-E743-BF99-61B814ACEB88}" name="Source_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="87"/>
-    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="86"/>
-    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="85"/>
-    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="84"/>
-    <tableColumn id="14" xr3:uid="{2E85A930-D53A-F74B-B953-E9762F261F04}" name="Communicator_role" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="Communicator_name" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{4833111C-1647-E743-BF99-61B814ACEB88}" name="Source_type" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{52690825-954F-3649-BFD2-FF86ED94FF97}" name="Company" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{BA2CDEC4-0D06-5441-9C84-D6A095CFEEAE}" name="Country" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{DE1A0B0E-3B3E-3940-8AFB-F333D11A8BC2}" name="Year" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{6CCD2097-9852-AA4A-B457-161E9F590F12}" name="Covid" dataDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{2E85A930-D53A-F74B-B953-E9762F261F04}" name="Communicator_role" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{5C8A2EE8-A8D3-6A48-BB93-021549E5F619}" name="Communicator_name" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{78135894-C31C-2E4E-8FBE-2E965C478A6D}" name="Comment" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2247,7 +2240,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3826A9C-6C80-494E-9252-B920A5705A8F}">
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2282,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -2297,16 +2290,16 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -2316,14 +2309,17 @@
       <c r="C2" s="1" t="s">
         <v>66</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -2338,7 +2334,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>14</v>
@@ -2354,14 +2350,17 @@
       <c r="C3" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -2376,7 +2375,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>14</v>
@@ -2399,10 +2398,10 @@
         <v>68</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -2417,18 +2416,18 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
@@ -2440,10 +2439,10 @@
         <v>67</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -2458,7 +2457,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>14</v>
@@ -2481,10 +2480,10 @@
         <v>68</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -2499,7 +2498,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>14</v>
@@ -2510,7 +2509,7 @@
         <v>75</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
@@ -2522,10 +2521,10 @@
         <v>68</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -2540,18 +2539,18 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
@@ -2563,10 +2562,10 @@
         <v>68</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -2581,7 +2580,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>14</v>
@@ -2589,7 +2588,7 @@
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>26</v>
@@ -2598,16 +2597,16 @@
         <v>65</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -2622,7 +2621,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>14</v>
@@ -2630,7 +2629,7 @@
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -2645,10 +2644,10 @@
         <v>67</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -2663,7 +2662,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>14</v>
@@ -2671,7 +2670,7 @@
     </row>
     <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>42</v>
@@ -2686,10 +2685,10 @@
         <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -2704,15 +2703,15 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>43</v>
@@ -2724,10 +2723,10 @@
         <v>70</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -2742,7 +2741,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>14</v>
@@ -2750,7 +2749,7 @@
     </row>
     <row r="13" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>44</v>
@@ -2762,10 +2761,10 @@
         <v>69</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -2780,7 +2779,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>14</v>
@@ -2800,10 +2799,10 @@
         <v>67</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -2818,7 +2817,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>14</v>
@@ -2826,7 +2825,7 @@
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
@@ -2841,10 +2840,10 @@
         <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -2859,18 +2858,18 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
@@ -2882,10 +2881,10 @@
         <v>68</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -2900,15 +2899,15 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>79</v>
@@ -2923,10 +2922,10 @@
         <v>67</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -2941,15 +2940,15 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>45</v>
@@ -2964,10 +2963,10 @@
         <v>68</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -2982,7 +2981,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>14</v>
@@ -2990,7 +2989,7 @@
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>30</v>
@@ -3005,10 +3004,10 @@
         <v>67</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -3023,15 +3022,15 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>46</v>
@@ -3046,10 +3045,10 @@
         <v>67</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -3064,15 +3063,15 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>47</v>
@@ -3087,10 +3086,10 @@
         <v>81</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -3105,15 +3104,15 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>48</v>
@@ -3128,10 +3127,10 @@
         <v>67</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -3146,7 +3145,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>14</v>
@@ -3154,7 +3153,7 @@
     </row>
     <row r="23" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>31</v>
@@ -3169,10 +3168,10 @@
         <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -3187,7 +3186,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>14</v>
@@ -3195,7 +3194,7 @@
     </row>
     <row r="24" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>32</v>
@@ -3210,10 +3209,10 @@
         <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -3228,18 +3227,18 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>64</v>
@@ -3251,10 +3250,10 @@
         <v>67</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -3269,18 +3268,18 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>64</v>
@@ -3292,10 +3291,10 @@
         <v>67</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -3310,18 +3309,18 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>64</v>
@@ -3333,10 +3332,10 @@
         <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -3351,18 +3350,18 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>64</v>
@@ -3374,10 +3373,10 @@
         <v>68</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -3392,30 +3391,33 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -3424,39 +3426,39 @@
         <v>12</v>
       </c>
       <c r="J29" s="1">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>67</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -3471,7 +3473,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>14</v>
@@ -3479,25 +3481,22 @@
     </row>
     <row r="31" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>66</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -3512,30 +3511,33 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>139</v>
+        <v>77</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -3550,18 +3552,18 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>64</v>
@@ -3573,10 +3575,10 @@
         <v>81</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -3591,18 +3593,18 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>64</v>
@@ -3611,13 +3613,13 @@
         <v>77</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -3632,33 +3634,33 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="221" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -3667,39 +3669,39 @@
         <v>12</v>
       </c>
       <c r="J35" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -3708,13 +3710,13 @@
         <v>12</v>
       </c>
       <c r="J36" s="1">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>14</v>
@@ -3722,10 +3724,10 @@
     </row>
     <row r="37" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>65</v>
@@ -3733,14 +3735,11 @@
       <c r="D37" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -3755,30 +3754,30 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>69</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>13</v>
@@ -3793,18 +3792,18 @@
         <v>10</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>64</v>
@@ -3813,10 +3812,10 @@
         <v>69</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>13</v>
@@ -3831,27 +3830,30 @@
         <v>10</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>53</v>
+        <v>442</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D40" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -3866,7 +3868,7 @@
         <v>10</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>14</v>
@@ -3874,22 +3876,25 @@
     </row>
     <row r="41" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>447</v>
+        <v>54</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>69</v>
+        <v>137</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>13</v>
@@ -3904,33 +3909,33 @@
         <v>10</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>140</v>
+        <v>451</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>13</v>
@@ -3945,33 +3950,30 @@
         <v>10</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>13</v>
@@ -3986,7 +3988,7 @@
         <v>10</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>14</v>
@@ -3994,22 +3996,22 @@
     </row>
     <row r="44" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>13</v>
@@ -4024,30 +4026,27 @@
         <v>10</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>13</v>
@@ -4062,27 +4061,27 @@
         <v>10</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>57</v>
+        <v>443</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>13</v>
@@ -4097,27 +4096,33 @@
         <v>10</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>448</v>
+        <v>38</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>13</v>
@@ -4132,7 +4137,7 @@
         <v>10</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>14</v>
@@ -4140,25 +4145,25 @@
     </row>
     <row r="48" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>38</v>
+        <v>444</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>13</v>
@@ -4173,33 +4178,33 @@
         <v>10</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>13</v>
@@ -4214,7 +4219,7 @@
         <v>10</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>14</v>
@@ -4222,25 +4227,19 @@
     </row>
     <row r="50" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>450</v>
+        <v>58</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>13</v>
@@ -4255,27 +4254,27 @@
         <v>10</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>13</v>
@@ -4290,27 +4289,30 @@
         <v>10</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>13</v>
@@ -4325,7 +4327,7 @@
         <v>10</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>14</v>
@@ -4333,10 +4335,10 @@
     </row>
     <row r="53" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>39</v>
+        <v>446</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>65</v>
@@ -4345,10 +4347,10 @@
         <v>78</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>13</v>
@@ -4363,30 +4365,27 @@
         <v>10</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>13</v>
@@ -4401,27 +4400,27 @@
         <v>10</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>452</v>
+        <v>60</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>13</v>
@@ -4436,27 +4435,27 @@
         <v>10</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>13</v>
@@ -4471,27 +4470,27 @@
         <v>10</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>13</v>
@@ -4506,27 +4505,27 @@
         <v>10</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>13</v>
@@ -4541,27 +4540,27 @@
         <v>10</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="204" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>63</v>
+        <v>448</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>13</v>
@@ -4576,44 +4575,9 @@
         <v>10</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="85" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J60" s="1">
-        <v>2020</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="M60" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4662,7 +4626,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -4677,10 +4641,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -4691,16 +4655,16 @@
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -4715,7 +4679,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -4723,19 +4687,19 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -4750,7 +4714,7 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -4758,19 +4722,19 @@
     </row>
     <row r="4" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -4785,7 +4749,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -4793,19 +4757,19 @@
     </row>
     <row r="5" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -4820,7 +4784,7 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -4828,19 +4792,19 @@
     </row>
     <row r="6" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -4855,7 +4819,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -4863,19 +4827,19 @@
     </row>
     <row r="7" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -4890,7 +4854,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -4898,19 +4862,19 @@
     </row>
     <row r="8" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -4925,7 +4889,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -4933,19 +4897,19 @@
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -4960,7 +4924,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -4968,19 +4932,19 @@
     </row>
     <row r="10" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -4995,7 +4959,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -5003,19 +4967,19 @@
     </row>
     <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -5030,7 +4994,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -5038,19 +5002,19 @@
     </row>
     <row r="12" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -5065,7 +5029,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -5073,19 +5037,19 @@
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -5100,7 +5064,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
@@ -5108,19 +5072,19 @@
     </row>
     <row r="14" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -5135,7 +5099,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
@@ -5143,19 +5107,19 @@
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -5170,7 +5134,7 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -5178,19 +5142,19 @@
     </row>
     <row r="16" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -5205,7 +5169,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -5213,19 +5177,19 @@
     </row>
     <row r="17" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -5240,7 +5204,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -5248,19 +5212,19 @@
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -5275,7 +5239,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -5283,19 +5247,19 @@
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -5310,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -5318,19 +5282,19 @@
     </row>
     <row r="20" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -5345,27 +5309,27 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -5380,7 +5344,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -5388,19 +5352,19 @@
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -5415,7 +5379,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -5423,19 +5387,19 @@
     </row>
     <row r="23" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -5450,7 +5414,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>16</v>
@@ -5458,19 +5422,19 @@
     </row>
     <row r="24" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -5485,7 +5449,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>16</v>
@@ -5493,19 +5457,19 @@
     </row>
     <row r="25" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -5520,7 +5484,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>16</v>
@@ -5528,19 +5492,19 @@
     </row>
     <row r="26" spans="1:13" ht="187" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -5555,7 +5519,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>16</v>
@@ -5563,19 +5527,19 @@
     </row>
     <row r="27" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -5590,7 +5554,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>16</v>
@@ -5598,19 +5562,19 @@
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -5625,7 +5589,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>16</v>
@@ -5633,19 +5597,19 @@
     </row>
     <row r="29" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -5660,7 +5624,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>16</v>
@@ -5668,19 +5632,19 @@
     </row>
     <row r="30" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -5695,7 +5659,7 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>16</v>
@@ -5703,19 +5667,19 @@
     </row>
     <row r="31" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -5730,7 +5694,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>16</v>
@@ -5785,7 +5749,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -5800,10 +5764,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -5814,7 +5778,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>64</v>
@@ -5823,7 +5787,7 @@
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -5838,7 +5802,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -5846,10 +5810,10 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>65</v>
@@ -5858,7 +5822,7 @@
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -5873,18 +5837,18 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>64</v>
@@ -5893,7 +5857,7 @@
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -5908,7 +5872,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -5916,10 +5880,10 @@
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>65</v>
@@ -5928,7 +5892,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -5943,18 +5907,18 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="187" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
@@ -5963,7 +5927,7 @@
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -5978,7 +5942,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -5986,10 +5950,10 @@
     </row>
     <row r="7" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>65</v>
@@ -5998,7 +5962,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -6013,7 +5977,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -6021,7 +5985,7 @@
     </row>
     <row r="8" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
@@ -6030,7 +5994,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -6045,7 +6009,7 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -6053,10 +6017,10 @@
     </row>
     <row r="9" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>64</v>
@@ -6065,7 +6029,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -6080,7 +6044,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -6088,10 +6052,10 @@
     </row>
     <row r="10" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>64</v>
@@ -6100,7 +6064,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -6115,18 +6079,18 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
@@ -6135,7 +6099,7 @@
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -6150,7 +6114,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
@@ -6158,10 +6122,10 @@
     </row>
     <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>65</v>
@@ -6170,7 +6134,7 @@
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -6185,18 +6149,18 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>64</v>
@@ -6205,7 +6169,7 @@
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -6220,18 +6184,18 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="187" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
@@ -6240,7 +6204,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -6255,18 +6219,18 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>65</v>
@@ -6275,7 +6239,7 @@
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -6290,18 +6254,18 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
@@ -6310,7 +6274,7 @@
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -6325,7 +6289,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
@@ -6333,10 +6297,10 @@
     </row>
     <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>65</v>
@@ -6345,7 +6309,7 @@
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -6360,18 +6324,18 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>64</v>
@@ -6380,7 +6344,7 @@
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -6395,7 +6359,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
@@ -6403,10 +6367,10 @@
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>65</v>
@@ -6415,7 +6379,7 @@
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -6430,18 +6394,18 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
@@ -6450,7 +6414,7 @@
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -6465,18 +6429,18 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>65</v>
@@ -6485,7 +6449,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -6500,18 +6464,18 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>64</v>
@@ -6520,7 +6484,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -6535,7 +6499,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -6543,10 +6507,10 @@
     </row>
     <row r="23" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>65</v>
@@ -6555,7 +6519,7 @@
         <v>40</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -6570,18 +6534,18 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>64</v>
@@ -6590,7 +6554,7 @@
         <v>40</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -6605,18 +6569,18 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>64</v>
@@ -6625,7 +6589,7 @@
         <v>40</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -6640,7 +6604,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>16</v>
@@ -6648,10 +6612,10 @@
     </row>
     <row r="26" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>65</v>
@@ -6660,7 +6624,7 @@
         <v>40</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -6675,18 +6639,18 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="255" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="204" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>64</v>
@@ -6695,7 +6659,7 @@
         <v>40</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -6710,7 +6674,7 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>16</v>
@@ -6718,10 +6682,10 @@
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
@@ -6730,7 +6694,7 @@
         <v>40</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -6745,18 +6709,18 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>64</v>
@@ -6765,7 +6729,7 @@
         <v>40</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -6780,7 +6744,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>16</v>
@@ -6788,10 +6752,10 @@
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>65</v>
@@ -6800,7 +6764,7 @@
         <v>40</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -6815,18 +6779,18 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
@@ -6835,7 +6799,7 @@
         <v>40</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -6850,18 +6814,18 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>65</v>
@@ -6870,7 +6834,7 @@
         <v>40</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -6885,18 +6849,18 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="221" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>64</v>
@@ -6905,7 +6869,7 @@
         <v>40</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -6920,18 +6884,18 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>64</v>
@@ -6940,7 +6904,7 @@
         <v>40</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -6955,7 +6919,7 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>16</v>
@@ -6963,10 +6927,10 @@
     </row>
     <row r="35" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>64</v>
@@ -6975,7 +6939,7 @@
         <v>40</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -6990,7 +6954,7 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>16</v>
@@ -6998,10 +6962,10 @@
     </row>
     <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>65</v>
@@ -7010,7 +6974,7 @@
         <v>40</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -7025,18 +6989,18 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>64</v>
@@ -7045,7 +7009,7 @@
         <v>40</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -7060,7 +7024,7 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>16</v>
@@ -7115,7 +7079,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -7130,10 +7094,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -7144,16 +7108,16 @@
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -7168,27 +7132,27 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -7203,27 +7167,27 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -7238,27 +7202,27 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -7273,27 +7237,27 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -7308,27 +7272,27 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -7343,27 +7307,27 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -7378,27 +7342,27 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -7413,27 +7377,27 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="248" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -7448,27 +7412,27 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -7483,27 +7447,27 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -7518,27 +7482,27 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -7553,27 +7517,27 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="204" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="272" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -7588,27 +7552,27 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -7623,27 +7587,27 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -7658,27 +7622,27 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -7693,27 +7657,27 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -7728,27 +7692,27 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -7763,27 +7727,27 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="204" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -7798,27 +7762,27 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -7833,27 +7797,27 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -7868,27 +7832,27 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>13</v>
@@ -7903,27 +7867,27 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="404" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="323" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>13</v>
@@ -7938,27 +7902,27 @@
         <v>10</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -7973,27 +7937,27 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="289" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="356" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>13</v>
@@ -8008,27 +7972,27 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>13</v>
@@ -8043,27 +8007,27 @@
         <v>10</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>13</v>
@@ -8078,27 +8042,27 @@
         <v>10</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>13</v>
@@ -8113,27 +8077,27 @@
         <v>10</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>13</v>
@@ -8148,27 +8112,27 @@
         <v>10</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="187" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>13</v>
@@ -8183,27 +8147,27 @@
         <v>10</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>13</v>
@@ -8218,27 +8182,27 @@
         <v>10</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="323" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>13</v>
@@ -8253,15 +8217,15 @@
         <v>10</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>39</v>
@@ -8270,10 +8234,10 @@
         <v>65</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>13</v>
@@ -8288,27 +8252,27 @@
         <v>10</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>13</v>
@@ -8323,27 +8287,27 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>13</v>
@@ -8358,27 +8322,27 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="153" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>13</v>
@@ -8393,27 +8357,27 @@
         <v>10</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>65</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>13</v>
@@ -8428,27 +8392,27 @@
         <v>10</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>13</v>
@@ -8463,27 +8427,27 @@
         <v>10</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>13</v>
@@ -8498,27 +8462,27 @@
         <v>10</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="170" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>13</v>
@@ -8533,10 +8497,10 @@
         <v>10</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -8585,7 +8549,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -8600,10 +8564,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -8614,13 +8578,22 @@
         <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -8635,24 +8608,33 @@
         <v>18</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -8667,7 +8649,7 @@
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
@@ -8675,16 +8657,19 @@
     </row>
     <row r="4" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -8699,24 +8684,27 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -8731,7 +8719,7 @@
         <v>18</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
@@ -8739,16 +8727,19 @@
     </row>
     <row r="6" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -8763,7 +8754,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -8771,16 +8762,19 @@
     </row>
     <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -8795,7 +8789,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -8803,16 +8797,19 @@
     </row>
     <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>423</v>
+        <v>449</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -8827,7 +8824,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -8835,16 +8832,19 @@
     </row>
     <row r="9" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -8859,7 +8859,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -8867,16 +8867,19 @@
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -8891,7 +8894,7 @@
         <v>18</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
@@ -8899,16 +8902,19 @@
     </row>
     <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -8923,24 +8929,27 @@
         <v>18</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -8955,7 +8964,7 @@
         <v>18</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -8963,16 +8972,19 @@
     </row>
     <row r="13" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -8987,24 +8999,27 @@
         <v>18</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -9019,24 +9034,27 @@
         <v>18</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -9051,7 +9069,7 @@
         <v>18</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -9059,16 +9077,19 @@
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -9083,24 +9104,27 @@
         <v>18</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -9115,24 +9139,27 @@
         <v>18</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="153" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -9147,24 +9174,27 @@
         <v>18</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -9179,7 +9209,7 @@
         <v>18</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
@@ -9187,16 +9217,19 @@
     </row>
     <row r="20" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -9211,24 +9244,27 @@
         <v>18</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -9243,7 +9279,7 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
@@ -9251,16 +9287,19 @@
     </row>
     <row r="22" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -9275,7 +9314,7 @@
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>
@@ -9327,7 +9366,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -9342,10 +9381,10 @@
         <v>4</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -9356,13 +9395,16 @@
         <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -9377,7 +9419,7 @@
         <v>18</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>16</v>
@@ -9385,16 +9427,19 @@
     </row>
     <row r="3" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -9409,24 +9454,27 @@
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
@@ -9441,7 +9489,7 @@
         <v>18</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>16</v>
@@ -9449,16 +9497,19 @@
     </row>
     <row r="5" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -9473,24 +9524,27 @@
         <v>18</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>13</v>
@@ -9505,7 +9559,7 @@
         <v>18</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>16</v>
@@ -9513,16 +9567,19 @@
     </row>
     <row r="7" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>13</v>
@@ -9537,7 +9594,7 @@
         <v>18</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>16</v>
@@ -9545,16 +9602,19 @@
     </row>
     <row r="8" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>13</v>
@@ -9569,7 +9629,7 @@
         <v>18</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>16</v>
@@ -9577,16 +9637,19 @@
     </row>
     <row r="9" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
@@ -9601,7 +9664,7 @@
         <v>18</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>16</v>
@@ -9609,16 +9672,19 @@
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>13</v>
@@ -9633,24 +9699,27 @@
         <v>18</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -9665,24 +9734,27 @@
         <v>18</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>13</v>
@@ -9697,7 +9769,7 @@
         <v>18</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>16</v>
@@ -9705,16 +9777,19 @@
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>13</v>
@@ -9729,24 +9804,27 @@
         <v>18</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>13</v>
@@ -9761,24 +9839,27 @@
         <v>18</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>13</v>
@@ -9793,7 +9874,7 @@
         <v>18</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>16</v>
@@ -9801,16 +9882,19 @@
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>13</v>
@@ -9825,24 +9909,27 @@
         <v>18</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>13</v>
@@ -9857,7 +9944,7 @@
         <v>18</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>16</v>
@@ -9865,16 +9952,19 @@
     </row>
     <row r="18" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>13</v>
@@ -9889,24 +9979,27 @@
         <v>18</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>13</v>
@@ -9921,24 +10014,27 @@
         <v>18</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="204" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>13</v>
@@ -9953,24 +10049,27 @@
         <v>18</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="170" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>13</v>
@@ -9985,24 +10084,27 @@
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>13</v>
@@ -10017,7 +10119,7 @@
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>16</v>

--- a/data/input/asics.xlsx
+++ b/data/input/asics.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11020"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845E7155-1F68-8541-B8A0-E822208DAF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0799B496-FD9E-8341-9532-6DAC07C781DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13460" yWindow="600" windowWidth="24940" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="461">
   <si>
     <t>ID</t>
   </si>
@@ -207,10 +207,6 @@
   </si>
   <si>
     <t>JPN20A03-04</t>
-  </si>
-  <si>
-    <t>To continue the production and supply of products in a timely and appropriate manner, we are also working to prepare for unexpected disruptions in the supply chain. Going forward, we will transform our business model under the keywords “digital” and “sustainable” based on relationships of trust with the
-various partners that make up the ASICS supply chain, enhancing our existing strengths to make them even stronger.</t>
   </si>
   <si>
     <t>JPN20A04-00</t>
@@ -570,85 +566,43 @@
     <t>Another of these insights is to do with new sports. Among these, starting this year ASICS will make a full-scale entry into the US markets in addition to Japan for skateboarding, whose competitive population is expected to grow in the future. Skateboarding is a sport that involves split-second skills and is the subject of a thriving area of digital analysis. By combining its technologies in many ways, ASICS will be able to create value that goes beyond the conventional provision of products, including in the area of facilities &amp; community digitally providing locations and communities for people to enjoy sports, and the area of analysis &amp; diagnosis involving the provision of analysis and diagnostic findings using data obtained from those activities. Beyond the fusion of sport and digital technologies, we also hope to develop the new world of e-sports. We also aim to further expand the scope of the C Project that has to date focused on middle and long distances in track and field in a serious attempt to reach the pinnacle of performance in short distance and sprinting categories as well. We have begun developing new products and signing deals with athletes, aiming to reach the summit together with athletes who have the ability to make the podium in international competition for track and field’s highest profile event, the 100-meter sprint. In Japan, the support culture of TEAM RED that was cultivated during the Tokyo 2020 Games and the SUNRISE RED attire worn by Japanese Olympic athletes will continue to be passed down in the future. We will weave a legacy for the next generation in terms of both products and branding to ensure the idea that “ASICS is associated with the Olympics and Paralympics” firmly takes root.</t>
   </si>
   <si>
-    <t>JPN21A002-00</t>
-  </si>
-  <si>
     <t>Towards medium and long-term growth</t>
   </si>
   <si>
-    <t>JPN21A002-01</t>
-  </si>
-  <si>
     <t>Switching to management based on digital technologies</t>
   </si>
   <si>
-    <t>JPN21A002-02</t>
-  </si>
-  <si>
     <t>In Mid-Term Plan 2023 formulated to achieve the long-term VISION 2030, ASICS has positioned digital strategy as one of its strategic goals. While continuing to emphasize the need to cash in on our existing businesses, we will seek to maximize efficiency gains and profitability across the supply chain with new business development and new business models with digital at their core.</t>
   </si>
   <si>
-    <t>JPN21A002-03</t>
-  </si>
-  <si>
     <t>Working from a base of more than 5.8 million members (as of February 28, 2022) on our free membership-based service OneASICSTM, we will organically link the smartphone-based exercise recording app RunkeeperTM used in about 250 countries and regions around the world with the Race Roster race sign-up platform mainly used in the US and Canada and the Register Now race sign-up platform in Australia. Together with these services, we will form a worldwide running ecosystem providing services to runners, including through Runmetrix, which uses sensor technologies to measure running in real time and provide coaching, and Shoe Finder, which recommends shoes that are best for each individual based on their running style and images of their feet taken with a smartphone. In addition, in 2021 we launched ASICS STEPNOTE, an app-based service that measures the size of small children’s feet and predicts their growth to recommend the right shoes, reflecting our efforts to also develop a kids ecosystem. To make this running ecosystem a reality, we will need to foster and instill an organizational culture that thinks of everything in digital terms. We will transform ASICS into a digitally-driven company by appointing human resources from the digital native generation and re-skilling employees.</t>
   </si>
   <si>
-    <t>JPN21A002-04</t>
-  </si>
-  <si>
     <t>Sustainability is the core of management</t>
   </si>
   <si>
-    <t>JPN21A002-05</t>
-  </si>
-  <si>
     <t>Another strategic goal declared in Mid-Term Plan 2023 is sustainability. Sport is a symbol of peace, and sports will not be possible unless a good global environment is preserved. As a sports-related manufacturer, ASICS sees protecting a global environment that enables sports to be synonymous with safeguarding its own survival as a business.</t>
   </si>
   <si>
-    <t>JPN21A002-06</t>
-  </si>
-  <si>
     <t>In terms of consideration for the environment, in 2019 ASICS was the first sports-related manufacturer in the world to indicate support for the recommendations of the Task Force on Climate-related Financial Disclosures (TCFD), and to achieve the goal of reducing our CO2 emissions by 63% compared with 2015 levels by the year 2030, we are pursuing the initiatives outlined below.</t>
   </si>
   <si>
-    <t>JPN21A002-07</t>
-  </si>
-  <si>
     <t>(1) We are shifting to 100% renewable energy usage at domestic operating sites and promoting a shift to renewable energies at contracted production factories. (2) We have promoted recycling-oriented production utilizing recycled materials for at least 90% of new shoe products, and are continuing efforts with the ultimate goal of using 100% recycled materials for polyester, a major material used in our products. (3) In terms of finance, we have issued Japan’s first sustainability-linked bonds in which CO2 emission credits are purchased based on the target achievement levels. Measures to combat climate change are more effective when companies cooperate with one another through teamwork instead of going it alone. Going forward, ASICS will continue to run at the head of the pack and lead the way with sustainable initiatives.</t>
   </si>
   <si>
-    <t>JPN21A002-08</t>
-  </si>
-  <si>
     <t>From the perspective of contributing to society, we will work harder to improve working environments for the many skilled workers involved with our shoe manufacturing processes in Vietnam, Indonesia, Cambodia and elsewhere. Since shoes feature many curves, there are many aspects to the manufacturing process that rely on skilled manual sewng work, and retaining skilled workers in these areas is extremely important for maintaining and improving production quality. We have been implementing human rights due diligence activities in our overseas supply chains for more than two decades, and have introduced internal reporting systems and developed mechanisms to conduct engagement surveys and other activities simultaneously on a global basis. Each year we conduct technical skills training for more than 60 of our primary, secondary and tertiary suppliers, and also continue efforts to enhance welfare benefits and offer higher wages than our competitors. While being interrupted by the COVID-19 pandemic, I usually visit our manufacturing factories once a year to speak with factory managers and check working  conditions on-site. To ensure that ASICS is the choice for multiple stakeholders, including employees and customers, sustainability is the core of management.</t>
   </si>
   <si>
-    <t>JPN21A002-09</t>
-  </si>
-  <si>
     <t>Digitally minded human resources are the subject of intense competition for recruitment. At ASICS, some 400 digitally-literate human resources collaborate organically in Boston (headquarters of ASICS Digital), Toronto (Digital Strategy Development Division) and Amsterdam (IT Headquarters) with a sense of speed and sensitivity to human rights, leading the way in fostering and enhancing the digital mindset of all employees</t>
   </si>
   <si>
-    <t>JPN21A002-10</t>
-  </si>
-  <si>
     <t>Making 2022 a breakthrough year!</t>
   </si>
   <si>
-    <t>JPN21A002-11</t>
-  </si>
-  <si>
     <t>In 2022, the uncertain management environment is ongoing, with the prolonged COVID-19 pandemic, Russia’s invasion of Ukraine and other developments. But on the starting line for ASICS is a solid foundation built through past reforms, and I believe that 2022 will be a breakthrough year for us. By “breakthrough” I don’t mean rapid growth as a result of something accidental; I envisage significant growth as a result of all our efforts to date.</t>
   </si>
   <si>
-    <t>JPN21A002-12</t>
-  </si>
-  <si>
     <t>As the world changes, so will the way sports are played, enjoyed and supported. ASICS will continue to pass down its founding philosophy of “a sound mind in a sound body (“Anima Sana In Corpore Sano”) and the “Sound Mind, Sound Body” brand tagline while providing products and services that are valuable to all sports enthusiasts and stakeholders involved with ASICS’ businesses through reforms consistent with the today’s digital revolution. As a member of top management, I promise that we will seize upon changes in the times and major opportunities, engage in sound and transparent management, and enhance corporate value sustainably in the long term.</t>
-  </si>
-  <si>
-    <t>JPN21A002-13</t>
   </si>
   <si>
     <t>I hope that all of our stakeholders will look forward to seeing the ASICS Group achieve significant growth through the actions we take in line with the strategies and policies we have set forth.</t>
@@ -1375,16 +1329,100 @@
   </si>
   <si>
     <t>president</t>
+  </si>
+  <si>
+    <t>Communicates ASICS’s brand philosophy, tagline, and brand identity. The promotion of the translated philosophy is a brand initiative, so MARKET is preferred over STRAT.</t>
+  </si>
+  <si>
+    <t>Reports a realized operational development: outsourced factories are expanding production capacity and complying with ASICS policies.</t>
+  </si>
+  <si>
+    <t>To continue the production and supply of products in a timely and appropriate manner, we are also working to prepare for unexpected disruptions in the supply chain. Going forward, we will transform our business model under the keywords “digital” and “sustainable” based on relationships of trust with the various partners that make up the ASICS supply chain, enhancing our existing strengths to make them even stronger.</t>
+  </si>
+  <si>
+    <t>The primary purpose is to communicate ASICS’s future business-model transformation through digital and sustainable capabilities and stronger supply-chain relationships. CHALL as a alternative because supply-chain disruptions motivate the strategy.</t>
+  </si>
+  <si>
+    <t>PEOPLE is an alternative because employees and workers are discussed, but the communication concerns external stakeholder responsibility rather than ASICS’s internal organization.</t>
+  </si>
+  <si>
+    <t>MARKET selected because “performance running” identifies the product category. STRAT is an alternative interpretation.</t>
+  </si>
+  <si>
+    <t>MARKET as the alternative because the paragraph also concerns METASPEED, athletes, product functionality, and competitive market share.</t>
+  </si>
+  <si>
+    <t>JPN21A02-00</t>
+  </si>
+  <si>
+    <t>STAKE because it focuses on Japan’s healthy-life-expectancy gap and the societal health benefit of ASICS’s initiatives.</t>
+  </si>
+  <si>
+    <t>CHALL primary because itidentifies geopolitical conflict and economic instability as risks to the operating environment. STAKE is an alternative because social peace and public conditions are discussed, but the main purpose is risk recognition.</t>
+  </si>
+  <si>
+    <t>STRAT primary because the passage sets future expansion plans and a sales target. MARKET is alternative because specific emerging markets are discussed. PERF is not used because no result has yet been achieved.</t>
+  </si>
+  <si>
+    <t>STRAT primary because it ommunicates ASICS’s global digital transformation. MARKET is an alternative because customers, marketing, products, and services are discussed.</t>
+  </si>
+  <si>
+    <t>STAKE primary because the passage centers on shareholder relations and capital-market expectations. STRAT alternative because shareholder reform is also presented as a future management direction.</t>
+  </si>
+  <si>
+    <t>JPN21A02-01</t>
+  </si>
+  <si>
+    <t>JPN21A02-02</t>
+  </si>
+  <si>
+    <t>JPN21A02-03</t>
+  </si>
+  <si>
+    <t>JPN21A02-04</t>
+  </si>
+  <si>
+    <t>JPN21A02-05</t>
+  </si>
+  <si>
+    <t>JPN21A02-06</t>
+  </si>
+  <si>
+    <t>JPN21A02-07</t>
+  </si>
+  <si>
+    <t>JPN21A02-08</t>
+  </si>
+  <si>
+    <t>JPN21A02-09</t>
+  </si>
+  <si>
+    <t>JPN21A02-10</t>
+  </si>
+  <si>
+    <t>JPN21A02-11</t>
+  </si>
+  <si>
+    <t>JPN21A02-12</t>
+  </si>
+  <si>
+    <t>JPN21A02-13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1786,7 +1824,7 @@
     <col min="7" max="11" width="13.5" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="131.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.33203125" customWidth="1"/>
     <col min="16" max="16" width="18.5" customWidth="1"/>
     <col min="17" max="23" width="13.5" customWidth="1"/>
@@ -1859,7 +1897,7 @@
         <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
@@ -1881,6 +1919,9 @@
       </c>
       <c r="M2" t="s">
         <v>25</v>
+      </c>
+      <c r="O2" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -1900,7 +1941,7 @@
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -1922,6 +1963,9 @@
       </c>
       <c r="M3" t="s">
         <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -1941,7 +1985,7 @@
         <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -1963,6 +2007,9 @@
       </c>
       <c r="M4" t="s">
         <v>25</v>
+      </c>
+      <c r="O4" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -1982,7 +2029,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -2004,6 +2051,9 @@
       </c>
       <c r="M5" t="s">
         <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -2023,7 +2073,7 @@
         <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
@@ -2045,6 +2095,9 @@
       </c>
       <c r="M6" t="s">
         <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -2064,7 +2117,7 @@
         <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G7" t="s">
         <v>20</v>
@@ -2086,6 +2139,9 @@
       </c>
       <c r="M7" t="s">
         <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -2105,7 +2161,7 @@
         <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
@@ -2127,6 +2183,9 @@
       </c>
       <c r="M8" t="s">
         <v>25</v>
+      </c>
+      <c r="O8" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -2146,7 +2205,7 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
@@ -2168,6 +2227,9 @@
       </c>
       <c r="M9" t="s">
         <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -2187,7 +2249,7 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G10" t="s">
         <v>20</v>
@@ -2209,6 +2271,9 @@
       </c>
       <c r="M10" t="s">
         <v>25</v>
+      </c>
+      <c r="O10" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
@@ -2222,13 +2287,13 @@
         <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G11" t="s">
         <v>20</v>
@@ -2250,6 +2315,12 @@
       </c>
       <c r="M11" t="s">
         <v>25</v>
+      </c>
+      <c r="N11" t="s">
+        <v>435</v>
+      </c>
+      <c r="O11" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -2269,7 +2340,7 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
@@ -2291,6 +2362,9 @@
       </c>
       <c r="M12" t="s">
         <v>25</v>
+      </c>
+      <c r="O12" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -2310,7 +2384,7 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G13" t="s">
         <v>20</v>
@@ -2332,6 +2406,9 @@
       </c>
       <c r="M13" t="s">
         <v>25</v>
+      </c>
+      <c r="O13" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -2351,7 +2428,7 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G14" t="s">
         <v>20</v>
@@ -2373,6 +2450,9 @@
       </c>
       <c r="M14" t="s">
         <v>25</v>
+      </c>
+      <c r="O14" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -2392,7 +2472,7 @@
         <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
@@ -2414,6 +2494,9 @@
       </c>
       <c r="M15" t="s">
         <v>25</v>
+      </c>
+      <c r="O15" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -2433,7 +2516,7 @@
         <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
@@ -2456,8 +2539,11 @@
       <c r="M16" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O16" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -2468,13 +2554,13 @@
         <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G17" t="s">
         <v>20</v>
@@ -2497,13 +2583,19 @@
       <c r="M17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N17" t="s">
+        <v>436</v>
+      </c>
+      <c r="O17" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>437</v>
       </c>
       <c r="C18" t="s">
         <v>35</v>
@@ -2512,10 +2604,10 @@
         <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G18" t="s">
         <v>20</v>
@@ -2538,13 +2630,22 @@
       <c r="M18" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N18" t="s">
+        <v>438</v>
+      </c>
+      <c r="O18" t="s">
+        <v>23</v>
+      </c>
+      <c r="P18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
         <v>65</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
@@ -2556,7 +2657,7 @@
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G19" t="s">
         <v>20</v>
@@ -2579,25 +2680,28 @@
       <c r="M19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O19" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
         <v>67</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G20" t="s">
         <v>20</v>
@@ -2620,25 +2724,28 @@
       <c r="M20" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O20" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
         <v>70</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" t="s">
         <v>71</v>
       </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" t="s">
-        <v>72</v>
-      </c>
       <c r="F21" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G21" t="s">
         <v>20</v>
@@ -2661,25 +2768,28 @@
       <c r="M21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O21" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
         <v>73</v>
       </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
       <c r="C22" t="s">
         <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G22" t="s">
         <v>20</v>
@@ -2702,13 +2812,16 @@
       <c r="M22" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O22" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
         <v>75</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
@@ -2720,7 +2833,7 @@
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G23" t="s">
         <v>20</v>
@@ -2743,13 +2856,16 @@
       <c r="M23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O23" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
         <v>77</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
       </c>
       <c r="C24" t="s">
         <v>28</v>
@@ -2761,7 +2877,7 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G24" t="s">
         <v>20</v>
@@ -2784,13 +2900,16 @@
       <c r="M24" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O24" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
         <v>79</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
       </c>
       <c r="C25" t="s">
         <v>35</v>
@@ -2802,7 +2921,7 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G25" t="s">
         <v>20</v>
@@ -2825,13 +2944,16 @@
       <c r="M25" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O25" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
         <v>81</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
       </c>
       <c r="C26" t="s">
         <v>35</v>
@@ -2843,7 +2965,7 @@
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G26" t="s">
         <v>20</v>
@@ -2866,13 +2988,16 @@
       <c r="M26" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O26" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
         <v>83</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
       </c>
       <c r="C27" t="s">
         <v>35</v>
@@ -2881,10 +3006,10 @@
         <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G27" t="s">
         <v>20</v>
@@ -2907,13 +3032,16 @@
       <c r="M27" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O27" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s">
         <v>85</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
       </c>
       <c r="C28" t="s">
         <v>35</v>
@@ -2925,7 +3053,7 @@
         <v>32</v>
       </c>
       <c r="F28" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G28" t="s">
         <v>20</v>
@@ -2948,13 +3076,16 @@
       <c r="M28" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O28" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
         <v>87</v>
-      </c>
-      <c r="B29" t="s">
-        <v>88</v>
       </c>
       <c r="C29" t="s">
         <v>35</v>
@@ -2966,7 +3097,7 @@
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G29" t="s">
         <v>20</v>
@@ -2989,13 +3120,16 @@
       <c r="M29" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O29" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="s">
         <v>89</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
       </c>
       <c r="C30" t="s">
         <v>28</v>
@@ -3007,7 +3141,7 @@
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G30" t="s">
         <v>20</v>
@@ -3030,13 +3164,16 @@
       <c r="M30" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O30" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
         <v>91</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
       </c>
       <c r="C31" t="s">
         <v>28</v>
@@ -3048,7 +3185,7 @@
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G31" t="s">
         <v>20</v>
@@ -3071,13 +3208,16 @@
       <c r="M31" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O31" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
         <v>93</v>
-      </c>
-      <c r="B32" t="s">
-        <v>94</v>
       </c>
       <c r="C32" t="s">
         <v>35</v>
@@ -3086,10 +3226,10 @@
         <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F32" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G32" t="s">
         <v>20</v>
@@ -3112,13 +3252,16 @@
       <c r="M32" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O32" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
         <v>95</v>
-      </c>
-      <c r="B33" t="s">
-        <v>96</v>
       </c>
       <c r="C33" t="s">
         <v>35</v>
@@ -3127,10 +3270,10 @@
         <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F33" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G33" t="s">
         <v>20</v>
@@ -3153,13 +3296,16 @@
       <c r="M33" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O33" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
         <v>97</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
       </c>
       <c r="C34" t="s">
         <v>35</v>
@@ -3171,7 +3317,7 @@
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G34" t="s">
         <v>20</v>
@@ -3194,13 +3340,16 @@
       <c r="M34" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O34" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
         <v>99</v>
-      </c>
-      <c r="B35" t="s">
-        <v>100</v>
       </c>
       <c r="C35" t="s">
         <v>35</v>
@@ -3212,7 +3361,7 @@
         <v>32</v>
       </c>
       <c r="F35" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G35" t="s">
         <v>20</v>
@@ -3235,13 +3384,16 @@
       <c r="M35" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O35" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
         <v>101</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -3253,7 +3405,7 @@
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G36" t="s">
         <v>20</v>
@@ -3276,13 +3428,16 @@
       <c r="M36" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O36" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" t="s">
         <v>103</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -3294,7 +3449,7 @@
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G37" t="s">
         <v>20</v>
@@ -3317,13 +3472,16 @@
       <c r="M37" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O37" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" t="s">
         <v>105</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
       </c>
       <c r="C38" t="s">
         <v>35</v>
@@ -3335,7 +3493,7 @@
         <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G38" t="s">
         <v>20</v>
@@ -3358,13 +3516,16 @@
       <c r="M38" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O38" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
         <v>107</v>
-      </c>
-      <c r="B39" t="s">
-        <v>108</v>
       </c>
       <c r="C39" t="s">
         <v>35</v>
@@ -3376,7 +3537,7 @@
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G39" t="s">
         <v>20</v>
@@ -3399,13 +3560,16 @@
       <c r="M39" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O39" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" t="s">
         <v>109</v>
-      </c>
-      <c r="B40" t="s">
-        <v>110</v>
       </c>
       <c r="C40" t="s">
         <v>35</v>
@@ -3417,7 +3581,7 @@
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G40" t="s">
         <v>20</v>
@@ -3440,13 +3604,16 @@
       <c r="M40" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O40" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" t="s">
         <v>111</v>
-      </c>
-      <c r="B41" t="s">
-        <v>112</v>
       </c>
       <c r="C41" t="s">
         <v>35</v>
@@ -3455,10 +3622,10 @@
         <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F41" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G41" t="s">
         <v>20</v>
@@ -3481,13 +3648,16 @@
       <c r="M41" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O41" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" t="s">
         <v>113</v>
-      </c>
-      <c r="B42" t="s">
-        <v>114</v>
       </c>
       <c r="C42" t="s">
         <v>35</v>
@@ -3499,7 +3669,7 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G42" t="s">
         <v>20</v>
@@ -3522,13 +3692,16 @@
       <c r="M42" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O42" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
         <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -3540,7 +3713,7 @@
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G43" t="s">
         <v>20</v>
@@ -3563,13 +3736,16 @@
       <c r="M43" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O43" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>116</v>
+      </c>
+      <c r="B44" t="s">
         <v>117</v>
-      </c>
-      <c r="B44" t="s">
-        <v>118</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
@@ -3581,7 +3757,7 @@
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G44" t="s">
         <v>20</v>
@@ -3604,13 +3780,16 @@
       <c r="M44" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O44" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" t="s">
         <v>119</v>
-      </c>
-      <c r="B45" t="s">
-        <v>120</v>
       </c>
       <c r="C45" t="s">
         <v>35</v>
@@ -3622,7 +3801,7 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G45" t="s">
         <v>20</v>
@@ -3645,13 +3824,16 @@
       <c r="M45" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O45" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" t="s">
         <v>121</v>
-      </c>
-      <c r="B46" t="s">
-        <v>122</v>
       </c>
       <c r="C46" t="s">
         <v>35</v>
@@ -3660,10 +3842,10 @@
         <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F46" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G46" t="s">
         <v>20</v>
@@ -3686,25 +3868,28 @@
       <c r="M46" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O46" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" t="s">
         <v>123</v>
-      </c>
-      <c r="B47" t="s">
-        <v>124</v>
       </c>
       <c r="C47" t="s">
         <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G47" t="s">
         <v>20</v>
@@ -3727,25 +3912,28 @@
       <c r="M47" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O47" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" t="s">
         <v>125</v>
-      </c>
-      <c r="B48" t="s">
-        <v>126</v>
       </c>
       <c r="C48" t="s">
         <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G48" t="s">
         <v>20</v>
@@ -3768,25 +3956,28 @@
       <c r="M48" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O48" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" t="s">
         <v>127</v>
       </c>
-      <c r="B49" t="s">
-        <v>128</v>
-      </c>
       <c r="C49" t="s">
         <v>35</v>
       </c>
       <c r="D49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F49" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G49" t="s">
         <v>20</v>
@@ -3809,13 +4000,16 @@
       <c r="M49" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O49" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" t="s">
         <v>129</v>
-      </c>
-      <c r="B50" t="s">
-        <v>130</v>
       </c>
       <c r="C50" t="s">
         <v>35</v>
@@ -3827,7 +4021,7 @@
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G50" t="s">
         <v>20</v>
@@ -3850,25 +4044,28 @@
       <c r="M50" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O50" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>130</v>
+      </c>
+      <c r="B51" t="s">
         <v>131</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" t="s">
         <v>132</v>
-      </c>
-      <c r="C51" t="s">
-        <v>35</v>
-      </c>
-      <c r="D51" t="s">
-        <v>133</v>
       </c>
       <c r="E51" t="s">
         <v>32</v>
       </c>
       <c r="F51" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G51" t="s">
         <v>20</v>
@@ -3891,13 +4088,16 @@
       <c r="M51" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O51" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>133</v>
+      </c>
+      <c r="B52" t="s">
         <v>134</v>
-      </c>
-      <c r="B52" t="s">
-        <v>135</v>
       </c>
       <c r="C52" t="s">
         <v>28</v>
@@ -3909,7 +4109,7 @@
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G52" t="s">
         <v>20</v>
@@ -3932,13 +4132,16 @@
       <c r="M52" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O52" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>135</v>
+      </c>
+      <c r="B53" t="s">
         <v>136</v>
-      </c>
-      <c r="B53" t="s">
-        <v>137</v>
       </c>
       <c r="C53" t="s">
         <v>28</v>
@@ -3950,7 +4153,7 @@
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G53" t="s">
         <v>20</v>
@@ -3973,13 +4176,16 @@
       <c r="M53" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O53" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>137</v>
+      </c>
+      <c r="B54" t="s">
         <v>138</v>
-      </c>
-      <c r="B54" t="s">
-        <v>139</v>
       </c>
       <c r="C54" t="s">
         <v>35</v>
@@ -3991,7 +4197,7 @@
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G54" t="s">
         <v>20</v>
@@ -4014,13 +4220,16 @@
       <c r="M54" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O54" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" t="s">
         <v>140</v>
-      </c>
-      <c r="B55" t="s">
-        <v>141</v>
       </c>
       <c r="C55" t="s">
         <v>35</v>
@@ -4032,7 +4241,7 @@
         <v>32</v>
       </c>
       <c r="F55" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G55" t="s">
         <v>20</v>
@@ -4055,13 +4264,16 @@
       <c r="M55" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O55" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" t="s">
         <v>142</v>
-      </c>
-      <c r="B56" t="s">
-        <v>143</v>
       </c>
       <c r="C56" t="s">
         <v>35</v>
@@ -4073,7 +4285,7 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G56" t="s">
         <v>20</v>
@@ -4096,25 +4308,28 @@
       <c r="M56" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O56" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>143</v>
+      </c>
+      <c r="B57" t="s">
         <v>144</v>
       </c>
-      <c r="B57" t="s">
-        <v>145</v>
-      </c>
       <c r="C57" t="s">
         <v>35</v>
       </c>
       <c r="D57" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G57" t="s">
         <v>20</v>
@@ -4137,25 +4352,34 @@
       <c r="M57" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N57" t="s">
+        <v>439</v>
+      </c>
+      <c r="O57" t="s">
+        <v>23</v>
+      </c>
+      <c r="P57" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" t="s">
         <v>146</v>
       </c>
-      <c r="B58" t="s">
-        <v>147</v>
-      </c>
       <c r="C58" t="s">
         <v>35</v>
       </c>
       <c r="D58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G58" t="s">
         <v>20</v>
@@ -4178,13 +4402,16 @@
       <c r="M58" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O58" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>147</v>
+      </c>
+      <c r="B59" t="s">
         <v>148</v>
-      </c>
-      <c r="B59" t="s">
-        <v>149</v>
       </c>
       <c r="C59" t="s">
         <v>35</v>
@@ -4196,7 +4423,7 @@
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G59" t="s">
         <v>20</v>
@@ -4219,13 +4446,16 @@
       <c r="M59" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O59" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s">
         <v>150</v>
-      </c>
-      <c r="B60" t="s">
-        <v>151</v>
       </c>
       <c r="C60" t="s">
         <v>28</v>
@@ -4237,7 +4467,7 @@
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G60" t="s">
         <v>20</v>
@@ -4258,15 +4488,18 @@
         <v>24</v>
       </c>
       <c r="M60" t="s">
+        <v>151</v>
+      </c>
+      <c r="O60" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>153</v>
-      </c>
-      <c r="B61" t="s">
-        <v>154</v>
       </c>
       <c r="C61" t="s">
         <v>28</v>
@@ -4278,7 +4511,7 @@
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G61" t="s">
         <v>20</v>
@@ -4299,15 +4532,18 @@
         <v>24</v>
       </c>
       <c r="M61" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O61" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" t="s">
         <v>155</v>
-      </c>
-      <c r="B62" t="s">
-        <v>156</v>
       </c>
       <c r="C62" t="s">
         <v>28</v>
@@ -4316,10 +4552,10 @@
         <v>49</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F62" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G62" t="s">
         <v>20</v>
@@ -4340,15 +4576,18 @@
         <v>24</v>
       </c>
       <c r="M62" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O62" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" t="s">
         <v>157</v>
-      </c>
-      <c r="B63" t="s">
-        <v>158</v>
       </c>
       <c r="C63" t="s">
         <v>35</v>
@@ -4360,7 +4599,7 @@
         <v>32</v>
       </c>
       <c r="F63" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G63" t="s">
         <v>20</v>
@@ -4381,15 +4620,18 @@
         <v>24</v>
       </c>
       <c r="M63" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O63" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" t="s">
         <v>159</v>
-      </c>
-      <c r="B64" t="s">
-        <v>160</v>
       </c>
       <c r="C64" t="s">
         <v>28</v>
@@ -4401,7 +4643,7 @@
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G64" t="s">
         <v>20</v>
@@ -4422,27 +4664,30 @@
         <v>24</v>
       </c>
       <c r="M64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O64" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B65" t="s">
         <v>161</v>
       </c>
-      <c r="B65" t="s">
-        <v>162</v>
-      </c>
       <c r="C65" t="s">
         <v>35</v>
       </c>
       <c r="D65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G65" t="s">
         <v>20</v>
@@ -4463,27 +4708,30 @@
         <v>24</v>
       </c>
       <c r="M65" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O65" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>162</v>
+      </c>
+      <c r="B66" t="s">
         <v>163</v>
       </c>
-      <c r="B66" t="s">
-        <v>164</v>
-      </c>
       <c r="C66" t="s">
         <v>35</v>
       </c>
       <c r="D66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F66" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G66" t="s">
         <v>20</v>
@@ -4504,27 +4752,30 @@
         <v>24</v>
       </c>
       <c r="M66" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O66" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B67" t="s">
         <v>165</v>
-      </c>
-      <c r="B67" t="s">
-        <v>166</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E67" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G67" t="s">
         <v>20</v>
@@ -4545,15 +4796,24 @@
         <v>24</v>
       </c>
       <c r="M67" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="N67" t="s">
+        <v>440</v>
+      </c>
+      <c r="O67" t="s">
+        <v>23</v>
+      </c>
+      <c r="P67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>166</v>
+      </c>
+      <c r="B68" t="s">
         <v>167</v>
-      </c>
-      <c r="B68" t="s">
-        <v>168</v>
       </c>
       <c r="C68" t="s">
         <v>35</v>
@@ -4565,7 +4825,7 @@
         <v>32</v>
       </c>
       <c r="F68" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G68" t="s">
         <v>20</v>
@@ -4586,15 +4846,18 @@
         <v>24</v>
       </c>
       <c r="M68" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O68" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>168</v>
+      </c>
+      <c r="B69" t="s">
         <v>169</v>
-      </c>
-      <c r="B69" t="s">
-        <v>170</v>
       </c>
       <c r="C69" t="s">
         <v>28</v>
@@ -4606,7 +4869,7 @@
         <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G69" t="s">
         <v>20</v>
@@ -4627,15 +4890,18 @@
         <v>24</v>
       </c>
       <c r="M69" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O69" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" t="s">
         <v>171</v>
-      </c>
-      <c r="B70" t="s">
-        <v>172</v>
       </c>
       <c r="C70" t="s">
         <v>35</v>
@@ -4647,7 +4913,7 @@
         <v>32</v>
       </c>
       <c r="F70" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G70" t="s">
         <v>20</v>
@@ -4668,27 +4934,36 @@
         <v>24</v>
       </c>
       <c r="M70" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="N70" t="s">
+        <v>441</v>
+      </c>
+      <c r="O70" t="s">
+        <v>23</v>
+      </c>
+      <c r="P70" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71" t="s">
         <v>173</v>
-      </c>
-      <c r="B71" t="s">
-        <v>174</v>
       </c>
       <c r="C71" t="s">
         <v>28</v>
       </c>
       <c r="D71" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G71" t="s">
         <v>20</v>
@@ -4709,15 +4984,18 @@
         <v>24</v>
       </c>
       <c r="M71" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O71" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>174</v>
+      </c>
+      <c r="B72" t="s">
         <v>175</v>
-      </c>
-      <c r="B72" t="s">
-        <v>176</v>
       </c>
       <c r="C72" t="s">
         <v>35</v>
@@ -4729,7 +5007,7 @@
         <v>32</v>
       </c>
       <c r="F72" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G72" t="s">
         <v>20</v>
@@ -4750,15 +5028,18 @@
         <v>24</v>
       </c>
       <c r="M72" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O72" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>176</v>
+      </c>
+      <c r="B73" t="s">
         <v>177</v>
-      </c>
-      <c r="B73" t="s">
-        <v>178</v>
       </c>
       <c r="C73" t="s">
         <v>28</v>
@@ -4770,7 +5051,7 @@
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G73" t="s">
         <v>20</v>
@@ -4791,15 +5072,18 @@
         <v>24</v>
       </c>
       <c r="M73" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O73" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>178</v>
+      </c>
+      <c r="B74" t="s">
         <v>179</v>
-      </c>
-      <c r="B74" t="s">
-        <v>180</v>
       </c>
       <c r="C74" t="s">
         <v>35</v>
@@ -4811,7 +5095,7 @@
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G74" t="s">
         <v>20</v>
@@ -4832,15 +5116,18 @@
         <v>24</v>
       </c>
       <c r="M74" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O74" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>180</v>
+      </c>
+      <c r="B75" t="s">
         <v>181</v>
-      </c>
-      <c r="B75" t="s">
-        <v>182</v>
       </c>
       <c r="C75" t="s">
         <v>35</v>
@@ -4852,7 +5139,7 @@
         <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G75" t="s">
         <v>20</v>
@@ -4873,15 +5160,18 @@
         <v>24</v>
       </c>
       <c r="M75" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O75" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>183</v>
+        <v>442</v>
       </c>
       <c r="B76" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C76" t="s">
         <v>28</v>
@@ -4893,7 +5183,7 @@
         <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G76" t="s">
         <v>20</v>
@@ -4914,15 +5204,18 @@
         <v>24</v>
       </c>
       <c r="M76" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O76" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C77" t="s">
         <v>28</v>
@@ -4934,7 +5227,7 @@
         <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G77" t="s">
         <v>20</v>
@@ -4955,15 +5248,18 @@
         <v>24</v>
       </c>
       <c r="M77" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O77" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>187</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C78" t="s">
         <v>35</v>
@@ -4975,7 +5271,7 @@
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G78" t="s">
         <v>20</v>
@@ -4996,15 +5292,18 @@
         <v>24</v>
       </c>
       <c r="M78" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O78" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>189</v>
+        <v>450</v>
       </c>
       <c r="B79" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C79" t="s">
         <v>35</v>
@@ -5016,7 +5315,7 @@
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G79" t="s">
         <v>20</v>
@@ -5037,15 +5336,18 @@
         <v>24</v>
       </c>
       <c r="M79" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O79" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>191</v>
+        <v>451</v>
       </c>
       <c r="B80" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C80" t="s">
         <v>28</v>
@@ -5057,7 +5359,7 @@
         <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G80" t="s">
         <v>20</v>
@@ -5078,15 +5380,18 @@
         <v>24</v>
       </c>
       <c r="M80" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O80" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>193</v>
+        <v>452</v>
       </c>
       <c r="B81" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C81" t="s">
         <v>35</v>
@@ -5098,7 +5403,7 @@
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G81" t="s">
         <v>20</v>
@@ -5119,15 +5424,18 @@
         <v>24</v>
       </c>
       <c r="M81" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O81" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>195</v>
+        <v>453</v>
       </c>
       <c r="B82" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C82" t="s">
         <v>35</v>
@@ -5139,7 +5447,7 @@
         <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G82" t="s">
         <v>20</v>
@@ -5160,15 +5468,18 @@
         <v>24</v>
       </c>
       <c r="M82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O82" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>197</v>
+        <v>454</v>
       </c>
       <c r="B83" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C83" t="s">
         <v>35</v>
@@ -5180,7 +5491,7 @@
         <v>32</v>
       </c>
       <c r="F83" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G83" t="s">
         <v>20</v>
@@ -5201,27 +5512,30 @@
         <v>24</v>
       </c>
       <c r="M83" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O83" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>199</v>
+        <v>455</v>
       </c>
       <c r="B84" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C84" t="s">
         <v>35</v>
       </c>
       <c r="D84" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E84" t="s">
         <v>32</v>
       </c>
       <c r="F84" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G84" t="s">
         <v>20</v>
@@ -5242,27 +5556,30 @@
         <v>24</v>
       </c>
       <c r="M84" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O84" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>456</v>
       </c>
       <c r="B85" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C85" t="s">
         <v>35</v>
       </c>
       <c r="D85" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E85" t="s">
         <v>32</v>
       </c>
       <c r="F85" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G85" t="s">
         <v>20</v>
@@ -5283,15 +5600,18 @@
         <v>24</v>
       </c>
       <c r="M85" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O85" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>203</v>
+        <v>457</v>
       </c>
       <c r="B86" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C86" t="s">
         <v>28</v>
@@ -5303,7 +5623,7 @@
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G86" t="s">
         <v>20</v>
@@ -5324,15 +5644,18 @@
         <v>24</v>
       </c>
       <c r="M86" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O86" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>205</v>
+        <v>458</v>
       </c>
       <c r="B87" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C87" t="s">
         <v>35</v>
@@ -5344,7 +5667,7 @@
         <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G87" t="s">
         <v>20</v>
@@ -5365,15 +5688,18 @@
         <v>24</v>
       </c>
       <c r="M87" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O87" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>207</v>
+        <v>459</v>
       </c>
       <c r="B88" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C88" t="s">
         <v>35</v>
@@ -5385,7 +5711,7 @@
         <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G88" t="s">
         <v>20</v>
@@ -5406,15 +5732,18 @@
         <v>24</v>
       </c>
       <c r="M88" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O88" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>209</v>
+        <v>460</v>
       </c>
       <c r="B89" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C89" t="s">
         <v>35</v>
@@ -5426,7 +5755,7 @@
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G89" t="s">
         <v>20</v>
@@ -5447,15 +5776,18 @@
         <v>24</v>
       </c>
       <c r="M89" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O89" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="B90" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C90" t="s">
         <v>35</v>
@@ -5467,7 +5799,7 @@
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G90" t="s">
         <v>20</v>
@@ -5488,15 +5820,18 @@
         <v>24</v>
       </c>
       <c r="M90" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O90" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B91" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C91" t="s">
         <v>28</v>
@@ -5508,7 +5843,7 @@
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G91" t="s">
         <v>20</v>
@@ -5529,15 +5864,18 @@
         <v>24</v>
       </c>
       <c r="M91" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O91" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B92" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="C92" t="s">
         <v>35</v>
@@ -5549,7 +5887,7 @@
         <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G92" t="s">
         <v>20</v>
@@ -5570,15 +5908,18 @@
         <v>24</v>
       </c>
       <c r="M92" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O92" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B93" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C93" t="s">
         <v>28</v>
@@ -5590,7 +5931,7 @@
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G93" t="s">
         <v>20</v>
@@ -5611,15 +5952,18 @@
         <v>24</v>
       </c>
       <c r="M93" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O93" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B94" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C94" t="s">
         <v>35</v>
@@ -5631,7 +5975,7 @@
         <v>32</v>
       </c>
       <c r="F94" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G94" t="s">
         <v>20</v>
@@ -5652,27 +5996,30 @@
         <v>24</v>
       </c>
       <c r="M94" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O94" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B95" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C95" t="s">
         <v>28</v>
       </c>
       <c r="D95" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G95" t="s">
         <v>20</v>
@@ -5693,15 +6040,21 @@
         <v>24</v>
       </c>
       <c r="M95" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="N95" t="s">
+        <v>443</v>
+      </c>
+      <c r="O95" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B96" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C96" t="s">
         <v>35</v>
@@ -5713,7 +6066,7 @@
         <v>19</v>
       </c>
       <c r="F96" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G96" t="s">
         <v>20</v>
@@ -5734,15 +6087,18 @@
         <v>24</v>
       </c>
       <c r="M96" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O96" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B97" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C97" t="s">
         <v>35</v>
@@ -5754,7 +6110,7 @@
         <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G97" t="s">
         <v>20</v>
@@ -5775,15 +6131,18 @@
         <v>24</v>
       </c>
       <c r="M97" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O97" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B98" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C98" t="s">
         <v>35</v>
@@ -5795,7 +6154,7 @@
         <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G98" t="s">
         <v>20</v>
@@ -5816,27 +6175,30 @@
         <v>24</v>
       </c>
       <c r="M98" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O98" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B99" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C99" t="s">
         <v>35</v>
       </c>
       <c r="D99" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E99" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F99" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G99" t="s">
         <v>20</v>
@@ -5857,15 +6219,24 @@
         <v>24</v>
       </c>
       <c r="M99" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="N99" t="s">
+        <v>444</v>
+      </c>
+      <c r="O99" t="s">
+        <v>23</v>
+      </c>
+      <c r="P99" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B100" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C100" t="s">
         <v>28</v>
@@ -5877,7 +6248,7 @@
         <v>19</v>
       </c>
       <c r="F100" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G100" t="s">
         <v>20</v>
@@ -5898,15 +6269,18 @@
         <v>24</v>
       </c>
       <c r="M100" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O100" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B101" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C101" t="s">
         <v>35</v>
@@ -5918,7 +6292,7 @@
         <v>19</v>
       </c>
       <c r="F101" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G101" t="s">
         <v>20</v>
@@ -5939,15 +6313,18 @@
         <v>24</v>
       </c>
       <c r="M101" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O101" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="B102" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C102" t="s">
         <v>35</v>
@@ -5959,7 +6336,7 @@
         <v>32</v>
       </c>
       <c r="F102" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G102" t="s">
         <v>20</v>
@@ -5980,27 +6357,30 @@
         <v>24</v>
       </c>
       <c r="M102" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O102" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B103" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C103" t="s">
         <v>28</v>
       </c>
       <c r="D103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E103" t="s">
         <v>32</v>
       </c>
       <c r="F103" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G103" t="s">
         <v>20</v>
@@ -6021,27 +6401,30 @@
         <v>24</v>
       </c>
       <c r="M103" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O103" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B104" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C104" t="s">
         <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E104" t="s">
         <v>32</v>
       </c>
       <c r="F104" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G104" t="s">
         <v>20</v>
@@ -6062,15 +6445,18 @@
         <v>24</v>
       </c>
       <c r="M104" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O104" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="B105" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C105" t="s">
         <v>28</v>
@@ -6082,7 +6468,7 @@
         <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G105" t="s">
         <v>20</v>
@@ -6103,15 +6489,18 @@
         <v>24</v>
       </c>
       <c r="M105" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O105" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B106" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C106" t="s">
         <v>35</v>
@@ -6123,7 +6512,7 @@
         <v>32</v>
       </c>
       <c r="F106" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G106" t="s">
         <v>20</v>
@@ -6144,15 +6533,18 @@
         <v>24</v>
       </c>
       <c r="M106" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O106" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="B107" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C107" t="s">
         <v>28</v>
@@ -6164,7 +6556,7 @@
         <v>19</v>
       </c>
       <c r="F107" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G107" t="s">
         <v>20</v>
@@ -6185,15 +6577,18 @@
         <v>24</v>
       </c>
       <c r="M107" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O107" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B108" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C108" t="s">
         <v>35</v>
@@ -6205,7 +6600,7 @@
         <v>32</v>
       </c>
       <c r="F108" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G108" t="s">
         <v>20</v>
@@ -6226,15 +6621,18 @@
         <v>24</v>
       </c>
       <c r="M108" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O108" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B109" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C109" t="s">
         <v>28</v>
@@ -6246,7 +6644,7 @@
         <v>32</v>
       </c>
       <c r="F109" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G109" t="s">
         <v>20</v>
@@ -6267,15 +6665,18 @@
         <v>24</v>
       </c>
       <c r="M109" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O109" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B110" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="C110" t="s">
         <v>35</v>
@@ -6287,7 +6688,7 @@
         <v>32</v>
       </c>
       <c r="F110" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G110" t="s">
         <v>20</v>
@@ -6308,15 +6709,18 @@
         <v>24</v>
       </c>
       <c r="M110" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O110" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="B111" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C111" t="s">
         <v>28</v>
@@ -6328,7 +6732,7 @@
         <v>19</v>
       </c>
       <c r="F111" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G111" t="s">
         <v>20</v>
@@ -6349,15 +6753,18 @@
         <v>24</v>
       </c>
       <c r="M111" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O111" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="B112" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C112" t="s">
         <v>35</v>
@@ -6369,7 +6776,7 @@
         <v>32</v>
       </c>
       <c r="F112" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G112" t="s">
         <v>20</v>
@@ -6390,27 +6797,30 @@
         <v>24</v>
       </c>
       <c r="M112" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O112" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B113" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="C113" t="s">
         <v>35</v>
       </c>
       <c r="D113" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E113" t="s">
         <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G113" t="s">
         <v>20</v>
@@ -6431,27 +6841,30 @@
         <v>24</v>
       </c>
       <c r="M113" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O113" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="B114" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="C114" t="s">
         <v>28</v>
       </c>
       <c r="D114" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E114" t="s">
         <v>19</v>
       </c>
       <c r="F114" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G114" t="s">
         <v>20</v>
@@ -6472,27 +6885,30 @@
         <v>24</v>
       </c>
       <c r="M114" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O114" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B115" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="C115" t="s">
         <v>35</v>
       </c>
       <c r="D115" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E115" t="s">
         <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G115" t="s">
         <v>20</v>
@@ -6513,15 +6929,24 @@
         <v>24</v>
       </c>
       <c r="M115" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="N115" t="s">
+        <v>445</v>
+      </c>
+      <c r="O115" t="s">
+        <v>23</v>
+      </c>
+      <c r="P115" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="B116" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="C116" t="s">
         <v>28</v>
@@ -6533,7 +6958,7 @@
         <v>19</v>
       </c>
       <c r="F116" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G116" t="s">
         <v>20</v>
@@ -6554,15 +6979,18 @@
         <v>24</v>
       </c>
       <c r="M116" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O116" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="B117" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C117" t="s">
         <v>35</v>
@@ -6574,7 +7002,7 @@
         <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G117" t="s">
         <v>20</v>
@@ -6595,27 +7023,30 @@
         <v>24</v>
       </c>
       <c r="M117" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O117" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="B118" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="C118" t="s">
         <v>28</v>
       </c>
       <c r="D118" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E118" t="s">
         <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G118" t="s">
         <v>20</v>
@@ -6636,27 +7067,30 @@
         <v>24</v>
       </c>
       <c r="M118" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O118" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B119" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="C119" t="s">
         <v>35</v>
       </c>
       <c r="D119" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E119" t="s">
         <v>19</v>
       </c>
       <c r="F119" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G119" t="s">
         <v>20</v>
@@ -6677,15 +7111,18 @@
         <v>24</v>
       </c>
       <c r="M119" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O119" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="B120" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="C120" t="s">
         <v>28</v>
@@ -6697,7 +7134,7 @@
         <v>19</v>
       </c>
       <c r="F120" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G120" t="s">
         <v>20</v>
@@ -6718,15 +7155,18 @@
         <v>24</v>
       </c>
       <c r="M120" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O120" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B121" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="C121" t="s">
         <v>35</v>
@@ -6738,7 +7178,7 @@
         <v>19</v>
       </c>
       <c r="F121" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G121" t="s">
         <v>20</v>
@@ -6759,15 +7199,18 @@
         <v>24</v>
       </c>
       <c r="M121" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O121" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="B122" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="C122" t="s">
         <v>35</v>
@@ -6779,7 +7222,7 @@
         <v>19</v>
       </c>
       <c r="F122" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G122" t="s">
         <v>20</v>
@@ -6800,15 +7243,18 @@
         <v>24</v>
       </c>
       <c r="M122" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O122" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B123" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C123" t="s">
         <v>35</v>
@@ -6820,7 +7266,7 @@
         <v>32</v>
       </c>
       <c r="F123" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G123" t="s">
         <v>20</v>
@@ -6841,15 +7287,18 @@
         <v>24</v>
       </c>
       <c r="M123" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O123" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="B124" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="C124" t="s">
         <v>28</v>
@@ -6861,7 +7310,7 @@
         <v>19</v>
       </c>
       <c r="F124" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G124" t="s">
         <v>20</v>
@@ -6882,15 +7331,18 @@
         <v>24</v>
       </c>
       <c r="M124" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O124" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B125" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C125" t="s">
         <v>35</v>
@@ -6902,7 +7354,7 @@
         <v>19</v>
       </c>
       <c r="F125" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G125" t="s">
         <v>20</v>
@@ -6923,15 +7375,18 @@
         <v>24</v>
       </c>
       <c r="M125" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O125" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="B126" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="C126" t="s">
         <v>28</v>
@@ -6943,7 +7398,7 @@
         <v>19</v>
       </c>
       <c r="F126" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G126" t="s">
         <v>20</v>
@@ -6961,18 +7416,21 @@
         <v>23</v>
       </c>
       <c r="L126" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M126" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O126" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="B127" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C127" t="s">
         <v>28</v>
@@ -6984,7 +7442,7 @@
         <v>19</v>
       </c>
       <c r="F127" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G127" t="s">
         <v>20</v>
@@ -7002,18 +7460,21 @@
         <v>23</v>
       </c>
       <c r="L127" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M127" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O127" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B128" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="C128" t="s">
         <v>35</v>
@@ -7025,7 +7486,7 @@
         <v>19</v>
       </c>
       <c r="F128" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G128" t="s">
         <v>20</v>
@@ -7043,18 +7504,21 @@
         <v>23</v>
       </c>
       <c r="L128" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M128" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O128" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="B129" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="C129" t="s">
         <v>35</v>
@@ -7066,7 +7530,7 @@
         <v>19</v>
       </c>
       <c r="F129" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G129" t="s">
         <v>20</v>
@@ -7084,18 +7548,21 @@
         <v>23</v>
       </c>
       <c r="L129" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M129" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O129" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B130" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C130" t="s">
         <v>35</v>
@@ -7107,7 +7574,7 @@
         <v>19</v>
       </c>
       <c r="F130" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G130" t="s">
         <v>20</v>
@@ -7125,18 +7592,21 @@
         <v>23</v>
       </c>
       <c r="L130" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M130" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O130" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B131" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C131" t="s">
         <v>28</v>
@@ -7148,7 +7618,7 @@
         <v>19</v>
       </c>
       <c r="F131" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G131" t="s">
         <v>20</v>
@@ -7166,18 +7636,21 @@
         <v>23</v>
       </c>
       <c r="L131" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M131" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O131" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B132" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="C132" t="s">
         <v>35</v>
@@ -7189,7 +7662,7 @@
         <v>32</v>
       </c>
       <c r="F132" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G132" t="s">
         <v>20</v>
@@ -7207,18 +7680,21 @@
         <v>23</v>
       </c>
       <c r="L132" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M132" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O132" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B133" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C133" t="s">
         <v>28</v>
@@ -7230,7 +7706,7 @@
         <v>19</v>
       </c>
       <c r="F133" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G133" t="s">
         <v>20</v>
@@ -7248,18 +7724,21 @@
         <v>23</v>
       </c>
       <c r="L133" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M133" t="s">
+        <v>271</v>
+      </c>
+      <c r="O133" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>301</v>
-      </c>
       <c r="B134" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C134" t="s">
         <v>35</v>
@@ -7271,7 +7750,7 @@
         <v>32</v>
       </c>
       <c r="F134" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G134" t="s">
         <v>20</v>
@@ -7289,18 +7768,21 @@
         <v>23</v>
       </c>
       <c r="L134" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M134" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O134" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B135" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="C135" t="s">
         <v>35</v>
@@ -7312,7 +7794,7 @@
         <v>19</v>
       </c>
       <c r="F135" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G135" t="s">
         <v>20</v>
@@ -7330,18 +7812,21 @@
         <v>23</v>
       </c>
       <c r="L135" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M135" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O135" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B136" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C136" t="s">
         <v>35</v>
@@ -7353,7 +7838,7 @@
         <v>19</v>
       </c>
       <c r="F136" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G136" t="s">
         <v>20</v>
@@ -7371,18 +7856,21 @@
         <v>23</v>
       </c>
       <c r="L136" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M136" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O136" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B137" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="C137" t="s">
         <v>35</v>
@@ -7394,7 +7882,7 @@
         <v>19</v>
       </c>
       <c r="F137" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G137" t="s">
         <v>20</v>
@@ -7412,18 +7900,21 @@
         <v>23</v>
       </c>
       <c r="L137" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M137" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O137" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B138" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C138" t="s">
         <v>35</v>
@@ -7435,7 +7926,7 @@
         <v>32</v>
       </c>
       <c r="F138" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G138" t="s">
         <v>20</v>
@@ -7453,18 +7944,21 @@
         <v>23</v>
       </c>
       <c r="L138" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M138" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O138" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="B139" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C139" t="s">
         <v>28</v>
@@ -7476,7 +7970,7 @@
         <v>19</v>
       </c>
       <c r="F139" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G139" t="s">
         <v>20</v>
@@ -7494,18 +7988,21 @@
         <v>23</v>
       </c>
       <c r="L139" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M139" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O139" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B140" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="C140" t="s">
         <v>35</v>
@@ -7517,7 +8014,7 @@
         <v>19</v>
       </c>
       <c r="F140" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G140" t="s">
         <v>20</v>
@@ -7535,18 +8032,21 @@
         <v>23</v>
       </c>
       <c r="L140" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M140" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O140" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B141" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="C141" t="s">
         <v>28</v>
@@ -7558,7 +8058,7 @@
         <v>19</v>
       </c>
       <c r="F141" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G141" t="s">
         <v>20</v>
@@ -7576,18 +8076,21 @@
         <v>23</v>
       </c>
       <c r="L141" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M141" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O141" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="B142" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="C142" t="s">
         <v>35</v>
@@ -7599,7 +8102,7 @@
         <v>19</v>
       </c>
       <c r="F142" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G142" t="s">
         <v>20</v>
@@ -7617,30 +8120,33 @@
         <v>23</v>
       </c>
       <c r="L142" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M142" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O142" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="B143" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="C143" t="s">
         <v>28</v>
       </c>
       <c r="D143" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
       </c>
       <c r="F143" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G143" t="s">
         <v>20</v>
@@ -7658,30 +8164,33 @@
         <v>23</v>
       </c>
       <c r="L143" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M143" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O143" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B144" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C144" t="s">
         <v>35</v>
       </c>
       <c r="D144" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E144" t="s">
         <v>32</v>
       </c>
       <c r="F144" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G144" t="s">
         <v>20</v>
@@ -7699,30 +8208,33 @@
         <v>23</v>
       </c>
       <c r="L144" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M144" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O144" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="B145" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="C145" t="s">
         <v>35</v>
       </c>
       <c r="D145" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E145" t="s">
         <v>32</v>
       </c>
       <c r="F145" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G145" t="s">
         <v>20</v>
@@ -7740,18 +8252,21 @@
         <v>23</v>
       </c>
       <c r="L145" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M145" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O145" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="B146" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="C146" t="s">
         <v>28</v>
@@ -7763,7 +8278,7 @@
         <v>19</v>
       </c>
       <c r="F146" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G146" t="s">
         <v>20</v>
@@ -7781,18 +8296,21 @@
         <v>23</v>
       </c>
       <c r="L146" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M146" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O146" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="B147" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="C147" t="s">
         <v>35</v>
@@ -7804,7 +8322,7 @@
         <v>19</v>
       </c>
       <c r="F147" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G147" t="s">
         <v>20</v>
@@ -7822,30 +8340,33 @@
         <v>23</v>
       </c>
       <c r="L147" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M147" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O147" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="B148" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="C148" t="s">
         <v>35</v>
       </c>
       <c r="D148" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E148" t="s">
         <v>32</v>
       </c>
       <c r="F148" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G148" t="s">
         <v>20</v>
@@ -7863,18 +8384,21 @@
         <v>23</v>
       </c>
       <c r="L148" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M148" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O148" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="B149" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="C149" t="s">
         <v>28</v>
@@ -7886,7 +8410,7 @@
         <v>19</v>
       </c>
       <c r="F149" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G149" t="s">
         <v>20</v>
@@ -7904,30 +8428,33 @@
         <v>23</v>
       </c>
       <c r="L149" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M149" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O149" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="B150" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="C150" t="s">
         <v>35</v>
       </c>
       <c r="D150" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E150" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F150" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G150" t="s">
         <v>20</v>
@@ -7945,18 +8472,27 @@
         <v>23</v>
       </c>
       <c r="L150" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M150" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="N150" t="s">
+        <v>446</v>
+      </c>
+      <c r="O150" t="s">
+        <v>23</v>
+      </c>
+      <c r="P150" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="B151" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C151" t="s">
         <v>28</v>
@@ -7968,7 +8504,7 @@
         <v>19</v>
       </c>
       <c r="F151" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G151" t="s">
         <v>20</v>
@@ -7986,18 +8522,21 @@
         <v>23</v>
       </c>
       <c r="L151" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M151" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O151" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="B152" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C152" t="s">
         <v>28</v>
@@ -8009,7 +8548,7 @@
         <v>19</v>
       </c>
       <c r="F152" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G152" t="s">
         <v>20</v>
@@ -8027,18 +8566,21 @@
         <v>23</v>
       </c>
       <c r="L152" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M152" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O152" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B153" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="C153" t="s">
         <v>35</v>
@@ -8050,7 +8592,7 @@
         <v>19</v>
       </c>
       <c r="F153" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G153" t="s">
         <v>20</v>
@@ -8068,18 +8610,21 @@
         <v>23</v>
       </c>
       <c r="L153" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M153" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O153" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="B154" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="C154" t="s">
         <v>28</v>
@@ -8091,7 +8636,7 @@
         <v>19</v>
       </c>
       <c r="F154" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G154" t="s">
         <v>20</v>
@@ -8109,18 +8654,21 @@
         <v>23</v>
       </c>
       <c r="L154" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M154" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O154" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B155" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C155" t="s">
         <v>35</v>
@@ -8132,7 +8680,7 @@
         <v>19</v>
       </c>
       <c r="F155" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G155" t="s">
         <v>20</v>
@@ -8150,30 +8698,33 @@
         <v>23</v>
       </c>
       <c r="L155" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M155" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O155" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="B156" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C156" t="s">
         <v>28</v>
       </c>
       <c r="D156" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E156" t="s">
         <v>19</v>
       </c>
       <c r="F156" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G156" t="s">
         <v>20</v>
@@ -8191,30 +8742,33 @@
         <v>23</v>
       </c>
       <c r="L156" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M156" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O156" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="B157" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C157" t="s">
         <v>35</v>
       </c>
       <c r="D157" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E157" t="s">
         <v>32</v>
       </c>
       <c r="F157" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G157" t="s">
         <v>20</v>
@@ -8232,18 +8786,21 @@
         <v>23</v>
       </c>
       <c r="L157" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M157" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O157" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="B158" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C158" t="s">
         <v>28</v>
@@ -8255,7 +8812,7 @@
         <v>19</v>
       </c>
       <c r="F158" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G158" t="s">
         <v>20</v>
@@ -8273,18 +8830,21 @@
         <v>23</v>
       </c>
       <c r="L158" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M158" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O158" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="B159" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="C159" t="s">
         <v>35</v>
@@ -8296,7 +8856,7 @@
         <v>19</v>
       </c>
       <c r="F159" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G159" t="s">
         <v>20</v>
@@ -8314,30 +8874,33 @@
         <v>23</v>
       </c>
       <c r="L159" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M159" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O159" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="B160" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C160" t="s">
         <v>28</v>
       </c>
       <c r="D160" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
       </c>
       <c r="F160" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G160" t="s">
         <v>20</v>
@@ -8355,30 +8918,33 @@
         <v>23</v>
       </c>
       <c r="L160" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M160" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O160" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="B161" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C161" t="s">
         <v>35</v>
       </c>
       <c r="D161" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
       </c>
       <c r="F161" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G161" t="s">
         <v>20</v>
@@ -8396,18 +8962,21 @@
         <v>23</v>
       </c>
       <c r="L161" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M161" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O161" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="B162" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C162" t="s">
         <v>28</v>
@@ -8419,7 +8988,7 @@
         <v>19</v>
       </c>
       <c r="F162" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G162" t="s">
         <v>20</v>
@@ -8437,18 +9006,21 @@
         <v>23</v>
       </c>
       <c r="L162" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M162" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O162" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="B163" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C163" t="s">
         <v>35</v>
@@ -8460,7 +9032,7 @@
         <v>32</v>
       </c>
       <c r="F163" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G163" t="s">
         <v>20</v>
@@ -8478,18 +9050,21 @@
         <v>23</v>
       </c>
       <c r="L163" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M163" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O163" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="B164" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C164" t="s">
         <v>35</v>
@@ -8501,7 +9076,7 @@
         <v>19</v>
       </c>
       <c r="F164" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G164" t="s">
         <v>20</v>
@@ -8519,18 +9094,21 @@
         <v>23</v>
       </c>
       <c r="L164" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M164" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O164" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="B165" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C165" t="s">
         <v>35</v>
@@ -8539,10 +9117,10 @@
         <v>31</v>
       </c>
       <c r="E165" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F165" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G165" t="s">
         <v>20</v>
@@ -8560,18 +9138,21 @@
         <v>23</v>
       </c>
       <c r="L165" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="M165" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="O165" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B166" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C166" t="s">
         <v>28</v>
@@ -8583,7 +9164,7 @@
         <v>19</v>
       </c>
       <c r="F166" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G166" t="s">
         <v>20</v>
@@ -8598,33 +9179,36 @@
         <v>2024</v>
       </c>
       <c r="K166" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L166" t="s">
         <v>24</v>
       </c>
       <c r="M166" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O166" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="B167" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="C167" t="s">
         <v>35</v>
       </c>
       <c r="D167" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E167" t="s">
         <v>19</v>
       </c>
       <c r="F167" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G167" t="s">
         <v>20</v>
@@ -8639,21 +9223,24 @@
         <v>2024</v>
       </c>
       <c r="K167" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L167" t="s">
         <v>24</v>
       </c>
       <c r="M167" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O167" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="B168" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="C168" t="s">
         <v>28</v>
@@ -8665,7 +9252,7 @@
         <v>19</v>
       </c>
       <c r="F168" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G168" t="s">
         <v>20</v>
@@ -8680,21 +9267,24 @@
         <v>2024</v>
       </c>
       <c r="K168" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L168" t="s">
         <v>24</v>
       </c>
       <c r="M168" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O168" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="B169" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C169" t="s">
         <v>35</v>
@@ -8706,7 +9296,7 @@
         <v>32</v>
       </c>
       <c r="F169" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G169" t="s">
         <v>20</v>
@@ -8721,21 +9311,24 @@
         <v>2024</v>
       </c>
       <c r="K169" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L169" t="s">
         <v>24</v>
       </c>
       <c r="M169" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O169" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="B170" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C170" t="s">
         <v>35</v>
@@ -8744,10 +9337,10 @@
         <v>49</v>
       </c>
       <c r="E170" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F170" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G170" t="s">
         <v>20</v>
@@ -8762,33 +9355,36 @@
         <v>2024</v>
       </c>
       <c r="K170" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L170" t="s">
         <v>24</v>
       </c>
       <c r="M170" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O170" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B171" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C171" t="s">
         <v>35</v>
       </c>
       <c r="D171" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E171" t="s">
         <v>19</v>
       </c>
       <c r="F171" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G171" t="s">
         <v>20</v>
@@ -8803,33 +9399,36 @@
         <v>2024</v>
       </c>
       <c r="K171" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L171" t="s">
         <v>24</v>
       </c>
       <c r="M171" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O171" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B172" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C172" t="s">
         <v>35</v>
       </c>
       <c r="D172" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E172" t="s">
         <v>32</v>
       </c>
       <c r="F172" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G172" t="s">
         <v>20</v>
@@ -8844,33 +9443,36 @@
         <v>2024</v>
       </c>
       <c r="K172" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L172" t="s">
         <v>24</v>
       </c>
       <c r="M172" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O172" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="B173" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="C173" t="s">
         <v>35</v>
       </c>
       <c r="D173" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E173" t="s">
         <v>32</v>
       </c>
       <c r="F173" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G173" t="s">
         <v>20</v>
@@ -8885,21 +9487,24 @@
         <v>2024</v>
       </c>
       <c r="K173" t="s">
+        <v>351</v>
+      </c>
+      <c r="L173" t="s">
+        <v>24</v>
+      </c>
+      <c r="M173" t="s">
+        <v>151</v>
+      </c>
+      <c r="O173" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
         <v>366</v>
       </c>
-      <c r="L173" t="s">
-        <v>24</v>
-      </c>
-      <c r="M173" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>381</v>
-      </c>
       <c r="B174" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="C174" t="s">
         <v>28</v>
@@ -8911,7 +9516,7 @@
         <v>19</v>
       </c>
       <c r="F174" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G174" t="s">
         <v>20</v>
@@ -8926,21 +9531,24 @@
         <v>2024</v>
       </c>
       <c r="K174" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L174" t="s">
         <v>24</v>
       </c>
       <c r="M174" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O174" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="B175" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="C175" t="s">
         <v>35</v>
@@ -8952,7 +9560,7 @@
         <v>19</v>
       </c>
       <c r="F175" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G175" t="s">
         <v>20</v>
@@ -8967,21 +9575,24 @@
         <v>2024</v>
       </c>
       <c r="K175" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L175" t="s">
         <v>24</v>
       </c>
       <c r="M175" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O175" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="B176" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="C176" t="s">
         <v>35</v>
@@ -8993,7 +9604,7 @@
         <v>19</v>
       </c>
       <c r="F176" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G176" t="s">
         <v>20</v>
@@ -9008,21 +9619,24 @@
         <v>2024</v>
       </c>
       <c r="K176" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L176" t="s">
         <v>24</v>
       </c>
       <c r="M176" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O176" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B177" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="C177" t="s">
         <v>35</v>
@@ -9034,7 +9648,7 @@
         <v>19</v>
       </c>
       <c r="F177" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G177" t="s">
         <v>20</v>
@@ -9049,21 +9663,24 @@
         <v>2024</v>
       </c>
       <c r="K177" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L177" t="s">
         <v>24</v>
       </c>
       <c r="M177" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O177" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="B178" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="C178" t="s">
         <v>35</v>
@@ -9075,7 +9692,7 @@
         <v>19</v>
       </c>
       <c r="F178" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G178" t="s">
         <v>20</v>
@@ -9090,21 +9707,24 @@
         <v>2024</v>
       </c>
       <c r="K178" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L178" t="s">
         <v>24</v>
       </c>
       <c r="M178" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O178" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="B179" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C179" t="s">
         <v>35</v>
@@ -9116,7 +9736,7 @@
         <v>32</v>
       </c>
       <c r="F179" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G179" t="s">
         <v>20</v>
@@ -9131,21 +9751,24 @@
         <v>2024</v>
       </c>
       <c r="K179" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L179" t="s">
         <v>24</v>
       </c>
       <c r="M179" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O179" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="B180" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="C180" t="s">
         <v>28</v>
@@ -9157,7 +9780,7 @@
         <v>19</v>
       </c>
       <c r="F180" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G180" t="s">
         <v>20</v>
@@ -9172,21 +9795,24 @@
         <v>2024</v>
       </c>
       <c r="K180" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L180" t="s">
         <v>24</v>
       </c>
       <c r="M180" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O180" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B181" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="C181" t="s">
         <v>35</v>
@@ -9198,7 +9824,7 @@
         <v>19</v>
       </c>
       <c r="F181" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G181" t="s">
         <v>20</v>
@@ -9213,21 +9839,24 @@
         <v>2024</v>
       </c>
       <c r="K181" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L181" t="s">
         <v>24</v>
       </c>
       <c r="M181" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O181" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="B182" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="C182" t="s">
         <v>35</v>
@@ -9239,7 +9868,7 @@
         <v>19</v>
       </c>
       <c r="F182" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G182" t="s">
         <v>20</v>
@@ -9254,21 +9883,30 @@
         <v>2024</v>
       </c>
       <c r="K182" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L182" t="s">
         <v>24</v>
       </c>
       <c r="M182" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="N182" t="s">
+        <v>447</v>
+      </c>
+      <c r="O182" t="s">
+        <v>23</v>
+      </c>
+      <c r="P182" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="B183" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="C183" t="s">
         <v>35</v>
@@ -9280,7 +9918,7 @@
         <v>32</v>
       </c>
       <c r="F183" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G183" t="s">
         <v>20</v>
@@ -9295,21 +9933,24 @@
         <v>2024</v>
       </c>
       <c r="K183" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L183" t="s">
         <v>24</v>
       </c>
       <c r="M183" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O183" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="B184" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="C184" t="s">
         <v>28</v>
@@ -9321,7 +9962,7 @@
         <v>19</v>
       </c>
       <c r="F184" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G184" t="s">
         <v>20</v>
@@ -9336,21 +9977,24 @@
         <v>2024</v>
       </c>
       <c r="K184" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L184" t="s">
         <v>24</v>
       </c>
       <c r="M184" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O184" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="B185" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="C185" t="s">
         <v>35</v>
@@ -9362,7 +10006,7 @@
         <v>19</v>
       </c>
       <c r="F185" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G185" t="s">
         <v>20</v>
@@ -9377,21 +10021,24 @@
         <v>2024</v>
       </c>
       <c r="K185" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L185" t="s">
         <v>24</v>
       </c>
       <c r="M185" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O185" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="B186" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="C186" t="s">
         <v>35</v>
@@ -9403,7 +10050,7 @@
         <v>19</v>
       </c>
       <c r="F186" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G186" t="s">
         <v>20</v>
@@ -9418,21 +10065,24 @@
         <v>2024</v>
       </c>
       <c r="K186" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L186" t="s">
         <v>24</v>
       </c>
       <c r="M186" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O186" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="B187" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C187" t="s">
         <v>28</v>
@@ -9444,7 +10094,7 @@
         <v>32</v>
       </c>
       <c r="F187" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G187" t="s">
         <v>20</v>
@@ -9459,21 +10109,24 @@
         <v>2025</v>
       </c>
       <c r="K187" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L187" t="s">
         <v>24</v>
       </c>
       <c r="M187" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O187" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B188" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="C188" t="s">
         <v>28</v>
@@ -9485,7 +10138,7 @@
         <v>19</v>
       </c>
       <c r="F188" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G188" t="s">
         <v>20</v>
@@ -9500,21 +10153,24 @@
         <v>2025</v>
       </c>
       <c r="K188" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L188" t="s">
         <v>24</v>
       </c>
       <c r="M188" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O188" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="B189" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="C189" t="s">
         <v>35</v>
@@ -9526,7 +10182,7 @@
         <v>32</v>
       </c>
       <c r="F189" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G189" t="s">
         <v>20</v>
@@ -9541,21 +10197,24 @@
         <v>2025</v>
       </c>
       <c r="K189" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L189" t="s">
         <v>24</v>
       </c>
       <c r="M189" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O189" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="B190" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C190" t="s">
         <v>35</v>
@@ -9567,7 +10226,7 @@
         <v>32</v>
       </c>
       <c r="F190" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G190" t="s">
         <v>20</v>
@@ -9582,21 +10241,24 @@
         <v>2025</v>
       </c>
       <c r="K190" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L190" t="s">
         <v>24</v>
       </c>
       <c r="M190" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O190" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="B191" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="C191" t="s">
         <v>35</v>
@@ -9608,7 +10270,7 @@
         <v>19</v>
       </c>
       <c r="F191" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G191" t="s">
         <v>20</v>
@@ -9623,21 +10285,24 @@
         <v>2025</v>
       </c>
       <c r="K191" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L191" t="s">
         <v>24</v>
       </c>
       <c r="M191" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O191" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="B192" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C192" t="s">
         <v>35</v>
@@ -9649,7 +10314,7 @@
         <v>32</v>
       </c>
       <c r="F192" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G192" t="s">
         <v>20</v>
@@ -9664,21 +10329,24 @@
         <v>2025</v>
       </c>
       <c r="K192" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L192" t="s">
         <v>24</v>
       </c>
       <c r="M192" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O192" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="B193" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="C193" t="s">
         <v>35</v>
@@ -9690,7 +10358,7 @@
         <v>32</v>
       </c>
       <c r="F193" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G193" t="s">
         <v>20</v>
@@ -9705,21 +10373,24 @@
         <v>2025</v>
       </c>
       <c r="K193" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L193" t="s">
         <v>24</v>
       </c>
       <c r="M193" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O193" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="B194" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="C194" t="s">
         <v>35</v>
@@ -9731,7 +10402,7 @@
         <v>19</v>
       </c>
       <c r="F194" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G194" t="s">
         <v>20</v>
@@ -9746,21 +10417,24 @@
         <v>2025</v>
       </c>
       <c r="K194" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L194" t="s">
         <v>24</v>
       </c>
       <c r="M194" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O194" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="B195" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="C195" t="s">
         <v>28</v>
@@ -9772,7 +10446,7 @@
         <v>19</v>
       </c>
       <c r="F195" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G195" t="s">
         <v>20</v>
@@ -9787,21 +10461,24 @@
         <v>2025</v>
       </c>
       <c r="K195" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L195" t="s">
         <v>24</v>
       </c>
       <c r="M195" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O195" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="B196" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C196" t="s">
         <v>35</v>
@@ -9813,7 +10490,7 @@
         <v>32</v>
       </c>
       <c r="F196" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G196" t="s">
         <v>20</v>
@@ -9828,21 +10505,24 @@
         <v>2025</v>
       </c>
       <c r="K196" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L196" t="s">
         <v>24</v>
       </c>
       <c r="M196" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O196" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="B197" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="C197" t="s">
         <v>35</v>
@@ -9854,7 +10534,7 @@
         <v>32</v>
       </c>
       <c r="F197" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G197" t="s">
         <v>20</v>
@@ -9869,21 +10549,24 @@
         <v>2025</v>
       </c>
       <c r="K197" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L197" t="s">
         <v>24</v>
       </c>
       <c r="M197" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O197" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="B198" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="C198" t="s">
         <v>28</v>
@@ -9895,7 +10578,7 @@
         <v>19</v>
       </c>
       <c r="F198" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G198" t="s">
         <v>20</v>
@@ -9910,21 +10593,24 @@
         <v>2025</v>
       </c>
       <c r="K198" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L198" t="s">
         <v>24</v>
       </c>
       <c r="M198" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O198" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="B199" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C199" t="s">
         <v>35</v>
@@ -9936,7 +10622,7 @@
         <v>32</v>
       </c>
       <c r="F199" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G199" t="s">
         <v>20</v>
@@ -9951,21 +10637,24 @@
         <v>2025</v>
       </c>
       <c r="K199" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L199" t="s">
         <v>24</v>
       </c>
       <c r="M199" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O199" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="B200" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C200" t="s">
         <v>35</v>
@@ -9977,7 +10666,7 @@
         <v>19</v>
       </c>
       <c r="F200" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G200" t="s">
         <v>20</v>
@@ -9992,21 +10681,24 @@
         <v>2025</v>
       </c>
       <c r="K200" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L200" t="s">
         <v>24</v>
       </c>
       <c r="M200" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O200" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="B201" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="C201" t="s">
         <v>28</v>
@@ -10018,7 +10710,7 @@
         <v>19</v>
       </c>
       <c r="F201" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G201" t="s">
         <v>20</v>
@@ -10033,21 +10725,24 @@
         <v>2025</v>
       </c>
       <c r="K201" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L201" t="s">
         <v>24</v>
       </c>
       <c r="M201" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O201" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="B202" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="C202" t="s">
         <v>35</v>
@@ -10059,7 +10754,7 @@
         <v>32</v>
       </c>
       <c r="F202" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G202" t="s">
         <v>20</v>
@@ -10074,33 +10769,36 @@
         <v>2025</v>
       </c>
       <c r="K202" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L202" t="s">
         <v>24</v>
       </c>
       <c r="M202" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O202" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="B203" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="C203" t="s">
         <v>28</v>
       </c>
       <c r="D203" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="E203" t="s">
         <v>19</v>
       </c>
       <c r="F203" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G203" t="s">
         <v>20</v>
@@ -10115,21 +10813,24 @@
         <v>2025</v>
       </c>
       <c r="K203" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L203" t="s">
         <v>24</v>
       </c>
       <c r="M203" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O203" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="B204" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="C204" t="s">
         <v>35</v>
@@ -10141,7 +10842,7 @@
         <v>32</v>
       </c>
       <c r="F204" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G204" t="s">
         <v>20</v>
@@ -10156,33 +10857,36 @@
         <v>2025</v>
       </c>
       <c r="K204" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L204" t="s">
         <v>24</v>
       </c>
       <c r="M204" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O204" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="B205" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="C205" t="s">
         <v>35</v>
       </c>
       <c r="D205" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E205" t="s">
         <v>19</v>
       </c>
       <c r="F205" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G205" t="s">
         <v>20</v>
@@ -10197,21 +10901,24 @@
         <v>2025</v>
       </c>
       <c r="K205" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L205" t="s">
         <v>24</v>
       </c>
       <c r="M205" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O205" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="B206" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="C206" t="s">
         <v>35</v>
@@ -10223,7 +10930,7 @@
         <v>19</v>
       </c>
       <c r="F206" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G206" t="s">
         <v>20</v>
@@ -10238,21 +10945,24 @@
         <v>2025</v>
       </c>
       <c r="K206" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L206" t="s">
         <v>24</v>
       </c>
       <c r="M206" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="O206" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="B207" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C207" t="s">
         <v>35</v>
@@ -10264,7 +10974,7 @@
         <v>19</v>
       </c>
       <c r="F207" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G207" t="s">
         <v>20</v>
@@ -10279,16 +10989,20 @@
         <v>2025</v>
       </c>
       <c r="K207" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="L207" t="s">
         <v>24</v>
       </c>
       <c r="M207" t="s">
-        <v>152</v>
+        <v>151</v>
+      </c>
+      <c r="O207" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <tableParts count="1">
